--- a/output/daily_screen_latest.xlsx
+++ b/output/daily_screen_latest.xlsx
@@ -1306,16 +1306,16 @@
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>37.47320239519422</v>
+        <v>37.47320239521468</v>
       </c>
       <c r="O7" t="n">
-        <v>32.13289453547415</v>
+        <v>32.13289453551437</v>
       </c>
       <c r="P7" t="n">
-        <v>5.34030785972007</v>
+        <v>5.340307859700317</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.239495932092019</v>
+        <v>3.239495932069605</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -14123,16 +14123,16 @@
         <v>43.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>37.47320239519422</v>
+        <v>37.47320239521468</v>
       </c>
       <c r="AL7" t="n">
-        <v>32.13289453547415</v>
+        <v>32.13289453551437</v>
       </c>
       <c r="AM7" t="n">
-        <v>5.34030785972007</v>
+        <v>5.340307859700317</v>
       </c>
       <c r="AN7" t="n">
-        <v>3.239495932092019</v>
+        <v>3.239495932069605</v>
       </c>
       <c r="AO7" t="b">
         <v>1</v>

--- a/output/daily_screen_latest.xlsx
+++ b/output/daily_screen_latest.xlsx
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>87.01960784313724</v>
+        <v>86.8235294117647</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -683,34 +683,34 @@
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>169.5</v>
+        <v>165</v>
       </c>
       <c r="Q2" t="n">
-        <v>169.5</v>
+        <v>165</v>
       </c>
       <c r="R2" t="n">
-        <v>18986171</v>
+        <v>35905249</v>
       </c>
       <c r="S2" t="n">
-        <v>158.8</v>
+        <v>157.9</v>
       </c>
       <c r="T2" t="n">
-        <v>135.575</v>
+        <v>135.35</v>
       </c>
       <c r="U2" t="n">
         <v>132.275</v>
       </c>
       <c r="V2" t="n">
-        <v>110.8433097839356</v>
+        <v>110.7683097839355</v>
       </c>
       <c r="W2" t="n">
-        <v>11.60123923392149</v>
+        <v>11.10123923392149</v>
       </c>
       <c r="X2" t="n">
-        <v>10.07186847632805</v>
+        <v>9.971868476328046</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.529370757593444</v>
+        <v>1.129370757593444</v>
       </c>
       <c r="Z2" t="n">
         <v>0.8483992520466259</v>
@@ -719,25 +719,25 @@
         <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.6376811594202898</v>
+        <v>0.5942028985507246</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.092205162957239</v>
+        <v>1.036659893144215</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.5173764102410146</v>
+        <v>0.5014063875337269</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.7205181676231789</v>
+        <v>0.6095502522474923</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.2031417573821643</v>
+        <v>-0.1081438647137654</v>
       </c>
       <c r="AG2" t="n">
         <v>98.0392156862745</v>
       </c>
       <c r="AH2" t="n">
-        <v>76.47058823529412</v>
+        <v>74.50980392156863</v>
       </c>
       <c r="AI2" t="b">
         <v>1</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>77.01960784313725</v>
+        <v>75.64705882352941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -823,34 +823,34 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>19.45000076293945</v>
+        <v>19.39999961853027</v>
       </c>
       <c r="Q3" t="n">
-        <v>19.45000076293945</v>
+        <v>19.39999961853027</v>
       </c>
       <c r="R3" t="n">
-        <v>23773017</v>
+        <v>35969294</v>
       </c>
       <c r="S3" t="n">
-        <v>19.20000038146973</v>
+        <v>19.19000015258789</v>
       </c>
       <c r="T3" t="n">
-        <v>18.74750022888184</v>
+        <v>18.74500017166138</v>
       </c>
       <c r="U3" t="n">
         <v>18.71750020980835</v>
       </c>
       <c r="V3" t="n">
-        <v>19.16583344141642</v>
+        <v>19.1650000890096</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1600980664793852</v>
+        <v>0.1545423837672537</v>
       </c>
       <c r="X3" t="n">
-        <v>0.06307514403880524</v>
+        <v>0.06196400749637893</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.09702292244057995</v>
+        <v>0.09257837627087478</v>
       </c>
       <c r="Z3" t="n">
         <v>0.09247098408578769</v>
@@ -859,25 +859,25 @@
         <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0318302583197585</v>
+        <v>0.02917767776817759</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.01566585641698337</v>
+        <v>0.01305483054725975</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.08847449085951675</v>
+        <v>-0.06361883324882012</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.3560211389170764</v>
+        <v>-0.4140548103494628</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2675466480575597</v>
+        <v>0.3504359771006427</v>
       </c>
       <c r="AG3" t="n">
-        <v>47.05882352941176</v>
+        <v>43.13725490196079</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.92156862745098</v>
+        <v>1.96078431372549</v>
       </c>
       <c r="AI3" t="b">
         <v>1</v>
@@ -916,21 +916,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>76.8235294117647</v>
+        <v>60.94117647058824</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,11 +943,11 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>511000</v>
+        <v>2169000</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
@@ -959,65 +959,65 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>511000</v>
+        <v>2169000</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>95.59999847412109</v>
+        <v>6030</v>
       </c>
       <c r="Q4" t="n">
-        <v>95.59999847412109</v>
+        <v>6030</v>
       </c>
       <c r="R4" t="n">
-        <v>1304441</v>
+        <v>397050</v>
       </c>
       <c r="S4" t="n">
-        <v>92.91999969482421</v>
+        <v>5817</v>
       </c>
       <c r="T4" t="n">
-        <v>83.58999938964844</v>
+        <v>5822.75</v>
       </c>
       <c r="U4" t="n">
-        <v>82.80999946594238</v>
+        <v>5772.75</v>
       </c>
       <c r="V4" t="n">
-        <v>81.47833302815755</v>
+        <v>4784.166666666667</v>
       </c>
       <c r="W4" t="n">
-        <v>3.959223821639995</v>
+        <v>103.7180619953206</v>
       </c>
       <c r="X4" t="n">
-        <v>2.399161345596774</v>
+        <v>173.5261543710339</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.560062476043221</v>
+        <v>-69.8080923757133</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.539528706158522</v>
+        <v>-96.5315853696751</v>
       </c>
       <c r="AA4" t="b">
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1949999809265137</v>
+        <v>0.1988071570576542</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.09132420250399176</v>
+        <v>1.216911764705882</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.07469523174723847</v>
+        <v>0.1060106460406565</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.280362792830068</v>
+        <v>0.7898021238091597</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3550580245773065</v>
+        <v>-0.6837914777685032</v>
       </c>
       <c r="AG4" t="n">
-        <v>76.47058823529412</v>
+        <v>80.3921568627451</v>
       </c>
       <c r="AH4" t="n">
-        <v>7.84313725490196</v>
+        <v>86.27450980392157</v>
       </c>
       <c r="AI4" t="b">
         <v>1</v>
@@ -1026,21 +1026,19 @@
         <v>1</v>
       </c>
       <c r="AK4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="b">
         <v>1</v>
       </c>
       <c r="AN4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>6825.96</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -1056,21 +1054,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>72.70588235294117</v>
+        <v>49.96078431372549</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,11 +1081,11 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3988000</v>
+        <v>1200000</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
@@ -1099,65 +1097,65 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3988000</v>
+        <v>1200000</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>100.5</v>
+        <v>1180</v>
       </c>
       <c r="Q5" t="n">
-        <v>100.5</v>
+        <v>1180</v>
       </c>
       <c r="R5" t="n">
-        <v>1868793</v>
+        <v>2639295</v>
       </c>
       <c r="S5" t="n">
-        <v>98.23999938964843</v>
+        <v>1163</v>
       </c>
       <c r="T5" t="n">
-        <v>95.50500030517578</v>
+        <v>1107.15</v>
       </c>
       <c r="U5" t="n">
-        <v>95.48000030517578</v>
+        <v>1098</v>
       </c>
       <c r="V5" t="n">
-        <v>97.97000033060709</v>
+        <v>999.9666666666667</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6890731394847336</v>
+        <v>34.38049037101223</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1833564236985528</v>
+        <v>41.23198174430112</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.8724295631832863</v>
+        <v>-6.851491373288887</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.792692952551374</v>
+        <v>-6.941223400875387</v>
       </c>
       <c r="AA5" t="b">
         <v>1</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.004999999999999893</v>
+        <v>0.1835506519558676</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1092715418610821</v>
+        <v>0.1028037383177569</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.1153047491792754</v>
+        <v>0.09075414093886991</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.2624154534729777</v>
+        <v>-0.3243059025789656</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1471107042937023</v>
+        <v>0.4150600435178355</v>
       </c>
       <c r="AG5" t="n">
-        <v>37.25490196078432</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="AH5" t="n">
-        <v>9.803921568627452</v>
+        <v>11.76470588235294</v>
       </c>
       <c r="AI5" t="b">
         <v>1</v>
@@ -1166,21 +1164,19 @@
         <v>1</v>
       </c>
       <c r="AK5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="b">
         <v>1</v>
       </c>
       <c r="AN5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1257.88</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -1196,21 +1192,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>71.92156862745099</v>
+        <v>45.64705882352941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1223,11 +1219,11 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1741000</v>
+        <v>1034000</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -1239,65 +1235,65 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1741000</v>
+        <v>1034000</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>220.5</v>
+        <v>1125</v>
       </c>
       <c r="Q6" t="n">
-        <v>220.5</v>
+        <v>1125</v>
       </c>
       <c r="R6" t="n">
-        <v>1621863</v>
+        <v>1561526</v>
       </c>
       <c r="S6" t="n">
-        <v>215.2</v>
+        <v>1081</v>
       </c>
       <c r="T6" t="n">
-        <v>208.325</v>
+        <v>1083.2</v>
       </c>
       <c r="U6" t="n">
-        <v>208.05</v>
+        <v>1080.7</v>
       </c>
       <c r="V6" t="n">
-        <v>207.4833333333333</v>
+        <v>1034.848440551758</v>
       </c>
       <c r="W6" t="n">
-        <v>3.515496398254413</v>
+        <v>0.3747388243014029</v>
       </c>
       <c r="X6" t="n">
-        <v>1.948391806133995</v>
+        <v>2.699578985391791</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.567104592120418</v>
+        <v>-2.324840161090388</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.554787379003262</v>
+        <v>-6.745457503645538</v>
       </c>
       <c r="AA6" t="b">
         <v>1</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0255813953488373</v>
+        <v>0.04651162790697683</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1605263157894736</v>
+        <v>0.6158535997364418</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.09472335383043795</v>
+        <v>-0.04628488311002088</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.2111606795445862</v>
+        <v>0.1887439588397193</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1164373257141482</v>
+        <v>-0.2350288419497402</v>
       </c>
       <c r="AG6" t="n">
-        <v>45.09803921568628</v>
+        <v>50.98039215686274</v>
       </c>
       <c r="AH6" t="n">
-        <v>13.72549019607843</v>
+        <v>49.01960784313725</v>
       </c>
       <c r="AI6" t="b">
         <v>1</v>
@@ -1306,21 +1302,19 @@
         <v>1</v>
       </c>
       <c r="AK6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="b">
         <v>1</v>
       </c>
       <c r="AN6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1152</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -1336,21 +1330,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>75.15686274509804</v>
+        <v>40.15686274509804</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1363,14 +1357,14 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>10828000</v>
+        <v>3645000</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="K7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
@@ -1379,66 +1373,66 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>10828000</v>
+        <v>3645000</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>891</v>
+        <v>325</v>
       </c>
       <c r="Q7" t="n">
-        <v>891</v>
+        <v>325</v>
       </c>
       <c r="R7" t="n">
-        <v>2569098</v>
+        <v>24070055</v>
       </c>
       <c r="S7" t="n">
-        <v>882</v>
+        <v>320.1</v>
       </c>
       <c r="T7" t="n">
-        <v>868.5</v>
+        <v>307.35</v>
       </c>
       <c r="U7" t="n">
-        <v>871.3</v>
+        <v>308.05</v>
       </c>
       <c r="V7" t="n">
-        <v>744.3666666666667</v>
+        <v>296.975</v>
       </c>
       <c r="W7" t="n">
-        <v>8.308209038491782</v>
+        <v>5.316555615809136</v>
       </c>
       <c r="X7" t="n">
-        <v>9.141430026102661</v>
+        <v>4.296119943221202</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.8332209876108791</v>
+        <v>1.020435672587935</v>
       </c>
       <c r="Z7" t="n">
-        <v>-1.186083704858063</v>
+        <v>0.7909858073156304</v>
       </c>
       <c r="AA7" t="b">
         <v>1</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.05913410770855332</v>
+        <v>-0.04129793510324486</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.106382978723404</v>
+        <v>0.1948529411764706</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.1794388568878286</v>
+        <v>-0.1340944461202426</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.7346959833893443</v>
+        <v>-0.232256699720252</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.9141348402771728</v>
+        <v>0.09816225360000941</v>
       </c>
       <c r="AG7" t="n">
+        <v>27.45098039215686</v>
+      </c>
+      <c r="AH7" t="n">
         <v>21.56862745098039</v>
       </c>
-      <c r="AH7" t="n">
-        <v>80.3921568627451</v>
-      </c>
       <c r="AI7" t="b">
         <v>1</v>
       </c>
@@ -1446,22 +1440,24 @@
         <v>0</v>
       </c>
       <c r="AK7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM7" t="b">
         <v>1</v>
       </c>
       <c r="AN7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>901.6900000000001</v>
+        <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP7" t="n">
-        <v>830.3200000000001</v>
+        <v>292.42</v>
       </c>
     </row>
     <row r="8">
@@ -1472,21 +1468,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>73.98039215686275</v>
+        <v>33.09803921568627</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1499,11 +1495,11 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2169000</v>
+        <v>1000</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
@@ -1515,71 +1511,71 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2169000</v>
+        <v>1000</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>6000</v>
+        <v>235.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>6000</v>
+        <v>235.5</v>
       </c>
       <c r="R8" t="n">
-        <v>197775</v>
+        <v>7502148</v>
       </c>
       <c r="S8" t="n">
-        <v>5811</v>
+        <v>229.2</v>
       </c>
       <c r="T8" t="n">
-        <v>5821.25</v>
+        <v>226.025</v>
       </c>
       <c r="U8" t="n">
-        <v>5772.75</v>
+        <v>226.675</v>
       </c>
       <c r="V8" t="n">
-        <v>4783.666666666667</v>
+        <v>193.5916666666667</v>
       </c>
       <c r="W8" t="n">
-        <v>100.3847286619866</v>
+        <v>3.301655800429103</v>
       </c>
       <c r="X8" t="n">
-        <v>172.8594877043671</v>
+        <v>4.029491294472227</v>
       </c>
       <c r="Y8" t="n">
-        <v>-72.47475904238044</v>
+        <v>-0.7278354940431244</v>
       </c>
       <c r="Z8" t="n">
-        <v>-96.5315853696751</v>
+        <v>-1.608171744958133</v>
       </c>
       <c r="AA8" t="b">
         <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1928429423459244</v>
+        <v>-0.0523138832997988</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.205882352941177</v>
+        <v>0.7706766917293233</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.07253819316664911</v>
+        <v>-0.1451103943167965</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.8341953576071168</v>
+        <v>0.3435670508326008</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.7616571644404677</v>
+        <v>-0.4886774451493973</v>
       </c>
       <c r="AG8" t="n">
-        <v>74.50980392156863</v>
+        <v>25.49019607843137</v>
       </c>
       <c r="AH8" t="n">
-        <v>84.31372549019608</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="AI8" t="b">
         <v>1</v>
       </c>
       <c r="AJ8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="b">
         <v>0</v>
@@ -1594,12 +1590,10 @@
         <v>1</v>
       </c>
       <c r="AO8" t="n">
-        <v>6816</v>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>243.98</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>214.03</v>
       </c>
     </row>
     <row r="9">
@@ -1610,21 +1604,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>71.82352941176471</v>
+        <v>77.21568627450981</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1637,11 +1631,11 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>7769000</v>
+        <v>18313000</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
@@ -1653,89 +1647,93 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>7769000</v>
+        <v>18313000</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>1340</v>
+        <v>755</v>
       </c>
       <c r="Q9" t="n">
-        <v>1340</v>
+        <v>755</v>
       </c>
       <c r="R9" t="n">
-        <v>711725</v>
+        <v>8871204</v>
       </c>
       <c r="S9" t="n">
-        <v>1329</v>
+        <v>789.8</v>
       </c>
       <c r="T9" t="n">
-        <v>1338.5</v>
+        <v>600.025</v>
       </c>
       <c r="U9" t="n">
-        <v>1344</v>
+        <v>580.85</v>
       </c>
       <c r="V9" t="n">
-        <v>1180.416666666667</v>
+        <v>393.0666666666667</v>
       </c>
       <c r="W9" t="n">
-        <v>2.973073487630927</v>
+        <v>91.51056474848281</v>
       </c>
       <c r="X9" t="n">
-        <v>6.799987779920381</v>
+        <v>87.04701482363542</v>
       </c>
       <c r="Y9" t="n">
-        <v>-3.826914292289453</v>
+        <v>4.463549924847385</v>
       </c>
       <c r="Z9" t="n">
-        <v>-4.612508583835297</v>
+        <v>15.75753401466386</v>
       </c>
       <c r="AA9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.07586206896551728</v>
+        <v>1.032301480484522</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.7608409986859395</v>
+        <v>2.038229376257545</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.1961668181447925</v>
+        <v>0.9395049694675246</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.3891540033518797</v>
+        <v>1.611119735360823</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.5853208214966722</v>
+        <v>-0.6716147658932983</v>
       </c>
       <c r="AG9" t="n">
-        <v>17.64705882352941</v>
+        <v>100</v>
       </c>
       <c r="AH9" t="n">
-        <v>62.74509803921568</v>
+        <v>96.07843137254902</v>
       </c>
       <c r="AI9" t="b">
         <v>1</v>
       </c>
       <c r="AJ9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1385.56</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1328.42</v>
+        <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1746,21 +1744,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>66.33333333333333</v>
+        <v>71.52941176470588</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1773,14 +1771,14 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6231000</v>
+        <v>71690000</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="b">
         <v>1</v>
@@ -1789,71 +1787,71 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>6231000</v>
+        <v>71690000</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>2520</v>
+        <v>125.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>2520</v>
+        <v>125.5</v>
       </c>
       <c r="R10" t="n">
-        <v>331526</v>
+        <v>151429262</v>
       </c>
       <c r="S10" t="n">
-        <v>2494</v>
+        <v>137.6</v>
       </c>
       <c r="T10" t="n">
-        <v>2499</v>
+        <v>119.9100002288818</v>
       </c>
       <c r="U10" t="n">
-        <v>2501</v>
+        <v>118.4600002288818</v>
       </c>
       <c r="V10" t="n">
-        <v>2070.583333333333</v>
+        <v>84.13166656494141</v>
       </c>
       <c r="W10" t="n">
-        <v>30.70067772875427</v>
+        <v>8.835867388474554</v>
       </c>
       <c r="X10" t="n">
-        <v>45.47348969687297</v>
+        <v>11.19014533062835</v>
       </c>
       <c r="Y10" t="n">
-        <v>-14.7728119681187</v>
+        <v>-2.354277942153798</v>
       </c>
       <c r="Z10" t="n">
-        <v>-16.6073198054698</v>
+        <v>-0.6983303021822458</v>
       </c>
       <c r="AA10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.015625</v>
+        <v>0.3005181347150259</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.826086956521739</v>
+        <v>1.102177527573967</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.1359297491792752</v>
+        <v>0.2077216236980282</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.4543999611876792</v>
+        <v>0.6750678866772444</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.5903297103669545</v>
+        <v>-0.4673462629792162</v>
       </c>
       <c r="AG10" t="n">
-        <v>35.29411764705883</v>
+        <v>84.31372549019608</v>
       </c>
       <c r="AH10" t="n">
-        <v>66.66666666666666</v>
+        <v>82.35294117647058</v>
       </c>
       <c r="AI10" t="b">
         <v>1</v>
       </c>
       <c r="AJ10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK10" t="b">
         <v>0</v>
@@ -1862,16 +1860,16 @@
         <v>0</v>
       </c>
       <c r="AM10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>2686.32</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>2352.89</v>
+        <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1882,21 +1880,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>66.13725490196079</v>
+        <v>64.07843137254902</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1909,14 +1907,14 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1200000</v>
+        <v>12466000</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="K11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -1925,65 +1923,65 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1200000</v>
+        <v>12466000</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>1210</v>
+        <v>978</v>
       </c>
       <c r="Q11" t="n">
-        <v>1210</v>
+        <v>978</v>
       </c>
       <c r="R11" t="n">
-        <v>1616128</v>
+        <v>5544998</v>
       </c>
       <c r="S11" t="n">
-        <v>1169</v>
+        <v>1011.6</v>
       </c>
       <c r="T11" t="n">
-        <v>1108.65</v>
+        <v>935.9</v>
       </c>
       <c r="U11" t="n">
-        <v>1098</v>
+        <v>931.8</v>
       </c>
       <c r="V11" t="n">
-        <v>1000.466666666667</v>
+        <v>732.275</v>
       </c>
       <c r="W11" t="n">
-        <v>37.71382370434571</v>
+        <v>38.02870957503342</v>
       </c>
       <c r="X11" t="n">
-        <v>41.89864841096782</v>
+        <v>49.34160696485605</v>
       </c>
       <c r="Y11" t="n">
-        <v>-4.184824706622102</v>
+        <v>-11.31289738982263</v>
       </c>
       <c r="Z11" t="n">
-        <v>-6.941223400875387</v>
+        <v>-6.293339870886868</v>
       </c>
       <c r="AA11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.2136409227683049</v>
+        <v>0.09151785714285721</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1308411214953271</v>
+        <v>1.51413881748072</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.09333617358902968</v>
+        <v>-0.001278653874140501</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.2408458738387327</v>
+        <v>1.087029176583997</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.3341820474277624</v>
+        <v>-1.088307830458138</v>
       </c>
       <c r="AG11" t="n">
-        <v>80.3921568627451</v>
+        <v>60.78431372549019</v>
       </c>
       <c r="AH11" t="n">
-        <v>11.76470588235294</v>
+        <v>90.19607843137256</v>
       </c>
       <c r="AI11" t="b">
         <v>1</v>
@@ -1998,13 +1996,13 @@
         <v>0</v>
       </c>
       <c r="AM11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="b">
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>1258.4</v>
+        <v>1107.1</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -2020,21 +2018,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>65.15686274509804</v>
+        <v>62.90196078431373</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2047,14 +2045,14 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2167000</v>
+        <v>17948000</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="K12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -2063,65 +2061,65 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2167000</v>
+        <v>17948000</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>1415</v>
+        <v>600</v>
       </c>
       <c r="Q12" t="n">
-        <v>1415</v>
+        <v>600</v>
       </c>
       <c r="R12" t="n">
-        <v>684510</v>
+        <v>7205584</v>
       </c>
       <c r="S12" t="n">
-        <v>1402</v>
+        <v>604</v>
       </c>
       <c r="T12" t="n">
-        <v>1409.25</v>
+        <v>564.85</v>
       </c>
       <c r="U12" t="n">
-        <v>1403</v>
+        <v>561.85</v>
       </c>
       <c r="V12" t="n">
-        <v>1126.4</v>
+        <v>460.65</v>
       </c>
       <c r="W12" t="n">
-        <v>26.36917692873112</v>
+        <v>23.03162032440741</v>
       </c>
       <c r="X12" t="n">
-        <v>33.18460562757933</v>
+        <v>25.23078729493248</v>
       </c>
       <c r="Y12" t="n">
-        <v>-6.815428698848208</v>
+        <v>-2.199166970525066</v>
       </c>
       <c r="Z12" t="n">
-        <v>-7.687376230837643</v>
+        <v>-0.0004004860842634628</v>
       </c>
       <c r="AA12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0968992248062015</v>
+        <v>0.1111111111111112</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.624569460390356</v>
+        <v>0.875</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0.02340552437307375</v>
+        <v>0.01831460009411345</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.2528824650562962</v>
+        <v>0.4478903591032775</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.2762879894293699</v>
+        <v>-0.429575759009164</v>
       </c>
       <c r="AG12" t="n">
-        <v>58.82352941176471</v>
+        <v>62.74509803921568</v>
       </c>
       <c r="AH12" t="n">
-        <v>47.05882352941176</v>
+        <v>68.62745098039215</v>
       </c>
       <c r="AI12" t="b">
         <v>1</v>
@@ -2136,13 +2134,13 @@
         <v>0</v>
       </c>
       <c r="AM12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="b">
         <v>1</v>
       </c>
       <c r="AO12" t="n">
-        <v>1494.24</v>
+        <v>625.2</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
@@ -2158,21 +2156,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>57.90196078431372</v>
+        <v>60.74509803921569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2185,11 +2183,11 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1034000</v>
+        <v>5775000</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -2201,65 +2199,65 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1034000</v>
+        <v>5775000</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>1090</v>
+        <v>257.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>1090</v>
+        <v>257.5</v>
       </c>
       <c r="R13" t="n">
-        <v>499070</v>
+        <v>23258689</v>
       </c>
       <c r="S13" t="n">
-        <v>1074</v>
+        <v>280.9</v>
       </c>
       <c r="T13" t="n">
-        <v>1081.45</v>
+        <v>234.1</v>
       </c>
       <c r="U13" t="n">
-        <v>1080.7</v>
+        <v>230.85</v>
       </c>
       <c r="V13" t="n">
-        <v>1034.265107218424</v>
+        <v>147.7183334350586</v>
       </c>
       <c r="W13" t="n">
-        <v>-3.514150064587739</v>
+        <v>21.92411684929559</v>
       </c>
       <c r="X13" t="n">
-        <v>1.921801207613963</v>
+        <v>24.50316473606305</v>
       </c>
       <c r="Y13" t="n">
-        <v>-5.435951272201701</v>
+        <v>-2.579047886767462</v>
       </c>
       <c r="Z13" t="n">
-        <v>-6.745457503645538</v>
+        <v>0.9570741363087407</v>
       </c>
       <c r="AA13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.01395348837209309</v>
+        <v>0.3376623376623376</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.5655825988557526</v>
+        <v>4.019493252038391</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.1063512608071822</v>
+        <v>0.2448658266453398</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.1938956035216928</v>
+        <v>3.592383611141668</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.3002468643288749</v>
+        <v>-3.347517784496328</v>
       </c>
       <c r="AG13" t="n">
-        <v>43.13725490196079</v>
+        <v>90.19607843137256</v>
       </c>
       <c r="AH13" t="n">
-        <v>45.09803921568628</v>
+        <v>100</v>
       </c>
       <c r="AI13" t="b">
         <v>1</v>
@@ -2274,13 +2272,13 @@
         <v>0</v>
       </c>
       <c r="AM13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="b">
         <v>1</v>
       </c>
       <c r="AO13" t="n">
-        <v>1153.22</v>
+        <v>286.86</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
@@ -2296,21 +2294,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>47.50980392156862</v>
+        <v>60.54901960784314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2323,14 +2321,14 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1000</v>
+        <v>7307000</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="K14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="b">
         <v>1</v>
@@ -2339,89 +2337,93 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1000</v>
+        <v>7307000</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>236</v>
+        <v>300</v>
       </c>
       <c r="Q14" t="n">
-        <v>236</v>
+        <v>300</v>
       </c>
       <c r="R14" t="n">
-        <v>3582405</v>
+        <v>43692807</v>
       </c>
       <c r="S14" t="n">
-        <v>229.3</v>
+        <v>298.6</v>
       </c>
       <c r="T14" t="n">
-        <v>226.05</v>
+        <v>263.35</v>
       </c>
       <c r="U14" t="n">
-        <v>226.675</v>
+        <v>261.025</v>
       </c>
       <c r="V14" t="n">
-        <v>193.6</v>
+        <v>228.5333333333333</v>
       </c>
       <c r="W14" t="n">
-        <v>3.357211355984617</v>
+        <v>16.18942370819047</v>
       </c>
       <c r="X14" t="n">
-        <v>4.04060240558333</v>
+        <v>11.91500887108731</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.683391049598713</v>
+        <v>4.274414837103162</v>
       </c>
       <c r="Z14" t="n">
-        <v>-1.608171744958133</v>
+        <v>5.400278270071549</v>
       </c>
       <c r="AA14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.05030181086519114</v>
+        <v>0.1834319526627219</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.7744360902255638</v>
+        <v>0.4251781472684086</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.1706065600444664</v>
+        <v>0.09063544164572424</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.402749094891504</v>
+        <v>-0.001931493628313907</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.5733556549359704</v>
+        <v>0.09256693527403814</v>
       </c>
       <c r="AG14" t="n">
-        <v>23.52941176470588</v>
+        <v>74.50980392156863</v>
       </c>
       <c r="AH14" t="n">
-        <v>64.70588235294117</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="AI14" t="b">
         <v>1</v>
       </c>
       <c r="AJ14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>244.02</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>213.53</v>
+        <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -2432,21 +2434,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>41.13725490196079</v>
+        <v>58.19607843137255</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2459,14 +2461,14 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3645000</v>
+        <v>6572000</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="K15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="b">
         <v>1</v>
@@ -2475,71 +2477,71 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3645000</v>
+        <v>6572000</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>328.5</v>
+        <v>2415</v>
       </c>
       <c r="Q15" t="n">
-        <v>328.5</v>
+        <v>2415</v>
       </c>
       <c r="R15" t="n">
-        <v>12479289</v>
+        <v>3111476</v>
       </c>
       <c r="S15" t="n">
-        <v>320.8</v>
+        <v>2419</v>
       </c>
       <c r="T15" t="n">
-        <v>307.525</v>
+        <v>2232.75</v>
       </c>
       <c r="U15" t="n">
-        <v>308.05</v>
+        <v>2226</v>
       </c>
       <c r="V15" t="n">
-        <v>297.0333333333334</v>
+        <v>1888.666666666667</v>
       </c>
       <c r="W15" t="n">
-        <v>5.705444504697994</v>
+        <v>89.00412244632889</v>
       </c>
       <c r="X15" t="n">
-        <v>4.373897720998973</v>
+        <v>79.82929541965294</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.331546783699021</v>
+        <v>9.174827026675956</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.7909858073156304</v>
+        <v>16.49176594822497</v>
       </c>
       <c r="AA15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.03097345132743368</v>
+        <v>0.05921052631578938</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.2077205882352942</v>
+        <v>0.9795081967213115</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.1512782005067089</v>
+        <v>-0.03358598470120833</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.1639664070987656</v>
+        <v>0.552398555824589</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.01268820659205672</v>
+        <v>-0.5859845405257973</v>
       </c>
       <c r="AG15" t="n">
-        <v>31.37254901960784</v>
+        <v>54.90196078431373</v>
       </c>
       <c r="AH15" t="n">
-        <v>19.6078431372549</v>
+        <v>72.54901960784314</v>
       </c>
       <c r="AI15" t="b">
         <v>1</v>
       </c>
       <c r="AJ15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK15" t="b">
         <v>1</v>
@@ -2548,7 +2550,7 @@
         <v>1</v>
       </c>
       <c r="AM15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="b">
         <v>0</v>
@@ -2558,8 +2560,10 @@
           <t>Already &gt; 0</t>
         </is>
       </c>
-      <c r="AP15" t="n">
-        <v>288.92</v>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -2570,12 +2574,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2584,7 +2588,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>77.21568627450981</v>
+        <v>56.82352941176471</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2597,11 +2601,11 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>18313000</v>
+        <v>11635000</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
@@ -2613,65 +2617,65 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>18313000</v>
+        <v>11635000</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>788</v>
+        <v>102</v>
       </c>
       <c r="Q16" t="n">
-        <v>788</v>
+        <v>102</v>
       </c>
       <c r="R16" t="n">
-        <v>3046048</v>
+        <v>54886353</v>
       </c>
       <c r="S16" t="n">
-        <v>796.4</v>
+        <v>103.1800003051758</v>
       </c>
       <c r="T16" t="n">
-        <v>601.675</v>
+        <v>89.76500053405762</v>
       </c>
       <c r="U16" t="n">
-        <v>580.85</v>
+        <v>89.57000045776367</v>
       </c>
       <c r="V16" t="n">
-        <v>393.6166666666667</v>
+        <v>73.76500040690104</v>
       </c>
       <c r="W16" t="n">
-        <v>95.17723141514944</v>
+        <v>5.56006487770739</v>
       </c>
       <c r="X16" t="n">
-        <v>87.78034815696874</v>
+        <v>4.901968525670797</v>
       </c>
       <c r="Y16" t="n">
-        <v>7.396883258180694</v>
+        <v>0.6580963520365932</v>
       </c>
       <c r="Z16" t="n">
-        <v>15.75753401466386</v>
+        <v>0.8867067986986141</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.121130551816958</v>
+        <v>0.03975536785464606</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.17102615694165</v>
+        <v>0.7465752968311232</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.000825802637683</v>
+        <v>-0.05304114316235164</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.79933916160759</v>
+        <v>0.3194656559344007</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.7985133589699069</v>
+        <v>-0.3725067990967523</v>
       </c>
       <c r="AG16" t="n">
-        <v>100</v>
+        <v>49.01960784313725</v>
       </c>
       <c r="AH16" t="n">
-        <v>96.07843137254902</v>
+        <v>60.78431372549019</v>
       </c>
       <c r="AI16" t="b">
         <v>1</v>
@@ -2710,12 +2714,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2724,7 +2728,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>72.70588235294117</v>
+        <v>56.82352941176471</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2737,14 +2741,14 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>71690000</v>
+        <v>4263000</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="K17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="b">
         <v>1</v>
@@ -2753,65 +2757,65 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>71690000</v>
+        <v>4263000</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>130</v>
+        <v>4505</v>
       </c>
       <c r="Q17" t="n">
-        <v>130</v>
+        <v>4505</v>
       </c>
       <c r="R17" t="n">
-        <v>83104172</v>
+        <v>4658394</v>
       </c>
       <c r="S17" t="n">
-        <v>138.5</v>
+        <v>4488</v>
       </c>
       <c r="T17" t="n">
-        <v>120.1350002288818</v>
+        <v>3928.25</v>
       </c>
       <c r="U17" t="n">
-        <v>118.4600002288818</v>
+        <v>3874</v>
       </c>
       <c r="V17" t="n">
-        <v>84.2066665649414</v>
+        <v>2620.916666666667</v>
       </c>
       <c r="W17" t="n">
-        <v>9.335867388474554</v>
+        <v>338.4446936886106</v>
       </c>
       <c r="X17" t="n">
-        <v>11.29014533062835</v>
+        <v>348.2664287747666</v>
       </c>
       <c r="Y17" t="n">
-        <v>-1.954277942153798</v>
+        <v>-9.821735086155968</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.6983303021822458</v>
+        <v>9.93446014543548</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.3471502590673574</v>
+        <v>0.317251461988304</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.177554411032794</v>
+        <v>1.705705705705706</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.2268455098880822</v>
+        <v>0.2244549509713063</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.8058674156987344</v>
+        <v>1.278596064808983</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.5790219058106523</v>
+        <v>-1.054141113837677</v>
       </c>
       <c r="AG17" t="n">
         <v>88.23529411764706</v>
       </c>
       <c r="AH17" t="n">
-        <v>82.35294117647058</v>
+        <v>94.11764705882352</v>
       </c>
       <c r="AI17" t="b">
         <v>1</v>
@@ -2829,10 +2833,10 @@
         <v>0</v>
       </c>
       <c r="AN17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO17" t="n">
-        <v>152.1</v>
+        <v>4622.13</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -2848,12 +2852,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2862,7 +2866,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>64.66666666666667</v>
+        <v>52.90196078431373</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2875,11 +2879,11 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>12466000</v>
+        <v>11960000</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
@@ -2891,65 +2895,65 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>12466000</v>
+        <v>11960000</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>995</v>
+        <v>2395</v>
       </c>
       <c r="Q18" t="n">
-        <v>995</v>
+        <v>2395</v>
       </c>
       <c r="R18" t="n">
-        <v>3154181</v>
+        <v>9355826</v>
       </c>
       <c r="S18" t="n">
-        <v>1015</v>
+        <v>2382</v>
       </c>
       <c r="T18" t="n">
-        <v>936.75</v>
+        <v>2286.75</v>
       </c>
       <c r="U18" t="n">
-        <v>931.8</v>
+        <v>2282.5</v>
       </c>
       <c r="V18" t="n">
-        <v>732.5583333333333</v>
+        <v>2085.991326904297</v>
       </c>
       <c r="W18" t="n">
-        <v>39.91759846392222</v>
+        <v>48.82709458157888</v>
       </c>
       <c r="X18" t="n">
-        <v>49.71938474263381</v>
+        <v>39.33032905010923</v>
       </c>
       <c r="Y18" t="n">
-        <v>-9.801786278711589</v>
+        <v>9.496765531469649</v>
       </c>
       <c r="Z18" t="n">
-        <v>-6.293339870886868</v>
+        <v>11.63837193615473</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.1104910714285714</v>
+        <v>0.03679653679653683</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.557840616966581</v>
+        <v>0.327521601158377</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.009813677750703853</v>
+        <v>-0.05599997422046088</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.186153621632521</v>
+        <v>-0.09958803973834551</v>
       </c>
       <c r="AF18" t="n">
-        <v>-1.195967299383225</v>
+        <v>0.04358806551788463</v>
       </c>
       <c r="AG18" t="n">
-        <v>62.74509803921568</v>
+        <v>47.05882352941176</v>
       </c>
       <c r="AH18" t="n">
-        <v>90.19607843137256</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="AI18" t="b">
         <v>1</v>
@@ -2958,19 +2962,21 @@
         <v>1</v>
       </c>
       <c r="AK18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM18" t="b">
         <v>0</v>
       </c>
       <c r="AN18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1106.44</v>
+        <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -2986,12 +2992,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3000,7 +3006,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>63.49019607843137</v>
+        <v>51.72549019607843</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3013,14 +3019,14 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>17948000</v>
+        <v>4400000</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="K19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="b">
         <v>1</v>
@@ -3029,65 +3035,65 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>17948000</v>
+        <v>4400000</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>611</v>
+        <v>1650</v>
       </c>
       <c r="Q19" t="n">
-        <v>611</v>
+        <v>1650</v>
       </c>
       <c r="R19" t="n">
-        <v>3678899</v>
+        <v>1549232</v>
       </c>
       <c r="S19" t="n">
-        <v>606.2</v>
+        <v>1666</v>
       </c>
       <c r="T19" t="n">
-        <v>565.4</v>
+        <v>1481.5</v>
       </c>
       <c r="U19" t="n">
-        <v>561.85</v>
+        <v>1471.25</v>
       </c>
       <c r="V19" t="n">
-        <v>460.8333333333333</v>
+        <v>1013.890655517578</v>
       </c>
       <c r="W19" t="n">
-        <v>24.2538425466297</v>
+        <v>103.9800584536943</v>
       </c>
       <c r="X19" t="n">
-        <v>25.47523173937694</v>
+        <v>106.143962024122</v>
       </c>
       <c r="Y19" t="n">
-        <v>-1.221389192747239</v>
+        <v>-2.163903570427721</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.0004004860842634628</v>
+        <v>4.397011361843539</v>
       </c>
       <c r="AA19" t="b">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.1314814814814815</v>
+        <v>0.1418685121107266</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.909375</v>
+        <v>2.663430705773743</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.01117673230220628</v>
+        <v>0.04907200109372889</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.5376880046659402</v>
+        <v>2.23632106487702</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.526511272363734</v>
+        <v>-2.187249063783291</v>
       </c>
       <c r="AG19" t="n">
-        <v>64.70588235294117</v>
+        <v>68.62745098039215</v>
       </c>
       <c r="AH19" t="n">
-        <v>68.62745098039215</v>
+        <v>98.0392156862745</v>
       </c>
       <c r="AI19" t="b">
         <v>1</v>
@@ -3108,7 +3114,7 @@
         <v>1</v>
       </c>
       <c r="AO19" t="n">
-        <v>625.66</v>
+        <v>1676.4</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -3124,12 +3130,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3138,7 +3144,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>61.92156862745098</v>
+        <v>50.15686274509805</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3151,11 +3157,11 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5775000</v>
+        <v>980000</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -3167,65 +3173,65 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>5775000</v>
+        <v>980000</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>272.5</v>
+        <v>612</v>
       </c>
       <c r="Q20" t="n">
-        <v>272.5</v>
+        <v>612</v>
       </c>
       <c r="R20" t="n">
-        <v>9655624</v>
+        <v>8835813</v>
       </c>
       <c r="S20" t="n">
-        <v>283.9</v>
+        <v>626</v>
       </c>
       <c r="T20" t="n">
-        <v>234.85</v>
+        <v>516.2</v>
       </c>
       <c r="U20" t="n">
-        <v>230.85</v>
+        <v>509.05</v>
       </c>
       <c r="V20" t="n">
-        <v>147.9683334350586</v>
+        <v>374.6666666666667</v>
       </c>
       <c r="W20" t="n">
-        <v>23.59078351596224</v>
+        <v>49.14997683959359</v>
       </c>
       <c r="X20" t="n">
-        <v>24.83649806939638</v>
+        <v>44.70190496681484</v>
       </c>
       <c r="Y20" t="n">
-        <v>-1.245714553434137</v>
+        <v>4.448071872778755</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.9570741363087407</v>
+        <v>8.739597002919723</v>
       </c>
       <c r="AA20" t="b">
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.4155844155844155</v>
+        <v>0.3049040511727079</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.311890917205676</v>
+        <v>1.632258064516129</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.2952796664051403</v>
+        <v>0.2121075401557102</v>
       </c>
       <c r="AE20" t="n">
-        <v>3.940203921871616</v>
+        <v>1.205148423619407</v>
       </c>
       <c r="AF20" t="n">
-        <v>-3.644924255466476</v>
+        <v>-0.9930408834636963</v>
       </c>
       <c r="AG20" t="n">
-        <v>94.11764705882352</v>
+        <v>86.27450980392157</v>
       </c>
       <c r="AH20" t="n">
-        <v>100</v>
+        <v>92.15686274509804</v>
       </c>
       <c r="AI20" t="b">
         <v>1</v>
@@ -3234,19 +3240,21 @@
         <v>1</v>
       </c>
       <c r="AK20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM20" t="b">
         <v>0</v>
       </c>
       <c r="AN20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>286.67</v>
+        <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
@@ -3262,12 +3270,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3276,7 +3284,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>61.52941176470588</v>
+        <v>50.15686274509804</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3289,14 +3297,14 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>7307000</v>
+        <v>3734000</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="K21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="b">
         <v>1</v>
@@ -3305,89 +3313,85 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>7307000</v>
+        <v>3734000</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>304</v>
+        <v>211.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>304</v>
+        <v>211.5</v>
       </c>
       <c r="R21" t="n">
-        <v>20679477</v>
+        <v>2954710</v>
       </c>
       <c r="S21" t="n">
-        <v>299.4</v>
+        <v>215</v>
       </c>
       <c r="T21" t="n">
-        <v>263.55</v>
+        <v>219.85</v>
       </c>
       <c r="U21" t="n">
-        <v>261.025</v>
+        <v>218.425</v>
       </c>
       <c r="V21" t="n">
-        <v>228.6</v>
+        <v>155.4266665140788</v>
       </c>
       <c r="W21" t="n">
-        <v>16.63386815263493</v>
+        <v>3.612432396374942</v>
       </c>
       <c r="X21" t="n">
-        <v>12.0038977599762</v>
+        <v>9.821048146665394</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.629970392658729</v>
+        <v>-6.208615750290452</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.400278270071549</v>
+        <v>-6.302955817868215</v>
       </c>
       <c r="AA21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.1992110453648914</v>
+        <v>0.1557377049180328</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.4441805225653206</v>
+        <v>1.226315789473684</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.07890629618561618</v>
+        <v>0.06294119390103514</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.07249352723126079</v>
+        <v>0.7992061485769617</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.006412768954355386</v>
+        <v>-0.7362649546759266</v>
       </c>
       <c r="AG21" t="n">
-        <v>78.43137254901961</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="AH21" t="n">
-        <v>31.37254901960784</v>
+        <v>88.23529411764706</v>
       </c>
       <c r="AI21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="b">
         <v>1</v>
       </c>
       <c r="AK21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN21" t="b">
         <v>0</v>
       </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
+      <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -3402,12 +3406,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3416,7 +3420,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>57.6078431372549</v>
+        <v>49.56862745098039</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3429,11 +3433,11 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>6572000</v>
+        <v>10828000</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K22" t="b">
         <v>1</v>
@@ -3445,93 +3449,89 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>6572000</v>
+        <v>10828000</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>2450</v>
+        <v>875</v>
       </c>
       <c r="Q22" t="n">
-        <v>2450</v>
+        <v>875</v>
       </c>
       <c r="R22" t="n">
-        <v>1513036</v>
+        <v>4292146</v>
       </c>
       <c r="S22" t="n">
-        <v>2426</v>
+        <v>878.8</v>
       </c>
       <c r="T22" t="n">
-        <v>2234.5</v>
+        <v>867.7</v>
       </c>
       <c r="U22" t="n">
-        <v>2226</v>
+        <v>871.3</v>
       </c>
       <c r="V22" t="n">
-        <v>1889.25</v>
+        <v>744.1</v>
       </c>
       <c r="W22" t="n">
-        <v>92.89301133521758</v>
+        <v>6.530431260714067</v>
       </c>
       <c r="X22" t="n">
-        <v>80.60707319743068</v>
+        <v>8.785874470547117</v>
       </c>
       <c r="Y22" t="n">
-        <v>12.2859381377869</v>
+        <v>-2.25544320983305</v>
       </c>
       <c r="Z22" t="n">
-        <v>16.49176594822497</v>
+        <v>-1.186083704858063</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.07456140350877183</v>
+        <v>-0.07602956705385433</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.008196721311475</v>
+        <v>1.06855791962175</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.04574334567050342</v>
+        <v>-0.168826078070852</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.6365097259774155</v>
+        <v>0.6414482787250271</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0.6822530716479189</v>
+        <v>-0.8102743567958791</v>
       </c>
       <c r="AG22" t="n">
-        <v>52.94117647058824</v>
+        <v>19.6078431372549</v>
       </c>
       <c r="AH22" t="n">
-        <v>72.54901960784314</v>
+        <v>80.3921568627451</v>
       </c>
       <c r="AI22" t="b">
         <v>1</v>
       </c>
       <c r="AJ22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="b">
         <v>0</v>
       </c>
       <c r="AN22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>901.25</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>846.3200000000001</v>
       </c>
     </row>
     <row r="23">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>56.23529411764706</v>
+        <v>48.19607843137255</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3569,11 +3569,11 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4263000</v>
+        <v>5441000</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
@@ -3585,65 +3585,65 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4263000</v>
+        <v>5441000</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>4570</v>
+        <v>399</v>
       </c>
       <c r="Q23" t="n">
-        <v>4570</v>
+        <v>399</v>
       </c>
       <c r="R23" t="n">
-        <v>3131749</v>
+        <v>25985308</v>
       </c>
       <c r="S23" t="n">
-        <v>4501</v>
+        <v>385.6</v>
       </c>
       <c r="T23" t="n">
-        <v>3931.5</v>
+        <v>334.525</v>
       </c>
       <c r="U23" t="n">
-        <v>3874</v>
+        <v>331.775</v>
       </c>
       <c r="V23" t="n">
-        <v>2622</v>
+        <v>315.3333333333333</v>
       </c>
       <c r="W23" t="n">
-        <v>345.6669159108328</v>
+        <v>21.76888490491933</v>
       </c>
       <c r="X23" t="n">
-        <v>349.7108732192111</v>
+        <v>8.987075980703729</v>
       </c>
       <c r="Y23" t="n">
-        <v>-4.043957308378253</v>
+        <v>12.7818089242156</v>
       </c>
       <c r="Z23" t="n">
-        <v>9.93446014543548</v>
+        <v>14.0184932770315</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.3362573099415205</v>
+        <v>0.1598837209302326</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.744744744744745</v>
+        <v>0.4148936170212767</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.2159525607622452</v>
+        <v>0.06708720991323491</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.373057749410685</v>
+        <v>-0.01221602387544585</v>
       </c>
       <c r="AF23" t="n">
-        <v>-1.15710518864844</v>
+        <v>0.07930323378868076</v>
       </c>
       <c r="AG23" t="n">
-        <v>86.27450980392157</v>
+        <v>72.54901960784314</v>
       </c>
       <c r="AH23" t="n">
-        <v>94.11764705882352</v>
+        <v>31.37254901960784</v>
       </c>
       <c r="AI23" t="b">
         <v>1</v>
@@ -3652,19 +3652,21 @@
         <v>1</v>
       </c>
       <c r="AK23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM23" t="b">
         <v>0</v>
       </c>
       <c r="AN23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>4615.7</v>
+        <v>0</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
@@ -3680,12 +3682,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3694,7 +3696,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53.88235294117648</v>
+        <v>48</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3707,14 +3709,14 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>11635000</v>
+        <v>5191000</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="b">
         <v>1</v>
@@ -3723,65 +3725,65 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>11635000</v>
+        <v>5191000</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>99.40000152587891</v>
+        <v>2710</v>
       </c>
       <c r="Q24" t="n">
-        <v>99.40000152587891</v>
+        <v>2710</v>
       </c>
       <c r="R24" t="n">
-        <v>12594631</v>
+        <v>2296862</v>
       </c>
       <c r="S24" t="n">
-        <v>102.6600006103516</v>
+        <v>2743</v>
       </c>
       <c r="T24" t="n">
-        <v>89.63500061035157</v>
+        <v>2579.5</v>
       </c>
       <c r="U24" t="n">
-        <v>89.57000045776367</v>
+        <v>2564.75</v>
       </c>
       <c r="V24" t="n">
-        <v>73.72166709899902</v>
+        <v>2381.416666666667</v>
       </c>
       <c r="W24" t="n">
-        <v>5.271176158360589</v>
+        <v>61.39479007515229</v>
       </c>
       <c r="X24" t="n">
-        <v>4.844190781801437</v>
+        <v>40.54290370469145</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.426985376559152</v>
+        <v>20.85188637046083</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.8867067986986141</v>
+        <v>32.43220069924789</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.01325181520875107</v>
+        <v>0.1221532091097308</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.7020547761772162</v>
+        <v>0.6276276276276276</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0.1070529339705242</v>
+        <v>0.02935669809273311</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.3303677808431564</v>
+        <v>0.200517986730905</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0.4374207148136806</v>
+        <v>-0.1711612886381719</v>
       </c>
       <c r="AG24" t="n">
-        <v>41.17647058823529</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="AH24" t="n">
-        <v>54.90196078431373</v>
+        <v>50.98039215686274</v>
       </c>
       <c r="AI24" t="b">
         <v>1</v>
@@ -3820,12 +3822,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3834,7 +3836,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53.49019607843137</v>
+        <v>47.41176470588236</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3847,14 +3849,14 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>11960000</v>
+        <v>686000</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="K25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="b">
         <v>1</v>
@@ -3863,65 +3865,65 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>11960000</v>
+        <v>686000</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>2400</v>
+        <v>246</v>
       </c>
       <c r="Q25" t="n">
-        <v>2400</v>
+        <v>246</v>
       </c>
       <c r="R25" t="n">
-        <v>6083298</v>
+        <v>507330</v>
       </c>
       <c r="S25" t="n">
-        <v>2383</v>
+        <v>248</v>
       </c>
       <c r="T25" t="n">
-        <v>2287</v>
+        <v>216.075</v>
       </c>
       <c r="U25" t="n">
-        <v>2282.5</v>
+        <v>212.775</v>
       </c>
       <c r="V25" t="n">
-        <v>2086.07466023763</v>
+        <v>182.0833333333333</v>
       </c>
       <c r="W25" t="n">
-        <v>49.38265013713453</v>
+        <v>15.22626343595209</v>
       </c>
       <c r="X25" t="n">
-        <v>39.44144016122032</v>
+        <v>15.26636004337053</v>
       </c>
       <c r="Y25" t="n">
-        <v>9.941209975914212</v>
+        <v>-0.04009660741844101</v>
       </c>
       <c r="Z25" t="n">
-        <v>11.63837193615478</v>
+        <v>1.378953189258032</v>
       </c>
       <c r="AA25" t="b">
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.03896103896103886</v>
+        <v>0.3666666666666667</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.3302930450021313</v>
+        <v>0.7142857142857142</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.08134371021823639</v>
+        <v>0.273870155649669</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.0413939503319285</v>
+        <v>0.2871760733889916</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.03994975988630789</v>
+        <v>-0.01330591773932266</v>
       </c>
       <c r="AG25" t="n">
-        <v>49.01960784313725</v>
+        <v>92.15686274509804</v>
       </c>
       <c r="AH25" t="n">
-        <v>23.52941176470588</v>
+        <v>58.82352941176471</v>
       </c>
       <c r="AI25" t="b">
         <v>1</v>
@@ -3930,21 +3932,19 @@
         <v>1</v>
       </c>
       <c r="AK25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="b">
         <v>0</v>
       </c>
       <c r="AN25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>246.49</v>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
@@ -3960,12 +3960,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>52.31372549019608</v>
+        <v>46.82352941176471</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3987,14 +3987,14 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>4400000</v>
+        <v>7769000</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="K26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="b">
         <v>1</v>
@@ -4003,71 +4003,71 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4400000</v>
+        <v>7769000</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>1670</v>
+        <v>1335</v>
       </c>
       <c r="Q26" t="n">
-        <v>1670</v>
+        <v>1335</v>
       </c>
       <c r="R26" t="n">
-        <v>774114</v>
+        <v>1645345</v>
       </c>
       <c r="S26" t="n">
-        <v>1670</v>
+        <v>1328</v>
       </c>
       <c r="T26" t="n">
-        <v>1482.5</v>
+        <v>1338.25</v>
       </c>
       <c r="U26" t="n">
-        <v>1471.25</v>
+        <v>1344</v>
       </c>
       <c r="V26" t="n">
-        <v>1014.223988850911</v>
+        <v>1180.333333333333</v>
       </c>
       <c r="W26" t="n">
-        <v>106.2022806759164</v>
+        <v>2.41751793207527</v>
       </c>
       <c r="X26" t="n">
-        <v>106.5884064685664</v>
+        <v>6.688876668809249</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.3861257926499775</v>
+        <v>-4.271358736733979</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.397011361843539</v>
+        <v>-4.612508583835297</v>
       </c>
       <c r="AA26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.1557093425605536</v>
+        <v>-0.07931034482758625</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.707835926449788</v>
+        <v>0.7542706964520367</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.03540459338127833</v>
+        <v>-0.172106855844584</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.336148931115728</v>
+        <v>0.3271610555553142</v>
       </c>
       <c r="AF26" t="n">
-        <v>-2.30074433773445</v>
+        <v>-0.4992679113998981</v>
       </c>
       <c r="AG26" t="n">
-        <v>70.58823529411765</v>
+        <v>17.64705882352941</v>
       </c>
       <c r="AH26" t="n">
-        <v>98.0392156862745</v>
+        <v>62.74509803921568</v>
       </c>
       <c r="AI26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="b">
         <v>0</v>
@@ -4076,18 +4076,16 @@
         <v>0</v>
       </c>
       <c r="AM26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN26" t="b">
         <v>1</v>
       </c>
       <c r="AO26" t="n">
-        <v>1676.68</v>
-      </c>
-      <c r="AP26" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>1383.06</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1333.42</v>
       </c>
     </row>
     <row r="27">
@@ -4098,12 +4096,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4112,7 +4110,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>49.56862745098039</v>
+        <v>45.84313725490196</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4125,11 +4123,11 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>980000</v>
+        <v>329000</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
@@ -4141,65 +4139,65 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>980000</v>
+        <v>329000</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>605</v>
+        <v>3785</v>
       </c>
       <c r="Q27" t="n">
-        <v>605</v>
+        <v>3785</v>
       </c>
       <c r="R27" t="n">
-        <v>4439002</v>
+        <v>1252412</v>
       </c>
       <c r="S27" t="n">
-        <v>624.6</v>
+        <v>3794</v>
       </c>
       <c r="T27" t="n">
-        <v>515.85</v>
+        <v>3380.25</v>
       </c>
       <c r="U27" t="n">
-        <v>509.05</v>
+        <v>3319.75</v>
       </c>
       <c r="V27" t="n">
-        <v>374.55</v>
+        <v>2735.043587239583</v>
       </c>
       <c r="W27" t="n">
-        <v>48.37219906181565</v>
+        <v>224.3114577068891</v>
       </c>
       <c r="X27" t="n">
-        <v>44.54634941125925</v>
+        <v>221.3142324465821</v>
       </c>
       <c r="Y27" t="n">
-        <v>3.8258496505564</v>
+        <v>2.997225260307033</v>
       </c>
       <c r="Z27" t="n">
-        <v>8.739597002919723</v>
+        <v>21.02710691230362</v>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.2899786780383795</v>
+        <v>0.4699029126213592</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.602150537634409</v>
+        <v>0.6925253971168674</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.1696739288591043</v>
+        <v>0.3771064016043615</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.230463542300349</v>
+        <v>0.2654157562201449</v>
       </c>
       <c r="AF27" t="n">
-        <v>-1.060789613441244</v>
+        <v>0.1116906453842166</v>
       </c>
       <c r="AG27" t="n">
-        <v>84.31372549019608</v>
+        <v>96.07843137254902</v>
       </c>
       <c r="AH27" t="n">
-        <v>92.15686274509804</v>
+        <v>52.94117647058824</v>
       </c>
       <c r="AI27" t="b">
         <v>1</v>
@@ -4238,12 +4236,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4252,7 +4250,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>49.37254901960785</v>
+        <v>45.64705882352941</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4265,11 +4263,11 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>3734000</v>
+        <v>1642000</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
@@ -4281,65 +4279,65 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3734000</v>
+        <v>1642000</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>210.5</v>
+        <v>747</v>
       </c>
       <c r="Q28" t="n">
-        <v>210.5</v>
+        <v>747</v>
       </c>
       <c r="R28" t="n">
-        <v>1496964</v>
+        <v>2937461</v>
       </c>
       <c r="S28" t="n">
-        <v>214.8</v>
+        <v>814.4</v>
       </c>
       <c r="T28" t="n">
-        <v>219.8</v>
+        <v>791.55</v>
       </c>
       <c r="U28" t="n">
-        <v>218.425</v>
+        <v>784.65</v>
       </c>
       <c r="V28" t="n">
-        <v>155.4099998474121</v>
+        <v>616.5649571736653</v>
       </c>
       <c r="W28" t="n">
-        <v>3.501321285263828</v>
+        <v>22.45758842496923</v>
       </c>
       <c r="X28" t="n">
-        <v>9.798825924443172</v>
+        <v>39.89374975460264</v>
       </c>
       <c r="Y28" t="n">
-        <v>-6.297504639179344</v>
+        <v>-17.43616132963341</v>
       </c>
       <c r="Z28" t="n">
-        <v>-6.302955817868215</v>
+        <v>-9.68869930629873</v>
       </c>
       <c r="AA28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.1502732240437159</v>
+        <v>0.2266009852216748</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.215789473684211</v>
+        <v>0.5282483782216345</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.02996847486444065</v>
+        <v>0.1338044742046771</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.8441024783501507</v>
+        <v>0.101138737324912</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.8141340034857101</v>
+        <v>0.03266573687976515</v>
       </c>
       <c r="AG28" t="n">
-        <v>68.62745098039215</v>
+        <v>82.35294117647058</v>
       </c>
       <c r="AH28" t="n">
-        <v>86.27450980392157</v>
+        <v>43.13725490196079</v>
       </c>
       <c r="AI28" t="b">
         <v>0</v>
@@ -4354,7 +4352,7 @@
         <v>0</v>
       </c>
       <c r="AM28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="b">
         <v>0</v>
@@ -4374,12 +4372,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4388,7 +4386,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>48.3921568627451</v>
+        <v>42.70588235294117</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4401,11 +4399,11 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>5441000</v>
+        <v>1000</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -4417,65 +4415,65 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>5441000</v>
+        <v>1000</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>407.5</v>
+        <v>881</v>
       </c>
       <c r="Q29" t="n">
-        <v>407.5</v>
+        <v>881</v>
       </c>
       <c r="R29" t="n">
-        <v>13440987</v>
+        <v>2650416</v>
       </c>
       <c r="S29" t="n">
-        <v>387.3</v>
+        <v>866</v>
       </c>
       <c r="T29" t="n">
-        <v>334.95</v>
+        <v>718.9</v>
       </c>
       <c r="U29" t="n">
-        <v>331.775</v>
+        <v>706.8</v>
       </c>
       <c r="V29" t="n">
-        <v>315.475</v>
+        <v>627.5666666666667</v>
       </c>
       <c r="W29" t="n">
-        <v>22.71332934936373</v>
+        <v>67.46716106186238</v>
       </c>
       <c r="X29" t="n">
-        <v>9.175964869592608</v>
+        <v>43.10667760160244</v>
       </c>
       <c r="Y29" t="n">
-        <v>13.53736447977112</v>
+        <v>24.36048346025994</v>
       </c>
       <c r="Z29" t="n">
-        <v>14.0184932770315</v>
+        <v>29.73688701388987</v>
       </c>
       <c r="AA29" t="b">
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.1845930232558139</v>
+        <v>0.3787167449139279</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.4450354609929077</v>
+        <v>0.7040618955512572</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.0642882740765387</v>
+        <v>0.2859202338969302</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.07334846565884789</v>
+        <v>0.2769522546545347</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.009060191582309196</v>
+        <v>0.008967979242395563</v>
       </c>
       <c r="AG29" t="n">
-        <v>72.54901960784314</v>
+        <v>94.11764705882352</v>
       </c>
       <c r="AH29" t="n">
-        <v>33.33333333333333</v>
+        <v>54.90196078431373</v>
       </c>
       <c r="AI29" t="b">
         <v>1</v>
@@ -4514,12 +4512,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4528,7 +4526,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>48</v>
+        <v>41.33333333333334</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4541,11 +4539,11 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>5191000</v>
+        <v>2437000</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -4557,65 +4555,65 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>5191000</v>
+        <v>2437000</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>2755</v>
+        <v>5430</v>
       </c>
       <c r="Q30" t="n">
-        <v>2755</v>
+        <v>5430</v>
       </c>
       <c r="R30" t="n">
-        <v>1023611</v>
+        <v>528147</v>
       </c>
       <c r="S30" t="n">
-        <v>2752</v>
+        <v>5493</v>
       </c>
       <c r="T30" t="n">
-        <v>2581.75</v>
+        <v>5330</v>
       </c>
       <c r="U30" t="n">
-        <v>2564.75</v>
+        <v>5302.5</v>
       </c>
       <c r="V30" t="n">
-        <v>2382.166666666667</v>
+        <v>4444.5</v>
       </c>
       <c r="W30" t="n">
-        <v>66.39479007515229</v>
+        <v>125.8931677857754</v>
       </c>
       <c r="X30" t="n">
-        <v>41.54290370469145</v>
+        <v>137.2574909638897</v>
       </c>
       <c r="Y30" t="n">
-        <v>24.85188637046083</v>
+        <v>-11.36432317811432</v>
       </c>
       <c r="Z30" t="n">
-        <v>32.43220069924789</v>
+        <v>-2.235203542517638</v>
       </c>
       <c r="AA30" t="b">
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.1407867494824016</v>
+        <v>0.1127049180327868</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.6546546546546546</v>
+        <v>0.3816793893129771</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.0204820003031263</v>
+        <v>0.01990840701578911</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.2829676593205948</v>
+        <v>-0.04543025158374547</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.2624856590174685</v>
+        <v>0.06533865859953458</v>
       </c>
       <c r="AG30" t="n">
-        <v>66.66666666666666</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="AH30" t="n">
-        <v>50.98039215686274</v>
+        <v>29.41176470588236</v>
       </c>
       <c r="AI30" t="b">
         <v>1</v>
@@ -4624,21 +4622,19 @@
         <v>1</v>
       </c>
       <c r="AK30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="b">
         <v>0</v>
       </c>
       <c r="AN30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>5560.32</v>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
@@ -4654,12 +4650,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4668,7 +4664,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>46.62745098039215</v>
+        <v>40.74509803921568</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4681,11 +4677,11 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>686000</v>
+        <v>6231000</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -4697,93 +4693,89 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>686000</v>
+        <v>6231000</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>248</v>
+        <v>2480</v>
       </c>
       <c r="Q31" t="n">
-        <v>248</v>
+        <v>2480</v>
       </c>
       <c r="R31" t="n">
-        <v>178019</v>
+        <v>805114</v>
       </c>
       <c r="S31" t="n">
-        <v>248.4</v>
+        <v>2486</v>
       </c>
       <c r="T31" t="n">
-        <v>216.175</v>
+        <v>2497</v>
       </c>
       <c r="U31" t="n">
-        <v>212.775</v>
+        <v>2501</v>
       </c>
       <c r="V31" t="n">
-        <v>182.1166666666667</v>
+        <v>2069.916666666667</v>
       </c>
       <c r="W31" t="n">
-        <v>15.44848565817435</v>
+        <v>26.25623328430947</v>
       </c>
       <c r="X31" t="n">
-        <v>15.31080448781498</v>
+        <v>44.58460080798401</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.1376811703593646</v>
+        <v>-18.32836752367454</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.378953189258032</v>
+        <v>-16.6073198054698</v>
       </c>
       <c r="AA31" t="b">
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.3777777777777778</v>
+        <v>-0.03125</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.7282229965156795</v>
+        <v>0.7971014492753623</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.2574730285985025</v>
+        <v>-0.1240465110169977</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.3565360011816197</v>
+        <v>0.3699918083786398</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.09906297258311714</v>
+        <v>-0.4940383193956375</v>
       </c>
       <c r="AG31" t="n">
-        <v>90.19607843137256</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="AH31" t="n">
-        <v>56.86274509803921</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="AI31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="b">
         <v>0</v>
       </c>
       <c r="AN31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP31" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>2688.32</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>2392.89</v>
       </c>
     </row>
     <row r="32">
@@ -4794,12 +4786,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4808,7 +4800,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>46.43137254901961</v>
+        <v>40.15686274509804</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4821,11 +4813,11 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>329000</v>
+        <v>2167000</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
@@ -4837,88 +4829,86 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>329000</v>
+        <v>2167000</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>3885</v>
+        <v>1390</v>
       </c>
       <c r="Q32" t="n">
-        <v>3885</v>
+        <v>1390</v>
       </c>
       <c r="R32" t="n">
-        <v>508213</v>
+        <v>1130833</v>
       </c>
       <c r="S32" t="n">
-        <v>3814</v>
+        <v>1397</v>
       </c>
       <c r="T32" t="n">
-        <v>3385.25</v>
+        <v>1408</v>
       </c>
       <c r="U32" t="n">
-        <v>3319.75</v>
+        <v>1403</v>
       </c>
       <c r="V32" t="n">
-        <v>2736.71025390625</v>
+        <v>1125.983333333333</v>
       </c>
       <c r="W32" t="n">
-        <v>235.4225688179999</v>
+        <v>23.59139915095352</v>
       </c>
       <c r="X32" t="n">
-        <v>223.5364546688042</v>
+        <v>32.62905007202382</v>
       </c>
       <c r="Y32" t="n">
-        <v>11.88611414919572</v>
+        <v>-9.037650921070295</v>
       </c>
       <c r="Z32" t="n">
-        <v>21.02710691230362</v>
+        <v>-7.687376230837643</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.5087378640776699</v>
+        <v>0.07751937984496116</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.7372420522586605</v>
+        <v>0.5958668197474168</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.3884331148983946</v>
+        <v>-0.01527713117203655</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.3655550569246007</v>
+        <v>0.1687571788506943</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.02287805797379394</v>
+        <v>-0.1840343100227309</v>
       </c>
       <c r="AG32" t="n">
-        <v>96.07843137254902</v>
+        <v>58.82352941176471</v>
       </c>
       <c r="AH32" t="n">
-        <v>58.82352941176471</v>
+        <v>47.05882352941176</v>
       </c>
       <c r="AI32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="b">
         <v>1</v>
       </c>
       <c r="AK32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="b">
         <v>0</v>
       </c>
       <c r="AN32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1492.86</v>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
@@ -4934,12 +4924,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4948,7 +4938,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>45.64705882352941</v>
+        <v>39.56862745098039</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4961,11 +4951,11 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1642000</v>
+        <v>4486000</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -4977,71 +4967,71 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1642000</v>
+        <v>4486000</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>762</v>
+        <v>4785</v>
       </c>
       <c r="Q33" t="n">
-        <v>762</v>
+        <v>4785</v>
       </c>
       <c r="R33" t="n">
-        <v>1572719</v>
+        <v>565532</v>
       </c>
       <c r="S33" t="n">
-        <v>817.4</v>
+        <v>4933</v>
       </c>
       <c r="T33" t="n">
-        <v>792.3</v>
+        <v>4897.75</v>
       </c>
       <c r="U33" t="n">
-        <v>784.65</v>
+        <v>4906.5</v>
       </c>
       <c r="V33" t="n">
-        <v>616.8149571736653</v>
+        <v>3932.916666666667</v>
       </c>
       <c r="W33" t="n">
-        <v>24.12425509163586</v>
+        <v>55.18755304886417</v>
       </c>
       <c r="X33" t="n">
-        <v>40.22708308793597</v>
+        <v>133.8110789380552</v>
       </c>
       <c r="Y33" t="n">
-        <v>-16.10282799630011</v>
+        <v>-78.62352588919106</v>
       </c>
       <c r="Z33" t="n">
-        <v>-9.68869930629873</v>
+        <v>-67.0610085410446</v>
       </c>
       <c r="AA33" t="b">
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.2512315270935961</v>
+        <v>-0.03528225806451613</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.5589360966598198</v>
+        <v>1.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.1309267779143208</v>
+        <v>-0.1280787690815138</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.18724910132576</v>
+        <v>0.7728903591032776</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.05632232341143917</v>
+        <v>-0.9009691281847915</v>
       </c>
       <c r="AG33" t="n">
-        <v>82.35294117647058</v>
+        <v>31.37254901960784</v>
       </c>
       <c r="AH33" t="n">
-        <v>43.13725490196079</v>
+        <v>84.31372549019608</v>
       </c>
       <c r="AI33" t="b">
         <v>0</v>
       </c>
       <c r="AJ33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="b">
         <v>0</v>
@@ -5055,11 +5045,11 @@
       <c r="AN33" t="b">
         <v>0</v>
       </c>
-      <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AO33" t="n">
+        <v>5675.01</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>4868.68</v>
       </c>
     </row>
     <row r="34">
@@ -5070,12 +5060,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5084,7 +5074,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>42.70588235294117</v>
+        <v>37.41176470588236</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5097,11 +5087,11 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1000</v>
+        <v>511000</v>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
@@ -5113,65 +5103,65 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1000</v>
+        <v>511000</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>904</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="Q34" t="n">
-        <v>904</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="R34" t="n">
-        <v>1198674</v>
+        <v>2539234</v>
       </c>
       <c r="S34" t="n">
-        <v>870.6</v>
+        <v>92.86000061035156</v>
       </c>
       <c r="T34" t="n">
-        <v>720.05</v>
+        <v>83.57499961853027</v>
       </c>
       <c r="U34" t="n">
-        <v>706.8</v>
+        <v>82.80999946594238</v>
       </c>
       <c r="V34" t="n">
-        <v>627.95</v>
+        <v>81.4733331044515</v>
       </c>
       <c r="W34" t="n">
-        <v>70.02271661741804</v>
+        <v>3.925890996932964</v>
       </c>
       <c r="X34" t="n">
-        <v>43.61778871271358</v>
+        <v>2.392494780655368</v>
       </c>
       <c r="Y34" t="n">
-        <v>26.40492790470446</v>
+        <v>1.533396216277596</v>
       </c>
       <c r="Z34" t="n">
-        <v>29.73688701388987</v>
+        <v>1.539528706158522</v>
       </c>
       <c r="AA34" t="b">
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.4147104851330203</v>
+        <v>0.1912500381469726</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.7485493230174081</v>
+        <v>0.08789959716621976</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.2944057359537451</v>
+        <v>0.0984535271299749</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.3768623276833483</v>
+        <v>-0.3392100437305028</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.08245659172960318</v>
+        <v>0.4376635708604777</v>
       </c>
       <c r="AG34" t="n">
-        <v>92.15686274509804</v>
+        <v>78.43137254901961</v>
       </c>
       <c r="AH34" t="n">
-        <v>60.78431372549019</v>
+        <v>7.84313725490196</v>
       </c>
       <c r="AI34" t="b">
         <v>1</v>
@@ -5210,12 +5200,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5224,7 +5214,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>40.54901960784314</v>
+        <v>32.90196078431373</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5237,11 +5227,11 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>4486000</v>
+        <v>1761000</v>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -5253,77 +5243,77 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4486000</v>
+        <v>1761000</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>4825</v>
+        <v>1985</v>
       </c>
       <c r="Q35" t="n">
-        <v>4825</v>
+        <v>1985</v>
       </c>
       <c r="R35" t="n">
-        <v>271214</v>
+        <v>678056</v>
       </c>
       <c r="S35" t="n">
-        <v>4941</v>
+        <v>2062</v>
       </c>
       <c r="T35" t="n">
-        <v>4899.75</v>
+        <v>1867.25</v>
       </c>
       <c r="U35" t="n">
-        <v>4906.5</v>
+        <v>1864</v>
       </c>
       <c r="V35" t="n">
-        <v>3933.583333333333</v>
+        <v>1885.5</v>
       </c>
       <c r="W35" t="n">
-        <v>59.63199749330852</v>
+        <v>55.763156836397</v>
       </c>
       <c r="X35" t="n">
-        <v>134.6999678269441</v>
+        <v>15.7715159380667</v>
       </c>
       <c r="Y35" t="n">
-        <v>-75.0679703336356</v>
+        <v>39.9916408983303</v>
       </c>
       <c r="Z35" t="n">
-        <v>-67.0610085410446</v>
+        <v>56.04366129912638</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0.02721774193548387</v>
+        <v>0.03385416666666674</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.218390804597701</v>
+        <v>0.1921921921921923</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.1475224911147591</v>
+        <v>-0.05894234435033097</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.8467038092636414</v>
+        <v>-0.2349174487045302</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.9942263003784005</v>
+        <v>0.1759751043541993</v>
       </c>
       <c r="AG35" t="n">
-        <v>33.33333333333333</v>
+        <v>45.09803921568628</v>
       </c>
       <c r="AH35" t="n">
-        <v>88.23529411764706</v>
+        <v>19.6078431372549</v>
       </c>
       <c r="AI35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM35" t="b">
         <v>0</v>
@@ -5331,11 +5321,15 @@
       <c r="AN35" t="b">
         <v>0</v>
       </c>
-      <c r="AO35" t="n">
-        <v>5674.2</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>4828.68</v>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -5346,12 +5340,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5360,7 +5354,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>39.96078431372549</v>
+        <v>32.70588235294117</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5373,11 +5367,11 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2437000</v>
+        <v>3988000</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
@@ -5389,91 +5383,91 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2437000</v>
+        <v>3988000</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>5400</v>
+        <v>98.80000305175781</v>
       </c>
       <c r="Q36" t="n">
-        <v>5400</v>
+        <v>98.80000305175781</v>
       </c>
       <c r="R36" t="n">
-        <v>285805</v>
+        <v>4175488</v>
       </c>
       <c r="S36" t="n">
-        <v>5487</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T36" t="n">
-        <v>5328.5</v>
+        <v>95.42000045776368</v>
       </c>
       <c r="U36" t="n">
-        <v>5302.5</v>
+        <v>95.48000030517578</v>
       </c>
       <c r="V36" t="n">
-        <v>4444</v>
+        <v>97.9416670481364</v>
       </c>
       <c r="W36" t="n">
-        <v>122.5598344524424</v>
+        <v>0.5001845896800461</v>
       </c>
       <c r="X36" t="n">
-        <v>136.5908242972231</v>
+        <v>-0.2211341336594903</v>
       </c>
       <c r="Y36" t="n">
-        <v>-14.03098984478075</v>
+        <v>0.7213187233395364</v>
       </c>
       <c r="Z36" t="n">
-        <v>-2.235203542517638</v>
+        <v>0.792692952551374</v>
       </c>
       <c r="AA36" t="b">
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.1065573770491803</v>
+        <v>-0.01199996948242188</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.3740458015267176</v>
+        <v>0.09050777831943302</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.01374737213009491</v>
+        <v>-0.1047964804994196</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.002358806192657825</v>
+        <v>-0.3366018625772895</v>
       </c>
       <c r="AF36" t="n">
-        <v>-0.01610617832275274</v>
+        <v>0.2318053820778699</v>
       </c>
       <c r="AG36" t="n">
-        <v>60.78431372549019</v>
+        <v>37.25490196078432</v>
       </c>
       <c r="AH36" t="n">
-        <v>27.45098039215686</v>
+        <v>9.803921568627452</v>
       </c>
       <c r="AI36" t="b">
         <v>1</v>
       </c>
       <c r="AJ36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM36" t="b">
         <v>0</v>
       </c>
       <c r="AN36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>5562</v>
-      </c>
-      <c r="AP36" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP36" t="n">
+        <v>91.94</v>
       </c>
     </row>
     <row r="37">
@@ -5484,12 +5478,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5498,7 +5492,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>34.86274509803921</v>
+        <v>32.70588235294117</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5511,11 +5505,11 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1761000</v>
+        <v>1334000</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K37" t="b">
         <v>0</v>
@@ -5527,93 +5521,89 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1761000</v>
+        <v>1334000</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>2030</v>
+        <v>1090</v>
       </c>
       <c r="Q37" t="n">
-        <v>2030</v>
+        <v>1090</v>
       </c>
       <c r="R37" t="n">
-        <v>263199</v>
+        <v>1182820</v>
       </c>
       <c r="S37" t="n">
-        <v>2071</v>
+        <v>1071</v>
       </c>
       <c r="T37" t="n">
-        <v>1869.5</v>
+        <v>1127.25</v>
       </c>
       <c r="U37" t="n">
-        <v>1864</v>
+        <v>1129.25</v>
       </c>
       <c r="V37" t="n">
-        <v>1886.25</v>
+        <v>1031.516666666667</v>
       </c>
       <c r="W37" t="n">
-        <v>60.763156836397</v>
+        <v>-20.51122897995947</v>
       </c>
       <c r="X37" t="n">
-        <v>16.7715159380667</v>
+        <v>-9.081809553575255</v>
       </c>
       <c r="Y37" t="n">
-        <v>43.9916408983303</v>
+        <v>-11.42941942638421</v>
       </c>
       <c r="Z37" t="n">
-        <v>56.04366129912638</v>
+        <v>-15.76878958699825</v>
       </c>
       <c r="AA37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.05729166666666674</v>
+        <v>-0.03539823008849563</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.2192192192192193</v>
+        <v>1.052730696798494</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.06301308251260851</v>
+        <v>-0.1281947411054933</v>
       </c>
       <c r="AE37" t="n">
-        <v>-0.1524677761148405</v>
+        <v>0.625621055901771</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.08945469360223202</v>
+        <v>-0.7538157970072643</v>
       </c>
       <c r="AG37" t="n">
-        <v>50.98039215686274</v>
+        <v>29.41176470588236</v>
       </c>
       <c r="AH37" t="n">
-        <v>21.56862745098039</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="AI37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP37" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1218.62</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1109.21</v>
       </c>
     </row>
     <row r="38">
@@ -5624,12 +5614,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5638,7 +5628,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>31.72549019607844</v>
+        <v>31.72549019607843</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5651,11 +5641,11 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>329000</v>
+        <v>422000</v>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
@@ -5667,65 +5657,65 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>329000</v>
+        <v>422000</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>265.5</v>
+        <v>18305</v>
       </c>
       <c r="Q38" t="n">
-        <v>265.5</v>
+        <v>18305</v>
       </c>
       <c r="R38" t="n">
-        <v>8797129</v>
+        <v>39027</v>
       </c>
       <c r="S38" t="n">
-        <v>272.6750366210937</v>
+        <v>18366</v>
       </c>
       <c r="T38" t="n">
-        <v>261.4058555603027</v>
+        <v>17516.25</v>
       </c>
       <c r="U38" t="n">
-        <v>260.481990814209</v>
+        <v>17495.5</v>
       </c>
       <c r="V38" t="n">
-        <v>248.2858322143555</v>
+        <v>14698.08333333333</v>
       </c>
       <c r="W38" t="n">
-        <v>4.092125816529006</v>
+        <v>416.4886376153372</v>
       </c>
       <c r="X38" t="n">
-        <v>5.715582626232131</v>
+        <v>429.0192350787105</v>
       </c>
       <c r="Y38" t="n">
-        <v>-1.623456809703126</v>
+        <v>-12.53059746337328</v>
       </c>
       <c r="Z38" t="n">
-        <v>-0.8454073717983484</v>
+        <v>-4.541236302445384</v>
       </c>
       <c r="AA38" t="b">
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.07479998616334171</v>
+        <v>0.02319731693683624</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.4653694018060288</v>
+        <v>0.9789189189189189</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.04550476301593354</v>
+        <v>-0.06959919408016146</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.09368240647196902</v>
+        <v>0.5518092780221964</v>
       </c>
       <c r="AF38" t="n">
-        <v>-0.1391871694879026</v>
+        <v>-0.6214084721023578</v>
       </c>
       <c r="AG38" t="n">
-        <v>54.90196078431373</v>
+        <v>41.17647058823529</v>
       </c>
       <c r="AH38" t="n">
-        <v>35.29411764705883</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="AI38" t="b">
         <v>1</v>
@@ -5746,7 +5736,7 @@
         <v>1</v>
       </c>
       <c r="AO38" t="n">
-        <v>284.08</v>
+        <v>18451.44</v>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
@@ -5762,12 +5752,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5776,7 +5766,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>31.33333333333333</v>
+        <v>31.13725490196079</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5789,11 +5779,11 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1334000</v>
+        <v>329000</v>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="K39" t="b">
         <v>0</v>
@@ -5805,71 +5795,71 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1334000</v>
+        <v>329000</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>1075</v>
+        <v>259</v>
       </c>
       <c r="Q39" t="n">
-        <v>1075</v>
+        <v>259</v>
       </c>
       <c r="R39" t="n">
-        <v>441616</v>
+        <v>21905116</v>
       </c>
       <c r="S39" t="n">
-        <v>1068</v>
+        <v>271.3750366210937</v>
       </c>
       <c r="T39" t="n">
-        <v>1126.5</v>
+        <v>261.0808555603027</v>
       </c>
       <c r="U39" t="n">
-        <v>1129.25</v>
+        <v>260.481990814209</v>
       </c>
       <c r="V39" t="n">
-        <v>1031.266666666667</v>
+        <v>248.1774988810221</v>
       </c>
       <c r="W39" t="n">
-        <v>-22.17789564662621</v>
+        <v>3.369903594306777</v>
       </c>
       <c r="X39" t="n">
-        <v>-9.415142886908605</v>
+        <v>5.571138181787686</v>
       </c>
       <c r="Y39" t="n">
-        <v>-12.76275275971761</v>
+        <v>-2.201234587480909</v>
       </c>
       <c r="Z39" t="n">
-        <v>-15.76878958699825</v>
+        <v>-0.8454073717983484</v>
       </c>
       <c r="AA39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>-0.04867256637168138</v>
+        <v>0.04848661550397559</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.024482109227872</v>
+        <v>0.4294940680518322</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.1689773155509566</v>
+        <v>-0.04430989551302211</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.6527951138938122</v>
+        <v>0.00238442715510967</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0.8217724294447688</v>
+        <v>-0.04669432266813178</v>
       </c>
       <c r="AG39" t="n">
-        <v>25.49019607843137</v>
+        <v>52.94117647058824</v>
       </c>
       <c r="AH39" t="n">
-        <v>74.50980392156863</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AI39" t="b">
         <v>0</v>
       </c>
       <c r="AJ39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK39" t="b">
         <v>0</v>
@@ -5878,16 +5868,18 @@
         <v>0</v>
       </c>
       <c r="AM39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="b">
         <v>1</v>
       </c>
       <c r="AO39" t="n">
-        <v>1219.05</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1124.21</v>
+        <v>283.86</v>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -5898,12 +5890,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5912,7 +5904,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>31.13725490196079</v>
+        <v>30.94117647058824</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5925,11 +5917,11 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>422000</v>
+        <v>2267000</v>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -5941,91 +5933,91 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>422000</v>
+        <v>2267000</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>18080</v>
+        <v>3755</v>
       </c>
       <c r="Q40" t="n">
-        <v>18080</v>
+        <v>3755</v>
       </c>
       <c r="R40" t="n">
-        <v>21389</v>
+        <v>709918</v>
       </c>
       <c r="S40" t="n">
-        <v>18321</v>
+        <v>3807</v>
       </c>
       <c r="T40" t="n">
-        <v>17505</v>
+        <v>3598.5</v>
       </c>
       <c r="U40" t="n">
-        <v>17495.5</v>
+        <v>3604.5</v>
       </c>
       <c r="V40" t="n">
-        <v>14694.33333333333</v>
+        <v>4038.416666666667</v>
       </c>
       <c r="W40" t="n">
-        <v>391.4886376153372</v>
+        <v>-14.0315202950128</v>
       </c>
       <c r="X40" t="n">
-        <v>424.0192350787105</v>
+        <v>-104.5448283533882</v>
       </c>
       <c r="Y40" t="n">
-        <v>-32.53059746337328</v>
+        <v>90.51330805837543</v>
       </c>
       <c r="Z40" t="n">
-        <v>-4.541236302445384</v>
+        <v>110.9240466277653</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.01062045835662384</v>
+        <v>-0.03096774193548391</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.9545945945945946</v>
+        <v>0.1808176100628931</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.1096842908226514</v>
+        <v>-0.1237642529524816</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.5829075992605348</v>
+        <v>-0.2462920308338294</v>
       </c>
       <c r="AF40" t="n">
-        <v>-0.6925918900831862</v>
+        <v>0.1225277778813478</v>
       </c>
       <c r="AG40" t="n">
-        <v>39.21568627450981</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AH40" t="n">
-        <v>70.58823529411765</v>
+        <v>17.64705882352941</v>
       </c>
       <c r="AI40" t="b">
         <v>1</v>
       </c>
       <c r="AJ40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM40" t="b">
         <v>0</v>
       </c>
       <c r="AN40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>18477.76</v>
-      </c>
-      <c r="AP40" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP40" t="n">
+        <v>3485.26</v>
       </c>
     </row>
     <row r="41">
@@ -6036,12 +6028,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6050,7 +6042,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>29.1764705882353</v>
+        <v>30.15686274509804</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6063,11 +6055,11 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2267000</v>
+        <v>1741000</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -6079,71 +6071,71 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2267000</v>
+        <v>1741000</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>3730</v>
+        <v>216</v>
       </c>
       <c r="Q41" t="n">
-        <v>3730</v>
+        <v>216</v>
       </c>
       <c r="R41" t="n">
-        <v>324804</v>
+        <v>3918660</v>
       </c>
       <c r="S41" t="n">
-        <v>3802</v>
+        <v>214.3</v>
       </c>
       <c r="T41" t="n">
-        <v>3597.25</v>
+        <v>208.1</v>
       </c>
       <c r="U41" t="n">
-        <v>3604.5</v>
+        <v>208.05</v>
       </c>
       <c r="V41" t="n">
-        <v>4038</v>
+        <v>207.4083333333333</v>
       </c>
       <c r="W41" t="n">
-        <v>-16.80929807279063</v>
+        <v>3.015496398254413</v>
       </c>
       <c r="X41" t="n">
-        <v>-105.1003839089438</v>
+        <v>1.848391806133995</v>
       </c>
       <c r="Y41" t="n">
-        <v>88.29108583615317</v>
+        <v>1.167104592120418</v>
       </c>
       <c r="Z41" t="n">
-        <v>110.9240466277653</v>
+        <v>1.554787379003262</v>
       </c>
       <c r="AA41" t="b">
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>-0.03741935483870973</v>
+        <v>0.004651162790697771</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.1729559748427674</v>
+        <v>0.1368421052631579</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.157724104017985</v>
+        <v>-0.08814534822629994</v>
       </c>
       <c r="AE41" t="n">
-        <v>-0.1987310204912924</v>
+        <v>-0.2902675356335647</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.04100691647330745</v>
+        <v>0.2021221874072647</v>
       </c>
       <c r="AG41" t="n">
-        <v>29.41176470588236</v>
+        <v>39.21568627450981</v>
       </c>
       <c r="AH41" t="n">
-        <v>17.64705882352941</v>
+        <v>13.72549019607843</v>
       </c>
       <c r="AI41" t="b">
         <v>1</v>
       </c>
       <c r="AJ41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK41" t="b">
         <v>1</v>
@@ -6162,8 +6154,10 @@
           <t>Already &gt; 0</t>
         </is>
       </c>
-      <c r="AP41" t="n">
-        <v>3510.26</v>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -6221,34 +6215,34 @@
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>93.69999694824219</v>
+        <v>93</v>
       </c>
       <c r="Q42" t="n">
-        <v>93.69999694824219</v>
+        <v>93</v>
       </c>
       <c r="R42" t="n">
-        <v>774206</v>
+        <v>1417113</v>
       </c>
       <c r="S42" t="n">
-        <v>92.91999969482421</v>
+        <v>92.78000030517578</v>
       </c>
       <c r="T42" t="n">
-        <v>88.3699993133545</v>
+        <v>88.33499946594239</v>
       </c>
       <c r="U42" t="n">
         <v>88.00999946594239</v>
       </c>
       <c r="V42" t="n">
-        <v>86.79833323160807</v>
+        <v>86.78666661580404</v>
       </c>
       <c r="W42" t="n">
-        <v>1.849931197574904</v>
+        <v>1.772153758881345</v>
       </c>
       <c r="X42" t="n">
-        <v>1.241579686144649</v>
+        <v>1.226024198405937</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.6083515114302551</v>
+        <v>0.5461295604754079</v>
       </c>
       <c r="Z42" t="n">
         <v>0.7262556831825802</v>
@@ -6257,19 +6251,19 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.08323695893921612</v>
+        <v>0.07514450867052025</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.1727158342780954</v>
+        <v>0.1639549214511355</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.03706779024005913</v>
+        <v>-0.01765200234647746</v>
       </c>
       <c r="AE42" t="n">
-        <v>-0.1989711610559644</v>
+        <v>-0.263154719445587</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.1619033708159052</v>
+        <v>0.2455027170991095</v>
       </c>
       <c r="AG42" t="n">
         <v>56.86274509803921</v>
@@ -6328,7 +6322,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>27.41176470588236</v>
+        <v>27.6078431372549</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6361,34 +6355,34 @@
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>364</v>
+        <v>365.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>364</v>
+        <v>365.5</v>
       </c>
       <c r="R43" t="n">
-        <v>530727</v>
+        <v>1159941</v>
       </c>
       <c r="S43" t="n">
-        <v>375.2</v>
+        <v>375.5</v>
       </c>
       <c r="T43" t="n">
-        <v>381.6</v>
+        <v>381.675</v>
       </c>
       <c r="U43" t="n">
         <v>383.75</v>
       </c>
       <c r="V43" t="n">
-        <v>350.625</v>
+        <v>350.65</v>
       </c>
       <c r="W43" t="n">
-        <v>-3.441565005451025</v>
+        <v>-3.27489833878434</v>
       </c>
       <c r="X43" t="n">
-        <v>-1.033249230202026</v>
+        <v>-0.9999158968686888</v>
       </c>
       <c r="Y43" t="n">
-        <v>-2.408315775248999</v>
+        <v>-2.274982441915651</v>
       </c>
       <c r="Z43" t="n">
         <v>-1.595170124141301</v>
@@ -6397,25 +6391,25 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>-0.1056511056511057</v>
+        <v>-0.101965601965602</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.4948665297741273</v>
+        <v>0.5010266940451746</v>
       </c>
       <c r="AD43" t="n">
-        <v>-0.2259558548303809</v>
+        <v>-0.1947621129825997</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.1231795344400675</v>
+        <v>0.07391705314845209</v>
       </c>
       <c r="AF43" t="n">
-        <v>-0.3491353892704484</v>
+        <v>-0.2686791661310518</v>
       </c>
       <c r="AG43" t="n">
         <v>13.72549019607843</v>
       </c>
       <c r="AH43" t="n">
-        <v>39.21568627450981</v>
+        <v>41.17647058823529</v>
       </c>
       <c r="AI43" t="b">
         <v>0</v>
@@ -6436,10 +6430,10 @@
         <v>1</v>
       </c>
       <c r="AO43" t="n">
-        <v>391.66</v>
+        <v>391.82</v>
       </c>
       <c r="AP43" t="n">
-        <v>406.53</v>
+        <v>405.03</v>
       </c>
     </row>
     <row r="44">
@@ -6464,7 +6458,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>25.64705882352941</v>
+        <v>25.25490196078432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6497,61 +6491,61 @@
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>2235</v>
+        <v>2145</v>
       </c>
       <c r="Q44" t="n">
-        <v>2235</v>
+        <v>2145</v>
       </c>
       <c r="R44" t="n">
-        <v>562030</v>
+        <v>1515838</v>
       </c>
       <c r="S44" t="n">
-        <v>2188</v>
+        <v>2170</v>
       </c>
       <c r="T44" t="n">
-        <v>2272.75</v>
+        <v>2268.25</v>
       </c>
       <c r="U44" t="n">
         <v>2300</v>
       </c>
       <c r="V44" t="n">
-        <v>2200.333333333333</v>
+        <v>2198.833333333333</v>
       </c>
       <c r="W44" t="n">
-        <v>-42.16622063753221</v>
+        <v>-52.16622063753221</v>
       </c>
       <c r="X44" t="n">
-        <v>-68.31363211633999</v>
+        <v>-70.31363211633999</v>
       </c>
       <c r="Y44" t="n">
-        <v>26.14741147880778</v>
+        <v>18.14741147880778</v>
       </c>
       <c r="Z44" t="n">
         <v>23.01011303055475</v>
       </c>
       <c r="AA44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.1960431654676259</v>
+        <v>-0.2284172661870504</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.4012539184952979</v>
+        <v>0.3448275862068966</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.3163479146469012</v>
+        <v>-0.3212137772040481</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.0295669231612381</v>
+        <v>-0.08228205468982597</v>
       </c>
       <c r="AF44" t="n">
-        <v>-0.3459148378081393</v>
+        <v>-0.2389317225142221</v>
       </c>
       <c r="AG44" t="n">
         <v>1.96078431372549</v>
       </c>
       <c r="AH44" t="n">
-        <v>29.41176470588236</v>
+        <v>25.49019607843137</v>
       </c>
       <c r="AI44" t="b">
         <v>0</v>
@@ -6566,7 +6560,7 @@
         <v>1</v>
       </c>
       <c r="AM44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="b">
         <v>0</v>
@@ -6577,7 +6571,7 @@
         </is>
       </c>
       <c r="AP44" t="n">
-        <v>2789.74</v>
+        <v>2879.74</v>
       </c>
     </row>
     <row r="45">
@@ -6588,12 +6582,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6602,7 +6596,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>21.92156862745098</v>
+        <v>21.52941176470588</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6615,11 +6609,11 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>852000</v>
+        <v>930000</v>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -6631,65 +6625,65 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>852000</v>
+        <v>930000</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>2505</v>
+        <v>3500</v>
       </c>
       <c r="Q45" t="n">
-        <v>2505</v>
+        <v>3500</v>
       </c>
       <c r="R45" t="n">
-        <v>67314</v>
+        <v>880821</v>
       </c>
       <c r="S45" t="n">
-        <v>2603</v>
+        <v>3291</v>
       </c>
       <c r="T45" t="n">
-        <v>2558</v>
+        <v>3500.5</v>
       </c>
       <c r="U45" t="n">
-        <v>2575.25</v>
+        <v>3512</v>
       </c>
       <c r="V45" t="n">
-        <v>2357.75</v>
+        <v>3547.916666666667</v>
       </c>
       <c r="W45" t="n">
-        <v>9.058049509932971</v>
+        <v>-70.77865993103933</v>
       </c>
       <c r="X45" t="n">
-        <v>13.36618241740763</v>
+        <v>-88.55682287102097</v>
       </c>
       <c r="Y45" t="n">
-        <v>-4.308132907474659</v>
+        <v>17.77816293998164</v>
       </c>
       <c r="Z45" t="n">
-        <v>6.328292574221891</v>
+        <v>-11.00101547515878</v>
       </c>
       <c r="AA45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.1210526315789474</v>
+        <v>-0.06166219839142095</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.6589403973509933</v>
+        <v>0.05105105105105112</v>
       </c>
       <c r="AD45" t="n">
-        <v>-0.2413573807582227</v>
+        <v>-0.1544587094084187</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.2872534020169335</v>
+        <v>-0.3760585898456714</v>
       </c>
       <c r="AF45" t="n">
-        <v>-0.5286107827751562</v>
+        <v>0.2215998804372528</v>
       </c>
       <c r="AG45" t="n">
-        <v>7.84313725490196</v>
+        <v>21.56862745098039</v>
       </c>
       <c r="AH45" t="n">
-        <v>52.94117647058824</v>
+        <v>3.92156862745098</v>
       </c>
       <c r="AI45" t="b">
         <v>0</v>
@@ -6698,22 +6692,24 @@
         <v>0</v>
       </c>
       <c r="AK45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>2555.1</v>
+        <v>0</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP45" t="n">
-        <v>2755.79</v>
+        <v>3580.53</v>
       </c>
     </row>
     <row r="46">
@@ -6724,12 +6720,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6738,7 +6734,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>20.74509803921568</v>
+        <v>20.74509803921569</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6751,11 +6747,11 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>167000</v>
+        <v>442000</v>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
@@ -6767,65 +6763,65 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>167000</v>
+        <v>442000</v>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>4610</v>
+        <v>8510</v>
       </c>
       <c r="Q46" t="n">
-        <v>4610</v>
+        <v>8510</v>
       </c>
       <c r="R46" t="n">
-        <v>237737</v>
+        <v>120036</v>
       </c>
       <c r="S46" t="n">
-        <v>4615</v>
+        <v>8436</v>
       </c>
       <c r="T46" t="n">
-        <v>4956.75</v>
+        <v>9286.75</v>
       </c>
       <c r="U46" t="n">
-        <v>4998.75</v>
+        <v>9354.25</v>
       </c>
       <c r="V46" t="n">
-        <v>3724.083333333333</v>
+        <v>8754.75</v>
       </c>
       <c r="W46" t="n">
-        <v>-38.00387931623663</v>
+        <v>-342.1216226599718</v>
       </c>
       <c r="X46" t="n">
-        <v>66.66459710008182</v>
+        <v>-239.8430153937691</v>
       </c>
       <c r="Y46" t="n">
-        <v>-104.6684764163185</v>
+        <v>-102.2786072662027</v>
       </c>
       <c r="Z46" t="n">
-        <v>-119.2039387840907</v>
+        <v>-146.0356984286772</v>
       </c>
       <c r="AA46" t="b">
         <v>1</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0.1541284403669725</v>
+        <v>-0.1369168356997972</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.105022831050228</v>
+        <v>0.7088353413654618</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.2744331895462477</v>
+        <v>-0.2297133467167949</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.7333358357161683</v>
+        <v>0.2817257004687392</v>
       </c>
       <c r="AF46" t="n">
-        <v>-1.007769025262416</v>
+        <v>-0.5114390471855341</v>
       </c>
       <c r="AG46" t="n">
-        <v>5.88235294117647</v>
+        <v>7.84313725490196</v>
       </c>
       <c r="AH46" t="n">
-        <v>78.43137254901961</v>
+        <v>56.86274509803921</v>
       </c>
       <c r="AI46" t="b">
         <v>0</v>
@@ -6843,11 +6839,13 @@
         <v>1</v>
       </c>
       <c r="AN46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>9667.360000000001</v>
+      </c>
       <c r="AP46" t="n">
-        <v>5575</v>
+        <v>10447.63</v>
       </c>
     </row>
     <row r="47">
@@ -6858,12 +6856,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6872,7 +6870,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>19.56862745098039</v>
+        <v>20.54901960784314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6885,11 +6883,11 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>107000</v>
+        <v>852000</v>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="K47" t="b">
         <v>0</v>
@@ -6901,65 +6899,65 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>107000</v>
+        <v>852000</v>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>105.5</v>
+        <v>2400</v>
       </c>
       <c r="Q47" t="n">
-        <v>105.5</v>
+        <v>2400</v>
       </c>
       <c r="R47" t="n">
-        <v>2600589</v>
+        <v>659668</v>
       </c>
       <c r="S47" t="n">
-        <v>107.3</v>
+        <v>2582</v>
       </c>
       <c r="T47" t="n">
-        <v>105.7</v>
+        <v>2552.75</v>
       </c>
       <c r="U47" t="n">
-        <v>105.925</v>
+        <v>2575.25</v>
       </c>
       <c r="V47" t="n">
-        <v>107.931666692098</v>
+        <v>2356</v>
       </c>
       <c r="W47" t="n">
-        <v>-0.0781756830967737</v>
+        <v>-2.608617156733089</v>
       </c>
       <c r="X47" t="n">
-        <v>-0.5108794442823443</v>
+        <v>11.03284908407442</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.4327037611855706</v>
+        <v>-13.64146624080751</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.6861140172179395</v>
+        <v>6.328292574221891</v>
       </c>
       <c r="AA47" t="b">
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.04090909090909089</v>
+        <v>-0.1578947368421053</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.08650877093595066</v>
+        <v>0.5894039735099337</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.1612138400883661</v>
+        <v>-0.250691247859103</v>
       </c>
       <c r="AE47" t="n">
-        <v>-0.2851782243981091</v>
+        <v>0.1622943326132111</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.123964384309743</v>
+        <v>-0.4129855804723142</v>
       </c>
       <c r="AG47" t="n">
-        <v>27.45098039215686</v>
+        <v>5.88235294117647</v>
       </c>
       <c r="AH47" t="n">
-        <v>5.88235294117647</v>
+        <v>45.09803921568628</v>
       </c>
       <c r="AI47" t="b">
         <v>0</v>
@@ -6968,24 +6966,22 @@
         <v>0</v>
       </c>
       <c r="AK47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="b">
         <v>0</v>
       </c>
       <c r="AN47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>2553.6</v>
       </c>
       <c r="AP47" t="n">
-        <v>107.21</v>
+        <v>2860.79</v>
       </c>
     </row>
     <row r="48">
@@ -6996,12 +6992,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7010,7 +7006,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>19.56862745098039</v>
+        <v>20.15686274509804</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7023,11 +7019,11 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>930000</v>
+        <v>167000</v>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -7039,65 +7035,65 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>930000</v>
+        <v>167000</v>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>3340</v>
+        <v>4515</v>
       </c>
       <c r="Q48" t="n">
-        <v>3340</v>
+        <v>4515</v>
       </c>
       <c r="R48" t="n">
-        <v>116350</v>
+        <v>539375</v>
       </c>
       <c r="S48" t="n">
-        <v>3259</v>
+        <v>4596</v>
       </c>
       <c r="T48" t="n">
-        <v>3492.5</v>
+        <v>4952</v>
       </c>
       <c r="U48" t="n">
-        <v>3512</v>
+        <v>4998.75</v>
       </c>
       <c r="V48" t="n">
-        <v>3545.25</v>
+        <v>3722.5</v>
       </c>
       <c r="W48" t="n">
-        <v>-88.55643770881716</v>
+        <v>-48.55943487179229</v>
       </c>
       <c r="X48" t="n">
-        <v>-92.11237842657653</v>
+        <v>64.55348598897068</v>
       </c>
       <c r="Y48" t="n">
-        <v>3.55594071775937</v>
+        <v>-113.112920860763</v>
       </c>
       <c r="Z48" t="n">
-        <v>-11.00101547515878</v>
+        <v>-119.2039387840907</v>
       </c>
       <c r="AA48" t="b">
         <v>1</v>
       </c>
       <c r="AB48" t="n">
-        <v>-0.1045576407506702</v>
+        <v>-0.171559633027523</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.003003003003003046</v>
+        <v>1.061643835616438</v>
       </c>
       <c r="AD48" t="n">
-        <v>-0.2248623899299454</v>
+        <v>-0.2643561440445207</v>
       </c>
       <c r="AE48" t="n">
-        <v>-0.3686839923310568</v>
+        <v>0.6345341947197158</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.1438216024011113</v>
+        <v>-0.8988903387642365</v>
       </c>
       <c r="AG48" t="n">
-        <v>15.68627450980392</v>
+        <v>3.92156862745098</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.96078431372549</v>
+        <v>78.43137254901961</v>
       </c>
       <c r="AI48" t="b">
         <v>0</v>
@@ -7106,10 +7102,10 @@
         <v>0</v>
       </c>
       <c r="AK48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="b">
         <v>1</v>
@@ -7117,13 +7113,9 @@
       <c r="AN48" t="b">
         <v>0</v>
       </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
+      <c r="AO48" t="inlineStr"/>
       <c r="AP48" t="n">
-        <v>3740.53</v>
+        <v>5670</v>
       </c>
     </row>
     <row r="49">
@@ -7148,7 +7140,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>18.98039215686275</v>
+        <v>19.76470588235294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7181,61 +7173,61 @@
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="Q49" t="n">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="R49" t="n">
-        <v>145937</v>
+        <v>217275</v>
       </c>
       <c r="S49" t="n">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="T49" t="n">
-        <v>1428.5</v>
+        <v>1428.25</v>
       </c>
       <c r="U49" t="n">
         <v>1437.25</v>
       </c>
       <c r="V49" t="n">
-        <v>1249.016666666667</v>
+        <v>1248.933333333333</v>
       </c>
       <c r="W49" t="n">
-        <v>-24.74770282208556</v>
+        <v>-25.30325837764099</v>
       </c>
       <c r="X49" t="n">
-        <v>-4.932782379826699</v>
+        <v>-5.043893490937784</v>
       </c>
       <c r="Y49" t="n">
-        <v>-19.81492044225886</v>
+        <v>-20.2593648867032</v>
       </c>
       <c r="Z49" t="n">
         <v>-20.096006647351</v>
       </c>
       <c r="AA49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>-0.1174496644295302</v>
+        <v>-0.1208053691275168</v>
       </c>
       <c r="AC49" t="n">
-        <v>0.3570691434468525</v>
+        <v>0.3519091847265221</v>
       </c>
       <c r="AD49" t="n">
-        <v>-0.2377544136088054</v>
+        <v>-0.2136018801445145</v>
       </c>
       <c r="AE49" t="n">
-        <v>-0.01461785188720732</v>
+        <v>-0.07520045617020044</v>
       </c>
       <c r="AF49" t="n">
-        <v>-0.2231365617215981</v>
+        <v>-0.1384014239743141</v>
       </c>
       <c r="AG49" t="n">
-        <v>9.803921568627452</v>
+        <v>11.76470588235294</v>
       </c>
       <c r="AH49" t="n">
-        <v>25.49019607843137</v>
+        <v>27.45098039215686</v>
       </c>
       <c r="AI49" t="b">
         <v>0</v>
@@ -7250,16 +7242,16 @@
         <v>0</v>
       </c>
       <c r="AM49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN49" t="b">
         <v>0</v>
       </c>
       <c r="AO49" t="n">
-        <v>1538.55</v>
+        <v>1537.94</v>
       </c>
       <c r="AP49" t="n">
-        <v>1624.47</v>
+        <v>1629.47</v>
       </c>
     </row>
     <row r="50">
@@ -7270,12 +7262,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7284,7 +7276,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>18.7843137254902</v>
+        <v>18.3921568627451</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7297,11 +7289,11 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>442000</v>
+        <v>107000</v>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
@@ -7313,65 +7305,65 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>442000</v>
+        <v>107000</v>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>8210</v>
+        <v>104</v>
       </c>
       <c r="Q50" t="n">
-        <v>8210</v>
+        <v>104</v>
       </c>
       <c r="R50" t="n">
-        <v>7535</v>
+        <v>6641744</v>
       </c>
       <c r="S50" t="n">
-        <v>8376</v>
+        <v>107</v>
       </c>
       <c r="T50" t="n">
-        <v>9271.75</v>
+        <v>105.625</v>
       </c>
       <c r="U50" t="n">
-        <v>9354.25</v>
+        <v>105.925</v>
       </c>
       <c r="V50" t="n">
-        <v>8749.75</v>
+        <v>107.906666692098</v>
       </c>
       <c r="W50" t="n">
-        <v>-375.4549559933057</v>
+        <v>-0.2448423497634451</v>
       </c>
       <c r="X50" t="n">
-        <v>-246.5096820604359</v>
+        <v>-0.5442127776156785</v>
       </c>
       <c r="Y50" t="n">
-        <v>-128.9452739328698</v>
+        <v>0.2993704278522334</v>
       </c>
       <c r="Z50" t="n">
-        <v>-146.0356984286772</v>
+        <v>0.6861140172179395</v>
       </c>
       <c r="AA50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>-0.1673427991886409</v>
+        <v>-0.05454545454545456</v>
       </c>
       <c r="AC50" t="n">
-        <v>0.6485943775100402</v>
+        <v>0.07106077893212204</v>
       </c>
       <c r="AD50" t="n">
-        <v>-0.2876475483679162</v>
+        <v>-0.1473419655624523</v>
       </c>
       <c r="AE50" t="n">
-        <v>0.2769073821759804</v>
+        <v>-0.3560488619646005</v>
       </c>
       <c r="AF50" t="n">
-        <v>-0.5645549305438966</v>
+        <v>0.2087068964021482</v>
       </c>
       <c r="AG50" t="n">
-        <v>3.92156862745098</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="AH50" t="n">
-        <v>49.01960784313725</v>
+        <v>5.88235294117647</v>
       </c>
       <c r="AI50" t="b">
         <v>0</v>
@@ -7380,22 +7372,24 @@
         <v>0</v>
       </c>
       <c r="AK50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN50" t="b">
         <v>0</v>
       </c>
-      <c r="AO50" t="n">
-        <v>9671.379999999999</v>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP50" t="n">
-        <v>10747.63</v>
+        <v>108.71</v>
       </c>
     </row>
     <row r="51">
@@ -7420,7 +7414,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>18.58823529411765</v>
+        <v>17.41176470588236</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7453,34 +7447,34 @@
       </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>4470</v>
+        <v>4400</v>
       </c>
       <c r="Q51" t="n">
-        <v>4470</v>
+        <v>4400</v>
       </c>
       <c r="R51" t="n">
-        <v>263614</v>
+        <v>599355</v>
       </c>
       <c r="S51" t="n">
-        <v>4582</v>
+        <v>4568</v>
       </c>
       <c r="T51" t="n">
-        <v>4723</v>
+        <v>4719.5</v>
       </c>
       <c r="U51" t="n">
         <v>4739.25</v>
       </c>
       <c r="V51" t="n">
-        <v>3862.166666666667</v>
+        <v>3861</v>
       </c>
       <c r="W51" t="n">
-        <v>6.83222283312989</v>
+        <v>-0.9455549446474834</v>
       </c>
       <c r="X51" t="n">
-        <v>62.52463848700732</v>
+        <v>60.96908293145184</v>
       </c>
       <c r="Y51" t="n">
-        <v>-55.69241565387743</v>
+        <v>-61.91463787609932</v>
       </c>
       <c r="Z51" t="n">
         <v>-51.06745263124361</v>
@@ -7489,22 +7483,22 @@
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>-0.06777893639207511</v>
+        <v>-0.08237747653806049</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.4924874791318865</v>
+        <v>0.4691151919866443</v>
       </c>
       <c r="AD51" t="n">
-        <v>-0.1880836855713504</v>
+        <v>-0.1751739875550582</v>
       </c>
       <c r="AE51" t="n">
-        <v>0.1208004837978267</v>
+        <v>0.04200555108992177</v>
       </c>
       <c r="AF51" t="n">
-        <v>-0.3088841693691771</v>
+        <v>-0.21717953864498</v>
       </c>
       <c r="AG51" t="n">
-        <v>19.6078431372549</v>
+        <v>15.68627450980392</v>
       </c>
       <c r="AH51" t="n">
         <v>37.25490196078432</v>
@@ -7528,10 +7522,10 @@
         <v>1</v>
       </c>
       <c r="AO51" t="n">
-        <v>5104.74</v>
+        <v>5104</v>
       </c>
       <c r="AP51" t="n">
-        <v>5156.32</v>
+        <v>5226.32</v>
       </c>
     </row>
     <row r="52">
@@ -7556,7 +7550,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>16.62745098039215</v>
+        <v>15.84313725490196</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7589,34 +7583,34 @@
       </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>165</v>
+        <v>162.5</v>
       </c>
       <c r="Q52" t="n">
-        <v>165</v>
+        <v>162.5</v>
       </c>
       <c r="R52" t="n">
-        <v>3096451</v>
+        <v>9631188</v>
       </c>
       <c r="S52" t="n">
-        <v>170.3</v>
+        <v>169.8</v>
       </c>
       <c r="T52" t="n">
-        <v>167.25</v>
+        <v>167.125</v>
       </c>
       <c r="U52" t="n">
         <v>168.275</v>
       </c>
       <c r="V52" t="n">
-        <v>141.9416666666667</v>
+        <v>141.9</v>
       </c>
       <c r="W52" t="n">
-        <v>2.334167831458871</v>
+        <v>2.056390053681127</v>
       </c>
       <c r="X52" t="n">
-        <v>3.289701431938443</v>
+        <v>3.234145876382895</v>
       </c>
       <c r="Y52" t="n">
-        <v>-0.9555336004795727</v>
+        <v>-1.177755822701767</v>
       </c>
       <c r="Z52" t="n">
         <v>-0.4431257960221235</v>
@@ -7625,25 +7619,25 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>-0.1105121293800539</v>
+        <v>-0.123989218328841</v>
       </c>
       <c r="AC52" t="n">
-        <v>0.5</v>
+        <v>0.4772727272727273</v>
       </c>
       <c r="AD52" t="n">
-        <v>-0.2308168785593292</v>
+        <v>-0.2167857293458387</v>
       </c>
       <c r="AE52" t="n">
-        <v>0.1283130046659402</v>
+        <v>0.05016308637600475</v>
       </c>
       <c r="AF52" t="n">
-        <v>-0.3591298832252694</v>
+        <v>-0.2669488157218435</v>
       </c>
       <c r="AG52" t="n">
-        <v>11.76470588235294</v>
+        <v>9.803921568627452</v>
       </c>
       <c r="AH52" t="n">
-        <v>41.17647058823529</v>
+        <v>39.21568627450981</v>
       </c>
       <c r="AI52" t="b">
         <v>0</v>
@@ -7664,10 +7658,10 @@
         <v>1</v>
       </c>
       <c r="AO52" t="n">
-        <v>175.89</v>
+        <v>175.82</v>
       </c>
       <c r="AP52" t="n">
-        <v>169.87</v>
+        <v>172.37</v>
       </c>
     </row>
   </sheetData>

--- a/output/daily_screen_latest.xlsx
+++ b/output/daily_screen_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP52"/>
+  <dimension ref="A1:AP51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,12 +636,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -650,94 +650,96 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>86.8235294117647</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5000</v>
+        <v>511000</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>511000</v>
       </c>
       <c r="N2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
       <c r="P2" t="n">
-        <v>165</v>
+        <v>96.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>165</v>
+        <v>96.5</v>
       </c>
       <c r="R2" t="n">
-        <v>35905249</v>
+        <v>8488255</v>
       </c>
       <c r="S2" t="n">
-        <v>157.9</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>135.35</v>
+        <v>83.63499946594239</v>
       </c>
       <c r="U2" t="n">
-        <v>132.275</v>
+        <v>82.80999946594238</v>
       </c>
       <c r="V2" t="n">
-        <v>110.7683097839355</v>
+        <v>81.49333305358887</v>
       </c>
       <c r="W2" t="n">
-        <v>11.10123923392149</v>
+        <v>4.059223991182094</v>
       </c>
       <c r="X2" t="n">
-        <v>9.971868476328046</v>
+        <v>2.419161379505194</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.129370757593444</v>
+        <v>1.6400626116769</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.8483992520466259</v>
+        <v>1.539528706158522</v>
       </c>
       <c r="AA2" t="b">
         <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5942028985507246</v>
+        <v>0.20625</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.036659893144215</v>
+        <v>0.1015981927044001</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.5014063875337269</v>
+        <v>0.1169740135302608</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.6095502522474923</v>
+        <v>-0.3209139092436204</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.1081438647137654</v>
+        <v>0.4378879227738812</v>
       </c>
       <c r="AG2" t="n">
-        <v>98.0392156862745</v>
+        <v>80</v>
       </c>
       <c r="AH2" t="n">
-        <v>74.50980392156863</v>
+        <v>10</v>
       </c>
       <c r="AI2" t="b">
         <v>1</v>
@@ -776,12 +778,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -790,94 +792,96 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>75.64705882352941</v>
+        <v>74</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5163000</v>
+        <v>2437000</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2437000</v>
       </c>
       <c r="N3" t="n">
-        <v>5163000</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
       <c r="P3" t="n">
-        <v>19.39999961853027</v>
+        <v>5570</v>
       </c>
       <c r="Q3" t="n">
-        <v>19.39999961853027</v>
+        <v>5570</v>
       </c>
       <c r="R3" t="n">
-        <v>35969294</v>
+        <v>1702970</v>
       </c>
       <c r="S3" t="n">
-        <v>19.19000015258789</v>
+        <v>5521</v>
       </c>
       <c r="T3" t="n">
-        <v>18.74500017166138</v>
+        <v>5337</v>
       </c>
       <c r="U3" t="n">
-        <v>18.71750020980835</v>
+        <v>5302.5</v>
       </c>
       <c r="V3" t="n">
-        <v>19.1650000890096</v>
+        <v>4446.833333333333</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1545423837672537</v>
+        <v>141.4487233413311</v>
       </c>
       <c r="X3" t="n">
-        <v>0.06196400749637893</v>
+        <v>140.3686020750009</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.09257837627087478</v>
+        <v>1.080121266330195</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.09247098408578769</v>
+        <v>-2.235203542517638</v>
       </c>
       <c r="AA3" t="b">
         <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02917767776817759</v>
+        <v>0.1413934426229508</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.01305483054725975</v>
+        <v>0.4173027989821882</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.06361883324882012</v>
+        <v>0.05211745615321162</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.4140548103494628</v>
+        <v>-0.005209302965832219</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3504359771006427</v>
+        <v>0.05732675911904384</v>
       </c>
       <c r="AG3" t="n">
-        <v>43.13725490196079</v>
+        <v>68</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.96078431372549</v>
+        <v>32</v>
       </c>
       <c r="AI3" t="b">
         <v>1</v>
@@ -930,16 +934,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>60.94117647058824</v>
+        <v>53.79999999999999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -953,44 +957,46 @@
         <v>0</v>
       </c>
       <c r="L4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2169000</v>
       </c>
       <c r="N4" t="n">
-        <v>2169000</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
       <c r="P4" t="n">
-        <v>6030</v>
+        <v>6070</v>
       </c>
       <c r="Q4" t="n">
-        <v>6030</v>
+        <v>6070</v>
       </c>
       <c r="R4" t="n">
-        <v>397050</v>
+        <v>902920</v>
       </c>
       <c r="S4" t="n">
-        <v>5817</v>
+        <v>5825</v>
       </c>
       <c r="T4" t="n">
-        <v>5822.75</v>
+        <v>5824.75</v>
       </c>
       <c r="U4" t="n">
         <v>5772.75</v>
       </c>
       <c r="V4" t="n">
-        <v>4784.166666666667</v>
+        <v>4784.833333333333</v>
       </c>
       <c r="W4" t="n">
-        <v>103.7180619953206</v>
+        <v>108.1625064397649</v>
       </c>
       <c r="X4" t="n">
-        <v>173.5261543710339</v>
+        <v>174.4150432599227</v>
       </c>
       <c r="Y4" t="n">
-        <v>-69.8080923757133</v>
+        <v>-66.25253682015781</v>
       </c>
       <c r="Z4" t="n">
         <v>-96.5315853696751</v>
@@ -999,25 +1005,25 @@
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1988071570576542</v>
+        <v>0.2067594433399602</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.216911764705882</v>
+        <v>1.231617647058823</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.1060106460406565</v>
+        <v>0.117483456870221</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.7898021238091597</v>
+        <v>0.8091055451108029</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.6837914777685032</v>
+        <v>-0.6916220882405819</v>
       </c>
       <c r="AG4" t="n">
-        <v>80.3921568627451</v>
+        <v>82</v>
       </c>
       <c r="AH4" t="n">
-        <v>86.27450980392157</v>
+        <v>88</v>
       </c>
       <c r="AI4" t="b">
         <v>1</v>
@@ -1038,7 +1044,7 @@
         <v>1</v>
       </c>
       <c r="AO4" t="n">
-        <v>6825.96</v>
+        <v>6822.68</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -1068,16 +1074,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>49.96078431372549</v>
+        <v>47</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1091,44 +1097,46 @@
         <v>0</v>
       </c>
       <c r="L5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1200000</v>
       </c>
       <c r="N5" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
       <c r="P5" t="n">
-        <v>1180</v>
+        <v>1230</v>
       </c>
       <c r="Q5" t="n">
-        <v>1180</v>
+        <v>1230</v>
       </c>
       <c r="R5" t="n">
-        <v>2639295</v>
+        <v>6414485</v>
       </c>
       <c r="S5" t="n">
-        <v>1163</v>
+        <v>1173</v>
       </c>
       <c r="T5" t="n">
-        <v>1107.15</v>
+        <v>1109.65</v>
       </c>
       <c r="U5" t="n">
         <v>1098</v>
       </c>
       <c r="V5" t="n">
-        <v>999.9666666666667</v>
+        <v>1000.8</v>
       </c>
       <c r="W5" t="n">
-        <v>34.38049037101223</v>
+        <v>39.93604592656789</v>
       </c>
       <c r="X5" t="n">
-        <v>41.23198174430112</v>
+        <v>42.34309285541225</v>
       </c>
       <c r="Y5" t="n">
-        <v>-6.851491373288887</v>
+        <v>-2.407046928844366</v>
       </c>
       <c r="Z5" t="n">
         <v>-6.941223400875387</v>
@@ -1137,25 +1145,25 @@
         <v>1</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1835506519558676</v>
+        <v>0.2337011033099299</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1028037383177569</v>
+        <v>0.1495327102803738</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.09075414093886991</v>
+        <v>0.1444251168401907</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.3243059025789656</v>
+        <v>-0.2729793916676466</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4150600435178355</v>
+        <v>0.4174045085078373</v>
       </c>
       <c r="AG5" t="n">
-        <v>76.47058823529412</v>
+        <v>84</v>
       </c>
       <c r="AH5" t="n">
-        <v>11.76470588235294</v>
+        <v>14</v>
       </c>
       <c r="AI5" t="b">
         <v>1</v>
@@ -1176,7 +1184,7 @@
         <v>1</v>
       </c>
       <c r="AO5" t="n">
-        <v>1257.88</v>
+        <v>1259.52</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -1192,12 +1200,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1206,94 +1214,96 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>45.64705882352941</v>
+        <v>44.8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1034000</v>
+        <v>2167000</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2167000</v>
       </c>
       <c r="N6" t="n">
-        <v>1034000</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
       <c r="P6" t="n">
-        <v>1125</v>
+        <v>1420</v>
       </c>
       <c r="Q6" t="n">
-        <v>1125</v>
+        <v>1420</v>
       </c>
       <c r="R6" t="n">
-        <v>1561526</v>
+        <v>2302942</v>
       </c>
       <c r="S6" t="n">
-        <v>1081</v>
+        <v>1403</v>
       </c>
       <c r="T6" t="n">
-        <v>1083.2</v>
+        <v>1409.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1080.7</v>
+        <v>1403</v>
       </c>
       <c r="V6" t="n">
-        <v>1034.848440551758</v>
+        <v>1126.483333333333</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3747388243014029</v>
+        <v>26.92473248428678</v>
       </c>
       <c r="X6" t="n">
-        <v>2.699578985391791</v>
+        <v>33.29571673869047</v>
       </c>
       <c r="Y6" t="n">
-        <v>-2.324840161090388</v>
+        <v>-6.370984254403687</v>
       </c>
       <c r="Z6" t="n">
-        <v>-6.745457503645538</v>
+        <v>-7.687376230837643</v>
       </c>
       <c r="AA6" t="b">
         <v>1</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.04651162790697683</v>
+        <v>0.1007751937984496</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.6158535997364418</v>
+        <v>0.6303099885189438</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.04628488311002088</v>
+        <v>0.01149920732871035</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.1887439588397193</v>
+        <v>0.2077978865709234</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.2350288419497402</v>
+        <v>-0.196298679242213</v>
       </c>
       <c r="AG6" t="n">
-        <v>50.98039215686274</v>
+        <v>64</v>
       </c>
       <c r="AH6" t="n">
-        <v>49.01960784313725</v>
+        <v>52</v>
       </c>
       <c r="AI6" t="b">
         <v>1</v>
@@ -1314,7 +1324,7 @@
         <v>1</v>
       </c>
       <c r="AO6" t="n">
-        <v>1152</v>
+        <v>1493.84</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -1330,12 +1340,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1344,94 +1354,96 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40.15686274509804</v>
+        <v>42.6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3645000</v>
+        <v>7769000</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="K7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>7769000</v>
       </c>
       <c r="N7" t="n">
-        <v>3645000</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
       <c r="P7" t="n">
-        <v>325</v>
+        <v>1350</v>
       </c>
       <c r="Q7" t="n">
-        <v>325</v>
+        <v>1350</v>
       </c>
       <c r="R7" t="n">
-        <v>24070055</v>
+        <v>4189747</v>
       </c>
       <c r="S7" t="n">
-        <v>320.1</v>
+        <v>1331</v>
       </c>
       <c r="T7" t="n">
-        <v>307.35</v>
+        <v>1339</v>
       </c>
       <c r="U7" t="n">
-        <v>308.05</v>
+        <v>1344</v>
       </c>
       <c r="V7" t="n">
-        <v>296.975</v>
+        <v>1180.583333333333</v>
       </c>
       <c r="W7" t="n">
-        <v>5.316555615809136</v>
+        <v>4.084184598742013</v>
       </c>
       <c r="X7" t="n">
-        <v>4.296119943221202</v>
+        <v>7.022210002142598</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.020435672587935</v>
+        <v>-2.938025403400585</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.7909858073156304</v>
+        <v>-4.612508583835297</v>
       </c>
       <c r="AA7" t="b">
         <v>1</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.04129793510324486</v>
+        <v>-0.06896551724137934</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1948529411764706</v>
+        <v>0.773981603153745</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.1340944461202426</v>
+        <v>-0.1582415037111186</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.232256699720252</v>
+        <v>0.3514695012057245</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.09816225360000941</v>
+        <v>-0.5097110049168431</v>
       </c>
       <c r="AG7" t="n">
-        <v>27.45098039215686</v>
+        <v>20</v>
       </c>
       <c r="AH7" t="n">
-        <v>21.56862745098039</v>
+        <v>62</v>
       </c>
       <c r="AI7" t="b">
         <v>1</v>
@@ -1440,24 +1452,22 @@
         <v>0</v>
       </c>
       <c r="AK7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="b">
         <v>1</v>
       </c>
       <c r="AN7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1385.1</v>
       </c>
       <c r="AP7" t="n">
-        <v>292.42</v>
+        <v>1318.42</v>
       </c>
     </row>
     <row r="8">
@@ -1468,12 +1478,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1482,100 +1492,102 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>33.09803921568627</v>
+        <v>40.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1000</v>
+        <v>1034000</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1034000</v>
       </c>
       <c r="N8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
       <c r="P8" t="n">
-        <v>235.5</v>
+        <v>1120</v>
       </c>
       <c r="Q8" t="n">
-        <v>235.5</v>
+        <v>1120</v>
       </c>
       <c r="R8" t="n">
-        <v>7502148</v>
+        <v>3671940</v>
       </c>
       <c r="S8" t="n">
-        <v>229.2</v>
+        <v>1080</v>
       </c>
       <c r="T8" t="n">
-        <v>226.025</v>
+        <v>1082.95</v>
       </c>
       <c r="U8" t="n">
-        <v>226.675</v>
+        <v>1080.7</v>
       </c>
       <c r="V8" t="n">
-        <v>193.5916666666667</v>
+        <v>1034.765107218424</v>
       </c>
       <c r="W8" t="n">
-        <v>3.301655800429103</v>
+        <v>-0.1808167312542537</v>
       </c>
       <c r="X8" t="n">
-        <v>4.029491294472227</v>
+        <v>2.588467874280659</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.7278354940431244</v>
+        <v>-2.769284605534913</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1.608171744958133</v>
+        <v>-6.745457503645538</v>
       </c>
       <c r="AA8" t="b">
         <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.0523138832997988</v>
+        <v>0.04186046511627906</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.7706766917293233</v>
+        <v>0.6086720281820577</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.1451103943167965</v>
+        <v>-0.04741552135346017</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.3435670508326008</v>
+        <v>0.1861599262340372</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.4886774451493973</v>
+        <v>-0.2335754475874974</v>
       </c>
       <c r="AG8" t="n">
-        <v>25.49019607843137</v>
+        <v>52</v>
       </c>
       <c r="AH8" t="n">
-        <v>64.70588235294117</v>
+        <v>48</v>
       </c>
       <c r="AI8" t="b">
         <v>1</v>
       </c>
       <c r="AJ8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK8" t="b">
         <v>0</v>
@@ -1590,10 +1602,12 @@
         <v>1</v>
       </c>
       <c r="AO8" t="n">
-        <v>243.98</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>214.03</v>
+        <v>1151.36</v>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1604,136 +1618,134 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>77.21568627450981</v>
+        <v>37.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>18313000</v>
+        <v>6231000</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>6231000</v>
       </c>
       <c r="N9" t="n">
-        <v>18313000</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
       <c r="P9" t="n">
-        <v>755</v>
+        <v>2510</v>
       </c>
       <c r="Q9" t="n">
-        <v>755</v>
+        <v>2510</v>
       </c>
       <c r="R9" t="n">
-        <v>8871204</v>
+        <v>2249619</v>
       </c>
       <c r="S9" t="n">
-        <v>789.8</v>
+        <v>2492</v>
       </c>
       <c r="T9" t="n">
-        <v>600.025</v>
+        <v>2498.5</v>
       </c>
       <c r="U9" t="n">
-        <v>580.85</v>
+        <v>2501</v>
       </c>
       <c r="V9" t="n">
-        <v>393.0666666666667</v>
+        <v>2070.416666666667</v>
       </c>
       <c r="W9" t="n">
-        <v>91.51056474848281</v>
+        <v>29.58956661764296</v>
       </c>
       <c r="X9" t="n">
-        <v>87.04701482363542</v>
+        <v>45.25126747465071</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.463549924847385</v>
+        <v>-15.66170085700775</v>
       </c>
       <c r="Z9" t="n">
-        <v>15.75753401466386</v>
+        <v>-16.6073198054698</v>
       </c>
       <c r="AA9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.032301480484522</v>
+        <v>-0.01953125</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.038229376257545</v>
+        <v>0.818840579710145</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.9395049694675246</v>
+        <v>-0.1088072364697392</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.611119735360823</v>
+        <v>0.3963284777621245</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.6716147658932983</v>
+        <v>-0.5051357142318638</v>
       </c>
       <c r="AG9" t="n">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="AH9" t="n">
-        <v>96.07843137254902</v>
+        <v>66</v>
       </c>
       <c r="AI9" t="b">
         <v>1</v>
       </c>
       <c r="AJ9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>2690.72</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2362.89</v>
       </c>
     </row>
     <row r="10">
@@ -1744,114 +1756,116 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>71.52941176470588</v>
+        <v>35.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>71690000</v>
+        <v>1000</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="K10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N10" t="n">
-        <v>71690000</v>
-      </c>
-      <c r="O10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
       <c r="P10" t="n">
-        <v>125.5</v>
+        <v>236.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>125.5</v>
+        <v>236.5</v>
       </c>
       <c r="R10" t="n">
-        <v>151429262</v>
+        <v>12800688</v>
       </c>
       <c r="S10" t="n">
-        <v>137.6</v>
+        <v>229.4</v>
       </c>
       <c r="T10" t="n">
-        <v>119.9100002288818</v>
+        <v>226.075</v>
       </c>
       <c r="U10" t="n">
-        <v>118.4600002288818</v>
+        <v>226.675</v>
       </c>
       <c r="V10" t="n">
-        <v>84.13166656494141</v>
+        <v>193.6083333333333</v>
       </c>
       <c r="W10" t="n">
-        <v>8.835867388474554</v>
+        <v>3.412766911540189</v>
       </c>
       <c r="X10" t="n">
-        <v>11.19014533062835</v>
+        <v>4.051713516694445</v>
       </c>
       <c r="Y10" t="n">
-        <v>-2.354277942153798</v>
+        <v>-0.6389466051542563</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.6983303021822458</v>
+        <v>-1.608171744958133</v>
       </c>
       <c r="AA10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.3005181347150259</v>
+        <v>-0.04828973843058348</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.102177527573967</v>
+        <v>0.7781954887218046</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.2077216236980282</v>
+        <v>-0.1375657249003227</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.6750678866772444</v>
+        <v>0.3556833867737841</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.4673462629792162</v>
+        <v>-0.4932491116741068</v>
       </c>
       <c r="AG10" t="n">
-        <v>84.31372549019608</v>
+        <v>28</v>
       </c>
       <c r="AH10" t="n">
-        <v>82.35294117647058</v>
+        <v>64</v>
       </c>
       <c r="AI10" t="b">
         <v>1</v>
       </c>
       <c r="AJ10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="b">
         <v>0</v>
@@ -1860,16 +1874,16 @@
         <v>0</v>
       </c>
       <c r="AM10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>244.07</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>213.03</v>
       </c>
     </row>
     <row r="11">
@@ -1880,134 +1894,136 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>64.07843137254902</v>
+        <v>27.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>12466000</v>
+        <v>930000</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
+        <v>35</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>930000</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3505</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3505</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1620880</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3292</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3500.75</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3512</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3548</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-70.22310437548413</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-88.44571175990993</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>18.2226073844258</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-11.00101547515878</v>
+      </c>
+      <c r="AA11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0.06032171581769441</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.05255255255255253</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0.1495977022874336</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.3699595493954679</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.2203618471080343</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH11" t="n">
         <v>4</v>
       </c>
-      <c r="K11" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" t="b">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>12466000</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="n">
-        <v>978</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>978</v>
-      </c>
-      <c r="R11" t="n">
-        <v>5544998</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1011.6</v>
-      </c>
-      <c r="T11" t="n">
-        <v>935.9</v>
-      </c>
-      <c r="U11" t="n">
-        <v>931.8</v>
-      </c>
-      <c r="V11" t="n">
-        <v>732.275</v>
-      </c>
-      <c r="W11" t="n">
-        <v>38.02870957503342</v>
-      </c>
-      <c r="X11" t="n">
-        <v>49.34160696485605</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>-11.31289738982263</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>-6.293339870886868</v>
-      </c>
-      <c r="AA11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.09151785714285721</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.51413881748072</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>-0.001278653874140501</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.087029176583997</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>-1.088307830458138</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>60.78431372549019</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>90.19607843137256</v>
-      </c>
       <c r="AI11" t="b">
         <v>1</v>
       </c>
       <c r="AJ11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1107.1</v>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP11" t="n">
+        <v>3575.53</v>
       </c>
     </row>
     <row r="12">
@@ -2018,12 +2034,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2032,94 +2048,96 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>62.90196078431373</v>
+        <v>60</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>17948000</v>
+        <v>18313000</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
       </c>
       <c r="L12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>18313000</v>
       </c>
       <c r="N12" t="n">
-        <v>17948000</v>
-      </c>
-      <c r="O12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
       <c r="P12" t="n">
-        <v>600</v>
+        <v>743</v>
       </c>
       <c r="Q12" t="n">
-        <v>600</v>
+        <v>743</v>
       </c>
       <c r="R12" t="n">
-        <v>7205584</v>
+        <v>23920412</v>
       </c>
       <c r="S12" t="n">
-        <v>604</v>
+        <v>787.4</v>
       </c>
       <c r="T12" t="n">
-        <v>564.85</v>
+        <v>599.425</v>
       </c>
       <c r="U12" t="n">
-        <v>561.85</v>
+        <v>580.85</v>
       </c>
       <c r="V12" t="n">
-        <v>460.65</v>
+        <v>392.8666666666667</v>
       </c>
       <c r="W12" t="n">
-        <v>23.03162032440741</v>
+        <v>90.17723141514944</v>
       </c>
       <c r="X12" t="n">
-        <v>25.23078729493248</v>
+        <v>86.78034815696874</v>
       </c>
       <c r="Y12" t="n">
-        <v>-2.199166970525066</v>
+        <v>3.396883258180694</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.0004004860842634628</v>
+        <v>15.75753401466386</v>
       </c>
       <c r="AA12" t="b">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.1111111111111112</v>
+        <v>1</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.875</v>
+        <v>1.989939637826962</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.01831460009411345</v>
+        <v>0.9107240135302608</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.4478903591032775</v>
+        <v>1.567427535878941</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.429575759009164</v>
+        <v>-0.6567035223486803</v>
       </c>
       <c r="AG12" t="n">
-        <v>62.74509803921568</v>
+        <v>100</v>
       </c>
       <c r="AH12" t="n">
-        <v>68.62745098039215</v>
+        <v>96</v>
       </c>
       <c r="AI12" t="b">
         <v>1</v>
@@ -2128,19 +2146,21 @@
         <v>1</v>
       </c>
       <c r="AK12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM12" t="b">
         <v>0</v>
       </c>
       <c r="AN12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>625.2</v>
+        <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
@@ -2156,12 +2176,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2170,94 +2190,96 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>60.74509803921569</v>
+        <v>55.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5775000</v>
+        <v>71690000</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>71690000</v>
       </c>
       <c r="N13" t="n">
-        <v>5775000</v>
-      </c>
-      <c r="O13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="P13" t="n">
-        <v>257.5</v>
+        <v>125</v>
       </c>
       <c r="Q13" t="n">
-        <v>257.5</v>
+        <v>125</v>
       </c>
       <c r="R13" t="n">
-        <v>23258689</v>
+        <v>377727651</v>
       </c>
       <c r="S13" t="n">
-        <v>280.9</v>
+        <v>137.5</v>
       </c>
       <c r="T13" t="n">
-        <v>234.1</v>
+        <v>119.8850002288818</v>
       </c>
       <c r="U13" t="n">
-        <v>230.85</v>
+        <v>118.4600002288818</v>
       </c>
       <c r="V13" t="n">
-        <v>147.7183334350586</v>
+        <v>84.12333323160807</v>
       </c>
       <c r="W13" t="n">
-        <v>21.92411684929559</v>
+        <v>8.780311832918997</v>
       </c>
       <c r="X13" t="n">
-        <v>24.50316473606305</v>
+        <v>11.17903421951724</v>
       </c>
       <c r="Y13" t="n">
-        <v>-2.579047886767462</v>
+        <v>-2.398722386598244</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.9570741363087407</v>
+        <v>-0.6983303021822458</v>
       </c>
       <c r="AA13" t="b">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.3376623376623376</v>
+        <v>0.2953367875647668</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.019493252038391</v>
+        <v>1.093802318300764</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.2448658266453398</v>
+        <v>0.2060608010950276</v>
       </c>
       <c r="AE13" t="n">
-        <v>3.592383611141668</v>
+        <v>0.6712902163527432</v>
       </c>
       <c r="AF13" t="n">
-        <v>-3.347517784496328</v>
+        <v>-0.4652294152577157</v>
       </c>
       <c r="AG13" t="n">
-        <v>90.19607843137256</v>
+        <v>90</v>
       </c>
       <c r="AH13" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AI13" t="b">
         <v>1</v>
@@ -2275,11 +2297,9 @@
         <v>0</v>
       </c>
       <c r="AN13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>286.86</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -2294,12 +2314,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2308,94 +2328,96 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>60.54901960784314</v>
+        <v>48.6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>7307000</v>
+        <v>5775000</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>5775000</v>
       </c>
       <c r="N14" t="n">
-        <v>7307000</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="P14" t="n">
-        <v>300</v>
+        <v>271</v>
       </c>
       <c r="Q14" t="n">
-        <v>300</v>
+        <v>271</v>
       </c>
       <c r="R14" t="n">
-        <v>43692807</v>
+        <v>45447891</v>
       </c>
       <c r="S14" t="n">
-        <v>298.6</v>
+        <v>283.6</v>
       </c>
       <c r="T14" t="n">
-        <v>263.35</v>
+        <v>234.775</v>
       </c>
       <c r="U14" t="n">
-        <v>261.025</v>
+        <v>230.85</v>
       </c>
       <c r="V14" t="n">
-        <v>228.5333333333333</v>
+        <v>147.9433334350586</v>
       </c>
       <c r="W14" t="n">
-        <v>16.18942370819047</v>
+        <v>23.42411684929559</v>
       </c>
       <c r="X14" t="n">
-        <v>11.91500887108731</v>
+        <v>24.80316473606305</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.274414837103162</v>
+        <v>-1.379047886767463</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.400278270071549</v>
+        <v>0.9570741363087407</v>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.1834319526627219</v>
+        <v>0.4077922077922078</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.4251781472684086</v>
+        <v>4.282651150688947</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.09063544164572424</v>
+        <v>0.3185162213224686</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.001931493628313907</v>
+        <v>3.860139048740927</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.09256693527403814</v>
+        <v>-3.541622827418458</v>
       </c>
       <c r="AG14" t="n">
-        <v>74.50980392156863</v>
+        <v>94</v>
       </c>
       <c r="AH14" t="n">
-        <v>33.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="AI14" t="b">
         <v>1</v>
@@ -2404,21 +2426,19 @@
         <v>1</v>
       </c>
       <c r="AK14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="b">
         <v>0</v>
       </c>
       <c r="AN14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>286.72</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -2434,12 +2454,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2448,94 +2468,96 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>58.19607843137255</v>
+        <v>47.6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>6572000</v>
+        <v>12466000</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
       </c>
       <c r="L15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>12466000</v>
       </c>
       <c r="N15" t="n">
-        <v>6572000</v>
-      </c>
-      <c r="O15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="P15" t="n">
-        <v>2415</v>
+        <v>971</v>
       </c>
       <c r="Q15" t="n">
-        <v>2415</v>
+        <v>971</v>
       </c>
       <c r="R15" t="n">
-        <v>3111476</v>
+        <v>13298768</v>
       </c>
       <c r="S15" t="n">
-        <v>2419</v>
+        <v>1010.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2232.75</v>
+        <v>935.55</v>
       </c>
       <c r="U15" t="n">
-        <v>2226</v>
+        <v>931.8</v>
       </c>
       <c r="V15" t="n">
-        <v>1888.666666666667</v>
+        <v>732.1583333333333</v>
       </c>
       <c r="W15" t="n">
-        <v>89.00412244632889</v>
+        <v>37.25093179725548</v>
       </c>
       <c r="X15" t="n">
-        <v>79.82929541965294</v>
+        <v>49.18605140930046</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.174827026675956</v>
+        <v>-11.93511961204499</v>
       </c>
       <c r="Z15" t="n">
-        <v>16.49176594822497</v>
+        <v>-6.293339870886868</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.05921052631578938</v>
+        <v>0.08370535714285721</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.9795081967213115</v>
+        <v>1.496143958868895</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.03358598470120833</v>
+        <v>-0.005570629326882015</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.552398555824589</v>
+        <v>1.073631856920874</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.5859845405257973</v>
+        <v>-1.079202486247756</v>
       </c>
       <c r="AG15" t="n">
-        <v>54.90196078431373</v>
+        <v>60</v>
       </c>
       <c r="AH15" t="n">
-        <v>72.54901960784314</v>
+        <v>92</v>
       </c>
       <c r="AI15" t="b">
         <v>1</v>
@@ -2544,21 +2566,19 @@
         <v>1</v>
       </c>
       <c r="AK15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="b">
         <v>0</v>
       </c>
       <c r="AN15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1106.94</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
@@ -2574,12 +2594,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2588,94 +2608,96 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>56.82352941176471</v>
+        <v>46.8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>11635000</v>
+        <v>5000</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="K16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="N16" t="n">
-        <v>11635000</v>
-      </c>
-      <c r="O16" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="P16" t="n">
-        <v>102</v>
+        <v>159.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>102</v>
+        <v>159.5</v>
       </c>
       <c r="R16" t="n">
-        <v>54886353</v>
+        <v>53752711</v>
       </c>
       <c r="S16" t="n">
-        <v>103.1800003051758</v>
+        <v>156.8</v>
       </c>
       <c r="T16" t="n">
-        <v>89.76500053405762</v>
+        <v>135.075</v>
       </c>
       <c r="U16" t="n">
-        <v>89.57000045776367</v>
+        <v>132.275</v>
       </c>
       <c r="V16" t="n">
-        <v>73.76500040690104</v>
+        <v>110.6766431172689</v>
       </c>
       <c r="W16" t="n">
-        <v>5.56006487770739</v>
+        <v>10.49012812281038</v>
       </c>
       <c r="X16" t="n">
-        <v>4.901968525670797</v>
+        <v>9.849646254105824</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.6580963520365932</v>
+        <v>0.6404818687045513</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.8867067986986141</v>
+        <v>0.8483992520466259</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.03975536785464606</v>
+        <v>0.5410628019323671</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.7465752968311232</v>
+        <v>0.9687712300394076</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.05304114316235164</v>
+        <v>0.4517868154626279</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.3194656559344007</v>
+        <v>0.5462591280913871</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.3725067990967523</v>
+        <v>-0.09447231262875921</v>
       </c>
       <c r="AG16" t="n">
-        <v>49.01960784313725</v>
+        <v>98</v>
       </c>
       <c r="AH16" t="n">
-        <v>60.78431372549019</v>
+        <v>70</v>
       </c>
       <c r="AI16" t="b">
         <v>1</v>
@@ -2728,16 +2750,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>56.82352941176471</v>
+        <v>46.2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2751,44 +2773,46 @@
         <v>0</v>
       </c>
       <c r="L17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4263000</v>
       </c>
       <c r="N17" t="n">
-        <v>4263000</v>
-      </c>
-      <c r="O17" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
       <c r="P17" t="n">
-        <v>4505</v>
+        <v>4430</v>
       </c>
       <c r="Q17" t="n">
-        <v>4505</v>
+        <v>4430</v>
       </c>
       <c r="R17" t="n">
-        <v>4658394</v>
+        <v>9666613</v>
       </c>
       <c r="S17" t="n">
-        <v>4488</v>
+        <v>4473</v>
       </c>
       <c r="T17" t="n">
-        <v>3928.25</v>
+        <v>3924.5</v>
       </c>
       <c r="U17" t="n">
         <v>3874</v>
       </c>
       <c r="V17" t="n">
-        <v>2620.916666666667</v>
+        <v>2619.666666666667</v>
       </c>
       <c r="W17" t="n">
-        <v>338.4446936886106</v>
+        <v>330.1113603552781</v>
       </c>
       <c r="X17" t="n">
-        <v>348.2664287747666</v>
+        <v>346.5997621081001</v>
       </c>
       <c r="Y17" t="n">
-        <v>-9.821735086155968</v>
+        <v>-16.48840175282203</v>
       </c>
       <c r="Z17" t="n">
         <v>9.93446014543548</v>
@@ -2797,25 +2821,25 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.317251461988304</v>
+        <v>0.2953216374269005</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.705705705705706</v>
+        <v>1.660660660660661</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.2244549509713063</v>
+        <v>0.2060456509571613</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.278596064808983</v>
+        <v>1.23814855871264</v>
       </c>
       <c r="AF17" t="n">
-        <v>-1.054141113837677</v>
+        <v>-1.032102907755479</v>
       </c>
       <c r="AG17" t="n">
-        <v>88.23529411764706</v>
+        <v>88</v>
       </c>
       <c r="AH17" t="n">
-        <v>94.11764705882352</v>
+        <v>94</v>
       </c>
       <c r="AI17" t="b">
         <v>1</v>
@@ -2836,7 +2860,7 @@
         <v>1</v>
       </c>
       <c r="AO17" t="n">
-        <v>4622.13</v>
+        <v>4616.06</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -2852,12 +2876,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2866,94 +2890,96 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>52.90196078431373</v>
+        <v>45.8</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>11960000</v>
+        <v>17948000</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
       </c>
       <c r="L18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>17948000</v>
       </c>
       <c r="N18" t="n">
-        <v>11960000</v>
-      </c>
-      <c r="O18" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
       <c r="P18" t="n">
-        <v>2395</v>
+        <v>593</v>
       </c>
       <c r="Q18" t="n">
-        <v>2395</v>
+        <v>593</v>
       </c>
       <c r="R18" t="n">
-        <v>9355826</v>
+        <v>21154351</v>
       </c>
       <c r="S18" t="n">
-        <v>2382</v>
+        <v>602.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2286.75</v>
+        <v>564.5</v>
       </c>
       <c r="U18" t="n">
-        <v>2282.5</v>
+        <v>561.85</v>
       </c>
       <c r="V18" t="n">
-        <v>2085.991326904297</v>
+        <v>460.5333333333334</v>
       </c>
       <c r="W18" t="n">
-        <v>48.82709458157888</v>
+        <v>22.2538425466297</v>
       </c>
       <c r="X18" t="n">
-        <v>39.33032905010923</v>
+        <v>25.07523173937694</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.496765531469649</v>
+        <v>-2.821389192747237</v>
       </c>
       <c r="Z18" t="n">
-        <v>11.63837193615473</v>
+        <v>-0.0004004860842634628</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.03679653679653683</v>
+        <v>0.0981481481481481</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.327521601158377</v>
+        <v>0.8531249999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.05599997422046088</v>
+        <v>0.008872161678408874</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.09958803973834551</v>
+        <v>0.4306128980519794</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.04358806551788463</v>
+        <v>-0.4217407363735706</v>
       </c>
       <c r="AG18" t="n">
-        <v>47.05882352941176</v>
+        <v>62</v>
       </c>
       <c r="AH18" t="n">
-        <v>23.52941176470588</v>
+        <v>68</v>
       </c>
       <c r="AI18" t="b">
         <v>1</v>
@@ -2962,21 +2988,19 @@
         <v>1</v>
       </c>
       <c r="AK18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="b">
         <v>0</v>
       </c>
       <c r="AN18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>625.02</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -2992,12 +3016,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3006,94 +3030,96 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>51.72549019607843</v>
+        <v>44.4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>4400000</v>
+        <v>7307000</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>7307000</v>
       </c>
       <c r="N19" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="O19" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
       <c r="P19" t="n">
-        <v>1650</v>
+        <v>293</v>
       </c>
       <c r="Q19" t="n">
-        <v>1650</v>
+        <v>293</v>
       </c>
       <c r="R19" t="n">
-        <v>1549232</v>
+        <v>110201540</v>
       </c>
       <c r="S19" t="n">
-        <v>1666</v>
+        <v>297.2</v>
       </c>
       <c r="T19" t="n">
-        <v>1481.5</v>
+        <v>263</v>
       </c>
       <c r="U19" t="n">
-        <v>1471.25</v>
+        <v>261.025</v>
       </c>
       <c r="V19" t="n">
-        <v>1013.890655517578</v>
+        <v>228.4166666666667</v>
       </c>
       <c r="W19" t="n">
-        <v>103.9800584536943</v>
+        <v>15.4116459304127</v>
       </c>
       <c r="X19" t="n">
-        <v>106.143962024122</v>
+        <v>11.75945331553176</v>
       </c>
       <c r="Y19" t="n">
-        <v>-2.163903570427721</v>
+        <v>3.652192614880946</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.397011361843539</v>
+        <v>5.400278270071549</v>
       </c>
       <c r="AA19" t="b">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.1418685121107266</v>
+        <v>0.155818540433925</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.663430705773743</v>
+        <v>0.3919239904988123</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.04907200109372889</v>
+        <v>0.06654255396418574</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.23632106487702</v>
+        <v>-0.03058811144920814</v>
       </c>
       <c r="AF19" t="n">
-        <v>-2.187249063783291</v>
+        <v>0.09713066541339388</v>
       </c>
       <c r="AG19" t="n">
-        <v>68.62745098039215</v>
+        <v>70</v>
       </c>
       <c r="AH19" t="n">
-        <v>98.0392156862745</v>
+        <v>30</v>
       </c>
       <c r="AI19" t="b">
         <v>1</v>
@@ -3102,19 +3128,21 @@
         <v>1</v>
       </c>
       <c r="AK19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM19" t="b">
         <v>0</v>
       </c>
       <c r="AN19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1676.4</v>
+        <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -3130,12 +3158,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3144,94 +3172,96 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>50.15686274509805</v>
+        <v>44</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>980000</v>
+        <v>6572000</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>6572000</v>
       </c>
       <c r="N20" t="n">
-        <v>980000</v>
-      </c>
-      <c r="O20" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
       <c r="P20" t="n">
-        <v>612</v>
+        <v>2425</v>
       </c>
       <c r="Q20" t="n">
-        <v>612</v>
+        <v>2425</v>
       </c>
       <c r="R20" t="n">
-        <v>8835813</v>
+        <v>7947877</v>
       </c>
       <c r="S20" t="n">
-        <v>626</v>
+        <v>2421</v>
       </c>
       <c r="T20" t="n">
-        <v>516.2</v>
+        <v>2233.25</v>
       </c>
       <c r="U20" t="n">
-        <v>509.05</v>
+        <v>2226</v>
       </c>
       <c r="V20" t="n">
-        <v>374.6666666666667</v>
+        <v>1888.833333333333</v>
       </c>
       <c r="W20" t="n">
-        <v>49.14997683959359</v>
+        <v>90.11523355743975</v>
       </c>
       <c r="X20" t="n">
-        <v>44.70190496681484</v>
+        <v>80.05151764187511</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.448071872778755</v>
+        <v>10.06371591556464</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.739597002919723</v>
+        <v>16.49176594822497</v>
       </c>
       <c r="AA20" t="b">
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.3049040511727079</v>
+        <v>0.06359649122807021</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.632258064516129</v>
+        <v>0.9877049180327868</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.2121075401557102</v>
+        <v>-0.02567949524166901</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.205148423619407</v>
+        <v>0.5651928160847663</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0.9930408834636963</v>
+        <v>-0.5908723113264354</v>
       </c>
       <c r="AG20" t="n">
-        <v>86.27450980392157</v>
+        <v>54</v>
       </c>
       <c r="AH20" t="n">
-        <v>92.15686274509804</v>
+        <v>74</v>
       </c>
       <c r="AI20" t="b">
         <v>1</v>
@@ -3270,12 +3300,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3284,97 +3314,99 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>50.15686274509804</v>
+        <v>43.4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>3734000</v>
+        <v>686000</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
       </c>
       <c r="L21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>686000</v>
       </c>
       <c r="N21" t="n">
-        <v>3734000</v>
-      </c>
-      <c r="O21" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
       <c r="P21" t="n">
-        <v>211.5</v>
+        <v>243.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>211.5</v>
+        <v>243.5</v>
       </c>
       <c r="R21" t="n">
-        <v>2954710</v>
+        <v>1983333</v>
       </c>
       <c r="S21" t="n">
-        <v>215</v>
+        <v>247.5</v>
       </c>
       <c r="T21" t="n">
-        <v>219.85</v>
+        <v>215.95</v>
       </c>
       <c r="U21" t="n">
-        <v>218.425</v>
+        <v>212.775</v>
       </c>
       <c r="V21" t="n">
-        <v>155.4266665140788</v>
+        <v>182.0416666666667</v>
       </c>
       <c r="W21" t="n">
-        <v>3.612432396374942</v>
+        <v>14.94848565817435</v>
       </c>
       <c r="X21" t="n">
-        <v>9.821048146665394</v>
+        <v>15.21080448781498</v>
       </c>
       <c r="Y21" t="n">
-        <v>-6.208615750290452</v>
+        <v>-0.2623188296406358</v>
       </c>
       <c r="Z21" t="n">
-        <v>-6.302955817868215</v>
+        <v>1.378953189258032</v>
       </c>
       <c r="AA21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.1557377049180328</v>
+        <v>0.3527777777777779</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.226315789473684</v>
+        <v>0.6968641114982579</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.06294119390103514</v>
+        <v>0.2635017913080386</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.7992061485769617</v>
+        <v>0.2743520095502374</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.7362649546759266</v>
+        <v>-0.01085021824219878</v>
       </c>
       <c r="AG21" t="n">
-        <v>70.58823529411765</v>
+        <v>92</v>
       </c>
       <c r="AH21" t="n">
-        <v>88.23529411764706</v>
+        <v>54</v>
       </c>
       <c r="AI21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ21" t="b">
         <v>1</v>
@@ -3386,12 +3418,14 @@
         <v>0</v>
       </c>
       <c r="AM21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>246.91</v>
+      </c>
       <c r="AP21" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -3406,12 +3440,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3420,118 +3454,124 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>49.56862745098039</v>
+        <v>42.8</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>10828000</v>
+        <v>980000</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="K22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>980000</v>
       </c>
       <c r="N22" t="n">
-        <v>10828000</v>
-      </c>
-      <c r="O22" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
       <c r="P22" t="n">
-        <v>875</v>
+        <v>565</v>
       </c>
       <c r="Q22" t="n">
-        <v>875</v>
+        <v>565</v>
       </c>
       <c r="R22" t="n">
-        <v>4292146</v>
+        <v>18525941</v>
       </c>
       <c r="S22" t="n">
-        <v>878.8</v>
+        <v>616.6</v>
       </c>
       <c r="T22" t="n">
-        <v>867.7</v>
+        <v>513.85</v>
       </c>
       <c r="U22" t="n">
-        <v>871.3</v>
+        <v>509.05</v>
       </c>
       <c r="V22" t="n">
-        <v>744.1</v>
+        <v>373.8833333333333</v>
       </c>
       <c r="W22" t="n">
-        <v>6.530431260714067</v>
+        <v>43.92775461737119</v>
       </c>
       <c r="X22" t="n">
-        <v>8.785874470547117</v>
+        <v>43.65746052237036</v>
       </c>
       <c r="Y22" t="n">
-        <v>-2.25544320983305</v>
+        <v>0.2702940950008355</v>
       </c>
       <c r="Z22" t="n">
-        <v>-1.186083704858063</v>
+        <v>8.739597002919723</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.07602956705385433</v>
+        <v>0.2046908315565032</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.06855791962175</v>
+        <v>1.43010752688172</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.168826078070852</v>
+        <v>0.115414845086764</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.6414482787250271</v>
+        <v>1.0075954249337</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0.8102743567958791</v>
+        <v>-0.892180579846936</v>
       </c>
       <c r="AG22" t="n">
-        <v>19.6078431372549</v>
+        <v>78</v>
       </c>
       <c r="AH22" t="n">
-        <v>80.3921568627451</v>
+        <v>90</v>
       </c>
       <c r="AI22" t="b">
         <v>1</v>
       </c>
       <c r="AJ22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM22" t="b">
         <v>0</v>
       </c>
       <c r="AN22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>901.25</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>846.3200000000001</v>
+        <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -3542,12 +3582,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3556,94 +3596,96 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>48.19607843137255</v>
+        <v>42.4</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5441000</v>
+        <v>4400000</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
       </c>
       <c r="L23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4400000</v>
       </c>
       <c r="N23" t="n">
-        <v>5441000</v>
-      </c>
-      <c r="O23" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
       <c r="P23" t="n">
-        <v>399</v>
+        <v>1695</v>
       </c>
       <c r="Q23" t="n">
-        <v>399</v>
+        <v>1695</v>
       </c>
       <c r="R23" t="n">
-        <v>25985308</v>
+        <v>3444977</v>
       </c>
       <c r="S23" t="n">
-        <v>385.6</v>
+        <v>1675</v>
       </c>
       <c r="T23" t="n">
-        <v>334.525</v>
+        <v>1483.75</v>
       </c>
       <c r="U23" t="n">
-        <v>331.775</v>
+        <v>1471.25</v>
       </c>
       <c r="V23" t="n">
-        <v>315.3333333333333</v>
+        <v>1014.640655517578</v>
       </c>
       <c r="W23" t="n">
-        <v>21.76888490491933</v>
+        <v>108.9800584536943</v>
       </c>
       <c r="X23" t="n">
-        <v>8.987075980703729</v>
+        <v>107.143962024122</v>
       </c>
       <c r="Y23" t="n">
-        <v>12.7818089242156</v>
+        <v>1.836096429572279</v>
       </c>
       <c r="Z23" t="n">
-        <v>14.0184932770315</v>
+        <v>4.397011361843539</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.1598837209302326</v>
+        <v>0.1730103806228374</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.4148936170212767</v>
+        <v>2.763342452294844</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.06708720991323491</v>
+        <v>0.08373439415309814</v>
       </c>
       <c r="AE23" t="n">
-        <v>-0.01221602387544585</v>
+        <v>2.340830350346824</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.07930323378868076</v>
+        <v>-2.257095956193726</v>
       </c>
       <c r="AG23" t="n">
-        <v>72.54901960784314</v>
+        <v>74</v>
       </c>
       <c r="AH23" t="n">
-        <v>31.37254901960784</v>
+        <v>98</v>
       </c>
       <c r="AI23" t="b">
         <v>1</v>
@@ -3682,12 +3724,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3696,106 +3738,108 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>48</v>
+        <v>40.6</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5191000</v>
+        <v>1642000</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
       </c>
       <c r="L24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1642000</v>
       </c>
       <c r="N24" t="n">
-        <v>5191000</v>
-      </c>
-      <c r="O24" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
       <c r="P24" t="n">
-        <v>2710</v>
+        <v>756</v>
       </c>
       <c r="Q24" t="n">
-        <v>2710</v>
+        <v>756</v>
       </c>
       <c r="R24" t="n">
-        <v>2296862</v>
+        <v>5103442</v>
       </c>
       <c r="S24" t="n">
-        <v>2743</v>
+        <v>816.2</v>
       </c>
       <c r="T24" t="n">
-        <v>2579.5</v>
+        <v>792</v>
       </c>
       <c r="U24" t="n">
-        <v>2564.75</v>
+        <v>784.65</v>
       </c>
       <c r="V24" t="n">
-        <v>2381.416666666667</v>
+        <v>616.7149571736653</v>
       </c>
       <c r="W24" t="n">
-        <v>61.39479007515229</v>
+        <v>23.45758842496923</v>
       </c>
       <c r="X24" t="n">
-        <v>40.54290370469145</v>
+        <v>40.09374975460264</v>
       </c>
       <c r="Y24" t="n">
-        <v>20.85188637046083</v>
+        <v>-16.63616132963341</v>
       </c>
       <c r="Z24" t="n">
-        <v>32.43220069924789</v>
+        <v>-9.68869930629873</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.1221532091097308</v>
+        <v>0.2413793103448276</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.6276276276276276</v>
+        <v>0.5466610092845456</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.02935669809273311</v>
+        <v>0.1521033238750884</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.200517986730905</v>
+        <v>0.1241489073365252</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0.1711612886381719</v>
+        <v>0.02795441653856323</v>
       </c>
       <c r="AG24" t="n">
-        <v>66.66666666666666</v>
+        <v>86</v>
       </c>
       <c r="AH24" t="n">
-        <v>50.98039215686274</v>
+        <v>44</v>
       </c>
       <c r="AI24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="b">
         <v>1</v>
       </c>
       <c r="AK24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="b">
         <v>0</v>
@@ -3803,11 +3847,7 @@
       <c r="AN24" t="b">
         <v>0</v>
       </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
+      <c r="AO24" t="inlineStr"/>
       <c r="AP24" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -3822,12 +3862,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3836,97 +3876,99 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>47.41176470588236</v>
+        <v>40.59999999999999</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>686000</v>
+        <v>3734000</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
       </c>
       <c r="L25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3734000</v>
       </c>
       <c r="N25" t="n">
-        <v>686000</v>
-      </c>
-      <c r="O25" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
       <c r="P25" t="n">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="Q25" t="n">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="R25" t="n">
-        <v>507330</v>
+        <v>6513491</v>
       </c>
       <c r="S25" t="n">
-        <v>248</v>
+        <v>215.1</v>
       </c>
       <c r="T25" t="n">
-        <v>216.075</v>
+        <v>219.875</v>
       </c>
       <c r="U25" t="n">
-        <v>212.775</v>
+        <v>218.425</v>
       </c>
       <c r="V25" t="n">
-        <v>182.0833333333333</v>
+        <v>155.4349998474121</v>
       </c>
       <c r="W25" t="n">
-        <v>15.22626343595209</v>
+        <v>3.667987951930513</v>
       </c>
       <c r="X25" t="n">
-        <v>15.26636004337053</v>
+        <v>9.832159257776508</v>
       </c>
       <c r="Y25" t="n">
-        <v>-0.04009660741844101</v>
+        <v>-6.164171305845995</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.378953189258032</v>
+        <v>-6.302955817868215</v>
       </c>
       <c r="AA25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.1584699453551912</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.7142857142857142</v>
+        <v>1.231578947368421</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.273870155649669</v>
+        <v>0.06919395888545199</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.2871760733889916</v>
+        <v>0.8090668454204004</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.01330591773932266</v>
+        <v>-0.7398728865349484</v>
       </c>
       <c r="AG25" t="n">
-        <v>92.15686274509804</v>
+        <v>72</v>
       </c>
       <c r="AH25" t="n">
-        <v>58.82352941176471</v>
+        <v>86</v>
       </c>
       <c r="AI25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="b">
         <v>1</v>
@@ -3938,14 +3980,12 @@
         <v>0</v>
       </c>
       <c r="AM25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>246.49</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -3960,12 +4000,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3974,118 +4014,124 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>46.82352941176471</v>
+        <v>38.6</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>7769000</v>
+        <v>11635000</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
       </c>
       <c r="L26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>11635000</v>
       </c>
       <c r="N26" t="n">
-        <v>7769000</v>
-      </c>
-      <c r="O26" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
       <c r="P26" t="n">
-        <v>1335</v>
+        <v>99.09999847412109</v>
       </c>
       <c r="Q26" t="n">
-        <v>1335</v>
+        <v>99.09999847412109</v>
       </c>
       <c r="R26" t="n">
-        <v>1645345</v>
+        <v>79546357</v>
       </c>
       <c r="S26" t="n">
-        <v>1328</v>
+        <v>102.6</v>
       </c>
       <c r="T26" t="n">
-        <v>1338.25</v>
+        <v>89.62000045776367</v>
       </c>
       <c r="U26" t="n">
-        <v>1344</v>
+        <v>89.57000045776367</v>
       </c>
       <c r="V26" t="n">
-        <v>1180.333333333333</v>
+        <v>73.71666704813639</v>
       </c>
       <c r="W26" t="n">
-        <v>2.41751793207527</v>
+        <v>5.237842485943048</v>
       </c>
       <c r="X26" t="n">
-        <v>6.688876668809249</v>
+        <v>4.837524047317928</v>
       </c>
       <c r="Y26" t="n">
-        <v>-4.271358736733979</v>
+        <v>0.4003184386251197</v>
       </c>
       <c r="Z26" t="n">
-        <v>-4.612508583835297</v>
+        <v>0.8867067986986141</v>
       </c>
       <c r="AA26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.07931034482758625</v>
+        <v>0.01019368007700638</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.7542706964520367</v>
+        <v>0.6969177377539402</v>
       </c>
       <c r="AD26" t="n">
-        <v>-0.172106855844584</v>
+        <v>-0.07908230639273284</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.3271610555553142</v>
+        <v>0.2744056358059197</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.4992679113998981</v>
+        <v>-0.3534879421986525</v>
       </c>
       <c r="AG26" t="n">
-        <v>17.64705882352941</v>
+        <v>42</v>
       </c>
       <c r="AH26" t="n">
-        <v>62.74509803921568</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="AI26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>1383.06</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1333.42</v>
+        <v>0</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -4096,12 +4142,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4110,94 +4156,96 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>45.84313725490196</v>
+        <v>37.2</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>329000</v>
+        <v>11960000</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="K27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>11960000</v>
       </c>
       <c r="N27" t="n">
-        <v>329000</v>
-      </c>
-      <c r="O27" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
       <c r="P27" t="n">
-        <v>3785</v>
+        <v>2385</v>
       </c>
       <c r="Q27" t="n">
-        <v>3785</v>
+        <v>2385</v>
       </c>
       <c r="R27" t="n">
-        <v>1252412</v>
+        <v>28261827</v>
       </c>
       <c r="S27" t="n">
-        <v>3794</v>
+        <v>2380</v>
       </c>
       <c r="T27" t="n">
-        <v>3380.25</v>
+        <v>2286.25</v>
       </c>
       <c r="U27" t="n">
-        <v>3319.75</v>
+        <v>2282.5</v>
       </c>
       <c r="V27" t="n">
-        <v>2735.043587239583</v>
+        <v>2085.82466023763</v>
       </c>
       <c r="W27" t="n">
-        <v>224.3114577068891</v>
+        <v>47.71598347048257</v>
       </c>
       <c r="X27" t="n">
-        <v>221.3142324465821</v>
+        <v>39.10810682791558</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.997225260307033</v>
+        <v>8.607876642566993</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.02710691230362</v>
+        <v>11.63837193613909</v>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.4699029126213592</v>
+        <v>0.03246753246753253</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.6925253971168674</v>
+        <v>0.321978713470868</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.3771064016043615</v>
+        <v>-0.05680845400220669</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.2654157562201449</v>
+        <v>-0.1005333884771524</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.1116906453842166</v>
+        <v>0.04372493447494574</v>
       </c>
       <c r="AG27" t="n">
-        <v>96.07843137254902</v>
+        <v>48</v>
       </c>
       <c r="AH27" t="n">
-        <v>52.94117647058824</v>
+        <v>24</v>
       </c>
       <c r="AI27" t="b">
         <v>1</v>
@@ -4236,12 +4284,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4250,106 +4298,108 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>45.64705882352941</v>
+        <v>36.6</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1642000</v>
+        <v>5441000</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
       </c>
       <c r="L28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>5441000</v>
       </c>
       <c r="N28" t="n">
-        <v>1642000</v>
-      </c>
-      <c r="O28" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
       <c r="P28" t="n">
-        <v>747</v>
+        <v>404</v>
       </c>
       <c r="Q28" t="n">
-        <v>747</v>
+        <v>404</v>
       </c>
       <c r="R28" t="n">
-        <v>2937461</v>
+        <v>73484154</v>
       </c>
       <c r="S28" t="n">
-        <v>814.4</v>
+        <v>386.6</v>
       </c>
       <c r="T28" t="n">
-        <v>791.55</v>
+        <v>334.775</v>
       </c>
       <c r="U28" t="n">
-        <v>784.65</v>
+        <v>331.775</v>
       </c>
       <c r="V28" t="n">
-        <v>616.5649571736653</v>
+        <v>315.4166666666667</v>
       </c>
       <c r="W28" t="n">
-        <v>22.45758842496923</v>
+        <v>22.32444046047488</v>
       </c>
       <c r="X28" t="n">
-        <v>39.89374975460264</v>
+        <v>9.098187091814838</v>
       </c>
       <c r="Y28" t="n">
-        <v>-17.43616132963341</v>
+        <v>13.22625336866004</v>
       </c>
       <c r="Z28" t="n">
-        <v>-9.68869930629873</v>
+        <v>14.0184932770315</v>
       </c>
       <c r="AA28" t="b">
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.2266009852216748</v>
+        <v>0.1744186046511629</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.5282483782216345</v>
+        <v>0.4326241134751774</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.1338044742046771</v>
+        <v>0.08514261818142366</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.101138737324912</v>
+        <v>0.01011201152715691</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.03266573687976515</v>
+        <v>0.07503060665426675</v>
       </c>
       <c r="AG28" t="n">
-        <v>82.35294117647058</v>
+        <v>76</v>
       </c>
       <c r="AH28" t="n">
-        <v>43.13725490196079</v>
+        <v>34</v>
       </c>
       <c r="AI28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ28" t="b">
         <v>1</v>
       </c>
       <c r="AK28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM28" t="b">
         <v>0</v>
@@ -4357,7 +4407,11 @@
       <c r="AN28" t="b">
         <v>0</v>
       </c>
-      <c r="AO28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
       <c r="AP28" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -4372,12 +4426,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4386,94 +4440,96 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>42.70588235294117</v>
+        <v>35.2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1000</v>
+        <v>5191000</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
       </c>
       <c r="L29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>5191000</v>
       </c>
       <c r="N29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O29" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
       <c r="P29" t="n">
-        <v>881</v>
+        <v>2710</v>
       </c>
       <c r="Q29" t="n">
-        <v>881</v>
+        <v>2710</v>
       </c>
       <c r="R29" t="n">
-        <v>2650416</v>
+        <v>4410184</v>
       </c>
       <c r="S29" t="n">
-        <v>866</v>
+        <v>2743</v>
       </c>
       <c r="T29" t="n">
-        <v>718.9</v>
+        <v>2579.5</v>
       </c>
       <c r="U29" t="n">
-        <v>706.8</v>
+        <v>2564.75</v>
       </c>
       <c r="V29" t="n">
-        <v>627.5666666666667</v>
+        <v>2381.416666666667</v>
       </c>
       <c r="W29" t="n">
-        <v>67.46716106186238</v>
+        <v>61.39479007515229</v>
       </c>
       <c r="X29" t="n">
-        <v>43.10667760160244</v>
+        <v>40.54290370469145</v>
       </c>
       <c r="Y29" t="n">
-        <v>24.36048346025994</v>
+        <v>20.85188637046083</v>
       </c>
       <c r="Z29" t="n">
-        <v>29.73688701388987</v>
+        <v>32.43220069924789</v>
       </c>
       <c r="AA29" t="b">
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.3787167449139279</v>
+        <v>0.1221532091097308</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.7040618955512572</v>
+        <v>0.6276276276276276</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.2859202338969302</v>
+        <v>0.0328772226399916</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.2769522546545347</v>
+        <v>0.2051155256796071</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.008967979242395563</v>
+        <v>-0.1722383030396155</v>
       </c>
       <c r="AG29" t="n">
-        <v>94.11764705882352</v>
+        <v>66</v>
       </c>
       <c r="AH29" t="n">
-        <v>54.90196078431373</v>
+        <v>50</v>
       </c>
       <c r="AI29" t="b">
         <v>1</v>
@@ -4512,12 +4568,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4526,94 +4582,96 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>41.33333333333334</v>
+        <v>34.99999999999999</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Heavy Sell</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2437000</v>
+        <v>161000</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
       </c>
       <c r="L30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>329000</v>
       </c>
       <c r="N30" t="n">
-        <v>2437000</v>
-      </c>
-      <c r="O30" t="inlineStr"/>
+        <v>-168000</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-0.5106382978723404</v>
+      </c>
       <c r="P30" t="n">
-        <v>5430</v>
+        <v>3825</v>
       </c>
       <c r="Q30" t="n">
-        <v>5430</v>
+        <v>3825</v>
       </c>
       <c r="R30" t="n">
-        <v>528147</v>
+        <v>2583515</v>
       </c>
       <c r="S30" t="n">
-        <v>5493</v>
+        <v>3802</v>
       </c>
       <c r="T30" t="n">
-        <v>5330</v>
+        <v>3382.25</v>
       </c>
       <c r="U30" t="n">
-        <v>5302.5</v>
+        <v>3319.75</v>
       </c>
       <c r="V30" t="n">
-        <v>4444.5</v>
+        <v>2735.71025390625</v>
       </c>
       <c r="W30" t="n">
-        <v>125.8931677857754</v>
+        <v>228.7559021513334</v>
       </c>
       <c r="X30" t="n">
-        <v>137.2574909638897</v>
+        <v>222.2031213354709</v>
       </c>
       <c r="Y30" t="n">
-        <v>-11.36432317811432</v>
+        <v>6.552780815862519</v>
       </c>
       <c r="Z30" t="n">
-        <v>-2.235203542517638</v>
+        <v>21.02710691230362</v>
       </c>
       <c r="AA30" t="b">
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.1127049180327868</v>
+        <v>0.4854368932038835</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.3816793893129771</v>
+        <v>0.7104120591735847</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.01990840701578911</v>
+        <v>0.3961609067341443</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.04543025158374547</v>
+        <v>0.2878999572255643</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.06533865859953458</v>
+        <v>0.10826094950858</v>
       </c>
       <c r="AG30" t="n">
-        <v>64.70588235294117</v>
+        <v>96</v>
       </c>
       <c r="AH30" t="n">
-        <v>29.41176470588236</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AI30" t="b">
         <v>1</v>
@@ -4622,19 +4680,21 @@
         <v>1</v>
       </c>
       <c r="AK30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM30" t="b">
         <v>0</v>
       </c>
       <c r="AN30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>5560.32</v>
+        <v>0</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
@@ -4650,12 +4710,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4664,97 +4724,99 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>40.74509803921568</v>
+        <v>33.6</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>6231000</v>
+        <v>10828000</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>10828000</v>
       </c>
       <c r="N31" t="n">
-        <v>6231000</v>
-      </c>
-      <c r="O31" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
       <c r="P31" t="n">
-        <v>2480</v>
+        <v>878</v>
       </c>
       <c r="Q31" t="n">
-        <v>2480</v>
+        <v>878</v>
       </c>
       <c r="R31" t="n">
-        <v>805114</v>
+        <v>8784013</v>
       </c>
       <c r="S31" t="n">
-        <v>2486</v>
+        <v>879.4</v>
       </c>
       <c r="T31" t="n">
-        <v>2497</v>
+        <v>867.85</v>
       </c>
       <c r="U31" t="n">
-        <v>2501</v>
+        <v>871.3</v>
       </c>
       <c r="V31" t="n">
-        <v>2069.916666666667</v>
+        <v>744.15</v>
       </c>
       <c r="W31" t="n">
-        <v>26.25623328430947</v>
+        <v>6.863764594047325</v>
       </c>
       <c r="X31" t="n">
-        <v>44.58460080798401</v>
+        <v>8.85254113721377</v>
       </c>
       <c r="Y31" t="n">
-        <v>-18.32836752367454</v>
+        <v>-1.988776543166445</v>
       </c>
       <c r="Z31" t="n">
-        <v>-16.6073198054698</v>
+        <v>-1.186083704858063</v>
       </c>
       <c r="AA31" t="b">
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.03125</v>
+        <v>-0.07286166842661035</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.7971014492753623</v>
+        <v>1.07565011820331</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.1240465110169977</v>
+        <v>-0.1621376548963496</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.3699918083786398</v>
+        <v>0.6531380162552893</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.4940383193956375</v>
+        <v>-0.8152756711516389</v>
       </c>
       <c r="AG31" t="n">
-        <v>33.33333333333333</v>
+        <v>18</v>
       </c>
       <c r="AH31" t="n">
-        <v>66.66666666666666</v>
+        <v>78</v>
       </c>
       <c r="AI31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ31" t="b">
         <v>0</v>
@@ -4772,10 +4834,10 @@
         <v>1</v>
       </c>
       <c r="AO31" t="n">
-        <v>2688.32</v>
+        <v>900.83</v>
       </c>
       <c r="AP31" t="n">
-        <v>2392.89</v>
+        <v>843.3200000000001</v>
       </c>
     </row>
     <row r="32">
@@ -4786,12 +4848,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4800,97 +4862,99 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>40.15686274509804</v>
+        <v>31.6</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>2167000</v>
+        <v>329000</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
       </c>
       <c r="L32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>329000</v>
       </c>
       <c r="N32" t="n">
-        <v>2167000</v>
-      </c>
-      <c r="O32" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
       <c r="P32" t="n">
-        <v>1390</v>
+        <v>265.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>1390</v>
+        <v>265.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1130833</v>
+        <v>39365317</v>
       </c>
       <c r="S32" t="n">
-        <v>1397</v>
+        <v>272.6750366210937</v>
       </c>
       <c r="T32" t="n">
-        <v>1408</v>
+        <v>261.4058555603027</v>
       </c>
       <c r="U32" t="n">
-        <v>1403</v>
+        <v>260.481990814209</v>
       </c>
       <c r="V32" t="n">
-        <v>1125.983333333333</v>
+        <v>248.2858322143555</v>
       </c>
       <c r="W32" t="n">
-        <v>23.59139915095352</v>
+        <v>4.092125816529006</v>
       </c>
       <c r="X32" t="n">
-        <v>32.62905007202382</v>
+        <v>5.715582626232131</v>
       </c>
       <c r="Y32" t="n">
-        <v>-9.037650921070295</v>
+        <v>-1.623456809703126</v>
       </c>
       <c r="Z32" t="n">
-        <v>-7.687376230837643</v>
+        <v>-0.8454073717983484</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.07751937984496116</v>
+        <v>0.07479998616334171</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.5958668197474168</v>
+        <v>0.4653694018060288</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.01527713117203655</v>
+        <v>-0.01447600030639751</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.1687571788506943</v>
+        <v>0.04285729985800835</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.1840343100227309</v>
+        <v>-0.05733330016440585</v>
       </c>
       <c r="AG32" t="n">
-        <v>58.82352941176471</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AH32" t="n">
-        <v>47.05882352941176</v>
+        <v>38</v>
       </c>
       <c r="AI32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ32" t="b">
         <v>1</v>
@@ -4908,7 +4972,7 @@
         <v>1</v>
       </c>
       <c r="AO32" t="n">
-        <v>1492.86</v>
+        <v>284.08</v>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
@@ -4924,12 +4988,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4938,100 +5002,102 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>39.56862745098039</v>
+        <v>30.8</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>4486000</v>
+        <v>422000</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
       </c>
       <c r="L33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>422000</v>
       </c>
       <c r="N33" t="n">
-        <v>4486000</v>
-      </c>
-      <c r="O33" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
       <c r="P33" t="n">
-        <v>4785</v>
+        <v>18265</v>
       </c>
       <c r="Q33" t="n">
-        <v>4785</v>
+        <v>18265</v>
       </c>
       <c r="R33" t="n">
-        <v>565532</v>
+        <v>165817</v>
       </c>
       <c r="S33" t="n">
-        <v>4933</v>
+        <v>18358</v>
       </c>
       <c r="T33" t="n">
-        <v>4897.75</v>
+        <v>17514.25</v>
       </c>
       <c r="U33" t="n">
-        <v>4906.5</v>
+        <v>17495.5</v>
       </c>
       <c r="V33" t="n">
-        <v>3932.916666666667</v>
+        <v>14697.41666666667</v>
       </c>
       <c r="W33" t="n">
-        <v>55.18755304886417</v>
+        <v>412.0441931708956</v>
       </c>
       <c r="X33" t="n">
-        <v>133.8110789380552</v>
+        <v>428.1303461898221</v>
       </c>
       <c r="Y33" t="n">
-        <v>-78.62352588919106</v>
+        <v>-16.08615301892655</v>
       </c>
       <c r="Z33" t="n">
-        <v>-67.0610085410446</v>
+        <v>-4.541236302445384</v>
       </c>
       <c r="AA33" t="b">
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>-0.03528225806451613</v>
+        <v>0.02096143096702074</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.2</v>
+        <v>0.9745945945945946</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.1280787690815138</v>
+        <v>-0.06831455550271848</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.7728903591032776</v>
+        <v>0.5520824926465742</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.9009691281847915</v>
+        <v>-0.6203970481492926</v>
       </c>
       <c r="AG33" t="n">
-        <v>31.37254901960784</v>
+        <v>44</v>
       </c>
       <c r="AH33" t="n">
-        <v>84.31372549019608</v>
+        <v>72</v>
       </c>
       <c r="AI33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK33" t="b">
         <v>0</v>
@@ -5043,13 +5109,15 @@
         <v>0</v>
       </c>
       <c r="AN33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO33" t="n">
-        <v>5675.01</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>4868.68</v>
+        <v>18447.65</v>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -5060,12 +5128,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5074,122 +5142,120 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>37.41176470588236</v>
+        <v>30</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>511000</v>
+        <v>1334000</v>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
       </c>
       <c r="L34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1334000</v>
       </c>
       <c r="N34" t="n">
-        <v>511000</v>
-      </c>
-      <c r="O34" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
       <c r="P34" t="n">
-        <v>95.30000305175781</v>
+        <v>1115</v>
       </c>
       <c r="Q34" t="n">
-        <v>95.30000305175781</v>
+        <v>1115</v>
       </c>
       <c r="R34" t="n">
-        <v>2539234</v>
+        <v>4254262</v>
       </c>
       <c r="S34" t="n">
-        <v>92.86000061035156</v>
+        <v>1076</v>
       </c>
       <c r="T34" t="n">
-        <v>83.57499961853027</v>
+        <v>1128.5</v>
       </c>
       <c r="U34" t="n">
-        <v>82.80999946594238</v>
+        <v>1129.25</v>
       </c>
       <c r="V34" t="n">
-        <v>81.4733331044515</v>
+        <v>1031.933333333333</v>
       </c>
       <c r="W34" t="n">
-        <v>3.925890996932964</v>
+        <v>-17.73345120218187</v>
       </c>
       <c r="X34" t="n">
-        <v>2.392494780655368</v>
+        <v>-8.526253998019737</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.533396216277596</v>
+        <v>-9.207197204162131</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.539528706158522</v>
+        <v>-15.76878958699825</v>
       </c>
       <c r="AA34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.1912500381469726</v>
+        <v>-0.01327433628318586</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.08789959716621976</v>
+        <v>1.099811676082862</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.0984535271299749</v>
+        <v>-0.1025503227529251</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.3392100437305028</v>
+        <v>0.677299574134842</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.4376635708604777</v>
+        <v>-0.7798498968877671</v>
       </c>
       <c r="AG34" t="n">
-        <v>78.43137254901961</v>
+        <v>38</v>
       </c>
       <c r="AH34" t="n">
-        <v>7.84313725490196</v>
+        <v>82</v>
       </c>
       <c r="AI34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP34" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1219.81</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1084.21</v>
       </c>
     </row>
     <row r="35">
@@ -5200,12 +5266,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5214,94 +5280,96 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>32.90196078431373</v>
+        <v>28.8</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1761000</v>
+        <v>18000</v>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
       </c>
       <c r="L35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="N35" t="n">
-        <v>1761000</v>
-      </c>
-      <c r="O35" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
       <c r="P35" t="n">
-        <v>1985</v>
+        <v>92.59999847412109</v>
       </c>
       <c r="Q35" t="n">
-        <v>1985</v>
+        <v>92.59999847412109</v>
       </c>
       <c r="R35" t="n">
-        <v>678056</v>
+        <v>2789169</v>
       </c>
       <c r="S35" t="n">
-        <v>2062</v>
+        <v>92.7</v>
       </c>
       <c r="T35" t="n">
-        <v>1867.25</v>
+        <v>88.31499938964843</v>
       </c>
       <c r="U35" t="n">
-        <v>1864</v>
+        <v>88.00999946594239</v>
       </c>
       <c r="V35" t="n">
-        <v>1885.5</v>
+        <v>86.77999992370606</v>
       </c>
       <c r="W35" t="n">
-        <v>55.763156836397</v>
+        <v>1.727709144894789</v>
       </c>
       <c r="X35" t="n">
-        <v>15.7715159380667</v>
+        <v>1.217135275608626</v>
       </c>
       <c r="Y35" t="n">
-        <v>39.9916408983303</v>
+        <v>0.510573869286163</v>
       </c>
       <c r="Z35" t="n">
-        <v>56.04366129912638</v>
+        <v>0.7262556831825802</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.03385416666666674</v>
+        <v>0.07052021357365423</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.1921921921921923</v>
+        <v>0.1589486446271065</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.05894234435033097</v>
+        <v>-0.01875577289608499</v>
       </c>
       <c r="AE35" t="n">
-        <v>-0.2349174487045302</v>
+        <v>-0.263563457320914</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.1759751043541993</v>
+        <v>0.244807684424829</v>
       </c>
       <c r="AG35" t="n">
-        <v>45.09803921568628</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="AH35" t="n">
-        <v>19.6078431372549</v>
+        <v>16</v>
       </c>
       <c r="AI35" t="b">
         <v>1</v>
@@ -5340,12 +5408,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5354,106 +5422,108 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>32.70588235294117</v>
+        <v>28.4</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3988000</v>
+        <v>4486000</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
       </c>
       <c r="L36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>4486000</v>
       </c>
       <c r="N36" t="n">
-        <v>3988000</v>
-      </c>
-      <c r="O36" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
       <c r="P36" t="n">
-        <v>98.80000305175781</v>
+        <v>4830</v>
       </c>
       <c r="Q36" t="n">
-        <v>98.80000305175781</v>
+        <v>4830</v>
       </c>
       <c r="R36" t="n">
-        <v>4175488</v>
+        <v>1614762</v>
       </c>
       <c r="S36" t="n">
-        <v>97.90000000000001</v>
+        <v>4942</v>
       </c>
       <c r="T36" t="n">
-        <v>95.42000045776368</v>
+        <v>4900</v>
       </c>
       <c r="U36" t="n">
-        <v>95.48000030517578</v>
+        <v>4906.5</v>
       </c>
       <c r="V36" t="n">
-        <v>97.9416670481364</v>
+        <v>3933.666666666667</v>
       </c>
       <c r="W36" t="n">
-        <v>0.5001845896800461</v>
+        <v>60.18755304886417</v>
       </c>
       <c r="X36" t="n">
-        <v>-0.2211341336594903</v>
+        <v>134.8110789380552</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.7213187233395364</v>
+        <v>-74.62352588919106</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.792692952551374</v>
+        <v>-67.0610085410446</v>
       </c>
       <c r="AA36" t="b">
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0.01199996948242188</v>
+        <v>-0.02620967741935487</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.09050777831943302</v>
+        <v>1.220689655172414</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.1047964804994196</v>
+        <v>-0.1154856638890941</v>
       </c>
       <c r="AE36" t="n">
-        <v>-0.3366018625772895</v>
+        <v>0.7981775532243933</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.2318053820778699</v>
+        <v>-0.9136632171134874</v>
       </c>
       <c r="AG36" t="n">
-        <v>37.25490196078432</v>
+        <v>32</v>
       </c>
       <c r="AH36" t="n">
-        <v>9.803921568627452</v>
+        <v>84</v>
       </c>
       <c r="AI36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="b">
         <v>0</v>
       </c>
       <c r="AK36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="b">
         <v>0</v>
@@ -5461,13 +5531,11 @@
       <c r="AN36" t="b">
         <v>0</v>
       </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+      <c r="AO36" t="n">
+        <v>5670.42</v>
       </c>
       <c r="AP36" t="n">
-        <v>91.94</v>
+        <v>4823.68</v>
       </c>
     </row>
     <row r="37">
@@ -5478,12 +5546,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5492,118 +5560,124 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>32.70588235294117</v>
+        <v>27.6</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1334000</v>
+        <v>1761000</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K37" t="b">
         <v>0</v>
       </c>
       <c r="L37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1761000</v>
       </c>
       <c r="N37" t="n">
-        <v>1334000</v>
-      </c>
-      <c r="O37" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
       <c r="P37" t="n">
-        <v>1090</v>
+        <v>1985</v>
       </c>
       <c r="Q37" t="n">
-        <v>1090</v>
+        <v>1985</v>
       </c>
       <c r="R37" t="n">
-        <v>1182820</v>
+        <v>1188788</v>
       </c>
       <c r="S37" t="n">
-        <v>1071</v>
+        <v>2062</v>
       </c>
       <c r="T37" t="n">
-        <v>1127.25</v>
+        <v>1867.25</v>
       </c>
       <c r="U37" t="n">
-        <v>1129.25</v>
+        <v>1864</v>
       </c>
       <c r="V37" t="n">
-        <v>1031.516666666667</v>
+        <v>1885.5</v>
       </c>
       <c r="W37" t="n">
-        <v>-20.51122897995947</v>
+        <v>55.763156836397</v>
       </c>
       <c r="X37" t="n">
-        <v>-9.081809553575255</v>
+        <v>15.7715159380667</v>
       </c>
       <c r="Y37" t="n">
-        <v>-11.42941942638421</v>
+        <v>39.9916408983303</v>
       </c>
       <c r="Z37" t="n">
-        <v>-15.76878958699825</v>
+        <v>56.04366129912638</v>
       </c>
       <c r="AA37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0.03539823008849563</v>
+        <v>0.03385416666666674</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.052730696798494</v>
+        <v>0.1921921921921923</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.1281947411054933</v>
+        <v>-0.05542181980307248</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.625621055901771</v>
+        <v>-0.2303199097558282</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.7538157970072643</v>
+        <v>0.1748980899527557</v>
       </c>
       <c r="AG37" t="n">
-        <v>29.41176470588236</v>
+        <v>50</v>
       </c>
       <c r="AH37" t="n">
-        <v>76.47058823529412</v>
+        <v>22</v>
       </c>
       <c r="AI37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>1218.62</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1109.21</v>
+        <v>0</v>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -5614,12 +5688,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5628,94 +5702,96 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>31.72549019607843</v>
+        <v>24.4</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>422000</v>
+        <v>5163000</v>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
       </c>
       <c r="L38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>5163000</v>
       </c>
       <c r="N38" t="n">
-        <v>422000</v>
-      </c>
-      <c r="O38" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
       <c r="P38" t="n">
-        <v>18305</v>
+        <v>19.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>18305</v>
+        <v>19.25</v>
       </c>
       <c r="R38" t="n">
-        <v>39027</v>
+        <v>75000381</v>
       </c>
       <c r="S38" t="n">
-        <v>18366</v>
+        <v>19.16000022888183</v>
       </c>
       <c r="T38" t="n">
-        <v>17516.25</v>
+        <v>18.73750019073486</v>
       </c>
       <c r="U38" t="n">
-        <v>17495.5</v>
+        <v>18.71750020980835</v>
       </c>
       <c r="V38" t="n">
-        <v>14698.08333333333</v>
+        <v>19.16250009536743</v>
       </c>
       <c r="W38" t="n">
-        <v>416.4886376153372</v>
+        <v>0.1378757594861106</v>
       </c>
       <c r="X38" t="n">
-        <v>429.0192350787105</v>
+        <v>0.05863068264015032</v>
       </c>
       <c r="Y38" t="n">
-        <v>-12.53059746337328</v>
+        <v>0.07924507684596033</v>
       </c>
       <c r="Z38" t="n">
-        <v>-4.541236302445384</v>
+        <v>0.09247098408578769</v>
       </c>
       <c r="AA38" t="b">
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.02319731693683624</v>
+        <v>0.02122013848463844</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.9789189189189189</v>
+        <v>0.005221952138994457</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.06959919408016146</v>
+        <v>-0.06805584798510078</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.5518092780221964</v>
+        <v>-0.417290149809026</v>
       </c>
       <c r="AF38" t="n">
-        <v>-0.6214084721023578</v>
+        <v>0.3492343018239252</v>
       </c>
       <c r="AG38" t="n">
-        <v>41.17647058823529</v>
+        <v>46</v>
       </c>
       <c r="AH38" t="n">
-        <v>70.58823529411765</v>
+        <v>2</v>
       </c>
       <c r="AI38" t="b">
         <v>1</v>
@@ -5724,19 +5800,21 @@
         <v>1</v>
       </c>
       <c r="AK38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM38" t="b">
         <v>0</v>
       </c>
       <c r="AN38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>18451.44</v>
+        <v>0</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
@@ -5752,12 +5830,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5766,115 +5844,119 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>31.13725490196079</v>
+        <v>23.6</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>329000</v>
+        <v>1741000</v>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="K39" t="b">
         <v>0</v>
       </c>
       <c r="L39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>1741000</v>
       </c>
       <c r="N39" t="n">
-        <v>329000</v>
-      </c>
-      <c r="O39" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
       <c r="P39" t="n">
-        <v>259</v>
+        <v>215.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>259</v>
+        <v>215.5</v>
       </c>
       <c r="R39" t="n">
-        <v>21905116</v>
+        <v>6451261</v>
       </c>
       <c r="S39" t="n">
-        <v>271.3750366210937</v>
+        <v>214.2</v>
       </c>
       <c r="T39" t="n">
-        <v>261.0808555603027</v>
+        <v>208.075</v>
       </c>
       <c r="U39" t="n">
-        <v>260.481990814209</v>
+        <v>208.05</v>
       </c>
       <c r="V39" t="n">
-        <v>248.1774988810221</v>
+        <v>207.4</v>
       </c>
       <c r="W39" t="n">
-        <v>3.369903594306777</v>
+        <v>2.959940842698842</v>
       </c>
       <c r="X39" t="n">
-        <v>5.571138181787686</v>
+        <v>1.837280695022881</v>
       </c>
       <c r="Y39" t="n">
-        <v>-2.201234587480909</v>
+        <v>1.122660147675961</v>
       </c>
       <c r="Z39" t="n">
-        <v>-0.8454073717983484</v>
+        <v>1.554787379003262</v>
       </c>
       <c r="AA39" t="b">
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.04848661550397559</v>
+        <v>0.002325581395348886</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.4294940680518322</v>
+        <v>0.1342105263157896</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.04430989551302211</v>
+        <v>-0.08695040507439034</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.00238442715510967</v>
+        <v>-0.2883015756322309</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0.04669432266813178</v>
+        <v>0.2013511705578406</v>
       </c>
       <c r="AG39" t="n">
-        <v>52.94117647058824</v>
+        <v>40</v>
       </c>
       <c r="AH39" t="n">
-        <v>35.29411764705883</v>
+        <v>12</v>
       </c>
       <c r="AI39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ39" t="b">
         <v>1</v>
       </c>
       <c r="AK39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM39" t="b">
         <v>0</v>
       </c>
       <c r="AN39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>283.86</v>
+        <v>0</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
@@ -5890,12 +5972,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5904,94 +5986,96 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>30.94117647058824</v>
+        <v>22</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2267000</v>
+        <v>3988000</v>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
       </c>
       <c r="L40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3988000</v>
       </c>
       <c r="N40" t="n">
-        <v>2267000</v>
-      </c>
-      <c r="O40" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
       <c r="P40" t="n">
-        <v>3755</v>
+        <v>98.19999694824219</v>
       </c>
       <c r="Q40" t="n">
-        <v>3755</v>
+        <v>98.19999694824219</v>
       </c>
       <c r="R40" t="n">
-        <v>709918</v>
+        <v>9103817</v>
       </c>
       <c r="S40" t="n">
-        <v>3807</v>
+        <v>97.77999877929688</v>
       </c>
       <c r="T40" t="n">
-        <v>3598.5</v>
+        <v>95.39000015258789</v>
       </c>
       <c r="U40" t="n">
-        <v>3604.5</v>
+        <v>95.48000030517578</v>
       </c>
       <c r="V40" t="n">
-        <v>4038.416666666667</v>
+        <v>97.93166694641113</v>
       </c>
       <c r="W40" t="n">
-        <v>-14.0315202950128</v>
+        <v>0.4335172448449924</v>
       </c>
       <c r="X40" t="n">
-        <v>-104.5448283533882</v>
+        <v>-0.234467602626501</v>
       </c>
       <c r="Y40" t="n">
-        <v>90.51330805837543</v>
+        <v>0.6679848474714934</v>
       </c>
       <c r="Z40" t="n">
-        <v>110.9240466277653</v>
+        <v>0.792692952551374</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>-0.03096774193548391</v>
+        <v>-0.01800003051757815</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.1808176100628931</v>
+        <v>0.0838851942838823</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.1237642529524816</v>
+        <v>-0.1072760169873174</v>
       </c>
       <c r="AE40" t="n">
-        <v>-0.2462920308338294</v>
+        <v>-0.3386269076641382</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.1225277778813478</v>
+        <v>0.2313508906768208</v>
       </c>
       <c r="AG40" t="n">
-        <v>35.29411764705883</v>
+        <v>36</v>
       </c>
       <c r="AH40" t="n">
-        <v>17.64705882352941</v>
+        <v>8</v>
       </c>
       <c r="AI40" t="b">
         <v>1</v>
@@ -6017,7 +6101,7 @@
         </is>
       </c>
       <c r="AP40" t="n">
-        <v>3485.26</v>
+        <v>92.54000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -6028,12 +6112,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6042,100 +6126,102 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>30.15686274509804</v>
+        <v>21.2</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1741000</v>
+        <v>2267000</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
       </c>
       <c r="L41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>2267000</v>
       </c>
       <c r="N41" t="n">
-        <v>1741000</v>
-      </c>
-      <c r="O41" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
       <c r="P41" t="n">
-        <v>216</v>
+        <v>3730</v>
       </c>
       <c r="Q41" t="n">
-        <v>216</v>
+        <v>3730</v>
       </c>
       <c r="R41" t="n">
-        <v>3918660</v>
+        <v>1439872</v>
       </c>
       <c r="S41" t="n">
-        <v>214.3</v>
+        <v>3802</v>
       </c>
       <c r="T41" t="n">
-        <v>208.1</v>
+        <v>3597.25</v>
       </c>
       <c r="U41" t="n">
-        <v>208.05</v>
+        <v>3604.5</v>
       </c>
       <c r="V41" t="n">
-        <v>207.4083333333333</v>
+        <v>4038</v>
       </c>
       <c r="W41" t="n">
-        <v>3.015496398254413</v>
+        <v>-16.80929807279063</v>
       </c>
       <c r="X41" t="n">
-        <v>1.848391806133995</v>
+        <v>-105.1003839089438</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.167104592120418</v>
+        <v>88.29108583615317</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.554787379003262</v>
+        <v>110.9240466277653</v>
       </c>
       <c r="AA41" t="b">
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.004651162790697771</v>
+        <v>-0.03741935483870973</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.1368421052631579</v>
+        <v>0.1729559748427674</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.08814534822629994</v>
+        <v>-0.1266953413084489</v>
       </c>
       <c r="AE41" t="n">
-        <v>-0.2902675356335647</v>
+        <v>-0.2495561271052531</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.2021221874072647</v>
+        <v>0.1228607857968042</v>
       </c>
       <c r="AG41" t="n">
-        <v>39.21568627450981</v>
+        <v>30</v>
       </c>
       <c r="AH41" t="n">
-        <v>13.72549019607843</v>
+        <v>18</v>
       </c>
       <c r="AI41" t="b">
         <v>1</v>
       </c>
       <c r="AJ41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="b">
         <v>1</v>
@@ -6154,10 +6240,8 @@
           <t>Already &gt; 0</t>
         </is>
       </c>
-      <c r="AP41" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AP41" t="n">
+        <v>3510.26</v>
       </c>
     </row>
     <row r="42">
@@ -6168,12 +6252,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6182,100 +6266,102 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>28.98039215686275</v>
+        <v>20.2</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>18000</v>
+        <v>3645000</v>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
       </c>
       <c r="L42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3645000</v>
       </c>
       <c r="N42" t="n">
-        <v>18000</v>
-      </c>
-      <c r="O42" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
       <c r="P42" t="n">
-        <v>93</v>
+        <v>322</v>
       </c>
       <c r="Q42" t="n">
-        <v>93</v>
+        <v>322</v>
       </c>
       <c r="R42" t="n">
-        <v>1417113</v>
+        <v>39580269</v>
       </c>
       <c r="S42" t="n">
-        <v>92.78000030517578</v>
+        <v>319.5</v>
       </c>
       <c r="T42" t="n">
-        <v>88.33499946594239</v>
+        <v>307.2</v>
       </c>
       <c r="U42" t="n">
-        <v>88.00999946594239</v>
+        <v>308.05</v>
       </c>
       <c r="V42" t="n">
-        <v>86.78666661580404</v>
+        <v>296.925</v>
       </c>
       <c r="W42" t="n">
-        <v>1.772153758881345</v>
+        <v>4.983222282475822</v>
       </c>
       <c r="X42" t="n">
-        <v>1.226024198405937</v>
+        <v>4.229453276554539</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.5461295604754079</v>
+        <v>0.7537690059212832</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.7262556831825802</v>
+        <v>0.7909858073156304</v>
       </c>
       <c r="AA42" t="b">
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.07514450867052025</v>
+        <v>-0.05014749262536877</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.1639549214511355</v>
+        <v>0.1838235294117647</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.01765200234647746</v>
+        <v>-0.139423479095108</v>
       </c>
       <c r="AE42" t="n">
-        <v>-0.263154719445587</v>
+        <v>-0.2386885725362557</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.2455027170991095</v>
+        <v>0.09926509344114776</v>
       </c>
       <c r="AG42" t="n">
-        <v>56.86274509803921</v>
+        <v>26</v>
       </c>
       <c r="AH42" t="n">
-        <v>15.68627450980392</v>
+        <v>20</v>
       </c>
       <c r="AI42" t="b">
         <v>1</v>
       </c>
       <c r="AJ42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="b">
         <v>1</v>
@@ -6294,10 +6380,8 @@
           <t>Already &gt; 0</t>
         </is>
       </c>
-      <c r="AP42" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AP42" t="n">
+        <v>295.42</v>
       </c>
     </row>
     <row r="43">
@@ -6308,12 +6392,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6322,94 +6406,96 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>27.6078431372549</v>
+        <v>19.2</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>3528000</v>
+        <v>167000</v>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="K43" t="b">
         <v>0</v>
       </c>
       <c r="L43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>167000</v>
       </c>
       <c r="N43" t="n">
-        <v>3528000</v>
-      </c>
-      <c r="O43" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
       <c r="P43" t="n">
-        <v>365.5</v>
+        <v>4400</v>
       </c>
       <c r="Q43" t="n">
-        <v>365.5</v>
+        <v>4400</v>
       </c>
       <c r="R43" t="n">
-        <v>1159941</v>
+        <v>1419538</v>
       </c>
       <c r="S43" t="n">
-        <v>375.5</v>
+        <v>4573</v>
       </c>
       <c r="T43" t="n">
-        <v>381.675</v>
+        <v>4946.25</v>
       </c>
       <c r="U43" t="n">
-        <v>383.75</v>
+        <v>4998.75</v>
       </c>
       <c r="V43" t="n">
-        <v>350.65</v>
+        <v>3720.583333333333</v>
       </c>
       <c r="W43" t="n">
-        <v>-3.27489833878434</v>
+        <v>-61.33721264956966</v>
       </c>
       <c r="X43" t="n">
-        <v>-0.9999158968686888</v>
+        <v>61.99793043341521</v>
       </c>
       <c r="Y43" t="n">
-        <v>-2.274982441915651</v>
+        <v>-123.3351430829849</v>
       </c>
       <c r="Z43" t="n">
-        <v>-1.595170124141301</v>
+        <v>-119.2039387840907</v>
       </c>
       <c r="AA43" t="b">
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>-0.101965601965602</v>
+        <v>-0.1926605504587156</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.5010266940451746</v>
+        <v>1.009132420091324</v>
       </c>
       <c r="AD43" t="n">
-        <v>-0.1947621129825997</v>
+        <v>-0.2819365369284548</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.07391705314845209</v>
+        <v>0.5866203181433036</v>
       </c>
       <c r="AF43" t="n">
-        <v>-0.2686791661310518</v>
+        <v>-0.8685568550717584</v>
       </c>
       <c r="AG43" t="n">
-        <v>13.72549019607843</v>
+        <v>4</v>
       </c>
       <c r="AH43" t="n">
-        <v>41.17647058823529</v>
+        <v>76</v>
       </c>
       <c r="AI43" t="b">
         <v>0</v>
@@ -6427,13 +6513,11 @@
         <v>0</v>
       </c>
       <c r="AN43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>391.82</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO43" t="inlineStr"/>
       <c r="AP43" t="n">
-        <v>405.03</v>
+        <v>5785</v>
       </c>
     </row>
     <row r="44">
@@ -6444,12 +6528,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6458,94 +6542,96 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>25.25490196078432</v>
+        <v>18.8</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>4703848</v>
+        <v>3528000</v>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
       </c>
       <c r="L44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3528000</v>
       </c>
       <c r="N44" t="n">
-        <v>4703848</v>
-      </c>
-      <c r="O44" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
       <c r="P44" t="n">
-        <v>2145</v>
+        <v>366</v>
       </c>
       <c r="Q44" t="n">
-        <v>2145</v>
+        <v>366</v>
       </c>
       <c r="R44" t="n">
-        <v>1515838</v>
+        <v>1876573</v>
       </c>
       <c r="S44" t="n">
-        <v>2170</v>
+        <v>375.6</v>
       </c>
       <c r="T44" t="n">
-        <v>2268.25</v>
+        <v>381.7</v>
       </c>
       <c r="U44" t="n">
-        <v>2300</v>
+        <v>383.75</v>
       </c>
       <c r="V44" t="n">
-        <v>2198.833333333333</v>
+        <v>350.6583333333334</v>
       </c>
       <c r="W44" t="n">
-        <v>-52.16622063753221</v>
+        <v>-3.219342783228853</v>
       </c>
       <c r="X44" t="n">
-        <v>-70.31363211633999</v>
+        <v>-0.9888047857575915</v>
       </c>
       <c r="Y44" t="n">
-        <v>18.14741147880778</v>
+        <v>-2.230537997471262</v>
       </c>
       <c r="Z44" t="n">
-        <v>23.01011303055475</v>
+        <v>-1.595170124141301</v>
       </c>
       <c r="AA44" t="b">
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.2284172661870504</v>
+        <v>-0.1007371007371007</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.3448275862068966</v>
+        <v>0.5030800821355237</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.3212137772040481</v>
+        <v>-0.19001308720684</v>
       </c>
       <c r="AE44" t="n">
-        <v>-0.08228205468982597</v>
+        <v>0.08056798018750322</v>
       </c>
       <c r="AF44" t="n">
-        <v>-0.2389317225142221</v>
+        <v>-0.2705810673943432</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.96078431372549</v>
+        <v>14</v>
       </c>
       <c r="AH44" t="n">
-        <v>25.49019607843137</v>
+        <v>42</v>
       </c>
       <c r="AI44" t="b">
         <v>0</v>
@@ -6554,24 +6640,22 @@
         <v>0</v>
       </c>
       <c r="AK44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="b">
         <v>0</v>
       </c>
       <c r="AN44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>391.62</v>
       </c>
       <c r="AP44" t="n">
-        <v>2879.74</v>
+        <v>404.53</v>
       </c>
     </row>
     <row r="45">
@@ -6582,12 +6666,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6596,94 +6680,96 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>21.52941176470588</v>
+        <v>18.8</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>930000</v>
+        <v>442000</v>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
       </c>
       <c r="L45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>442000</v>
       </c>
       <c r="N45" t="n">
-        <v>930000</v>
-      </c>
-      <c r="O45" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
       <c r="P45" t="n">
-        <v>3500</v>
+        <v>8650</v>
       </c>
       <c r="Q45" t="n">
-        <v>3500</v>
+        <v>8650</v>
       </c>
       <c r="R45" t="n">
-        <v>880821</v>
+        <v>343102</v>
       </c>
       <c r="S45" t="n">
-        <v>3291</v>
+        <v>8464</v>
       </c>
       <c r="T45" t="n">
-        <v>3500.5</v>
+        <v>9293.75</v>
       </c>
       <c r="U45" t="n">
-        <v>3512</v>
+        <v>9354.25</v>
       </c>
       <c r="V45" t="n">
-        <v>3547.916666666667</v>
+        <v>8757.083333333334</v>
       </c>
       <c r="W45" t="n">
-        <v>-70.77865993103933</v>
+        <v>-326.566067104417</v>
       </c>
       <c r="X45" t="n">
-        <v>-88.55682287102097</v>
+        <v>-236.7319042826581</v>
       </c>
       <c r="Y45" t="n">
-        <v>17.77816293998164</v>
+        <v>-89.83416282175887</v>
       </c>
       <c r="Z45" t="n">
-        <v>-11.00101547515878</v>
+        <v>-146.0356984286772</v>
       </c>
       <c r="AA45" t="b">
         <v>1</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.06166219839142095</v>
+        <v>-0.1227180527383367</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.05105105105105112</v>
+        <v>0.7369477911646587</v>
       </c>
       <c r="AD45" t="n">
-        <v>-0.1544587094084187</v>
+        <v>-0.2119940392080759</v>
       </c>
       <c r="AE45" t="n">
-        <v>-0.3760585898456714</v>
+        <v>0.3144356892166382</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.2215998804372528</v>
+        <v>-0.5264297284247141</v>
       </c>
       <c r="AG45" t="n">
-        <v>21.56862745098039</v>
+        <v>8</v>
       </c>
       <c r="AH45" t="n">
-        <v>3.92156862745098</v>
+        <v>60</v>
       </c>
       <c r="AI45" t="b">
         <v>0</v>
@@ -6692,24 +6778,22 @@
         <v>0</v>
       </c>
       <c r="AK45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="b">
         <v>1</v>
       </c>
       <c r="AN45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>9670.700000000001</v>
       </c>
       <c r="AP45" t="n">
-        <v>3580.53</v>
+        <v>10307.63</v>
       </c>
     </row>
     <row r="46">
@@ -6720,12 +6804,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6734,94 +6818,96 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>20.74509803921569</v>
+        <v>18.8</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>442000</v>
+        <v>1000</v>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
       </c>
       <c r="L46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N46" t="n">
-        <v>442000</v>
-      </c>
-      <c r="O46" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
       <c r="P46" t="n">
-        <v>8510</v>
+        <v>4340</v>
       </c>
       <c r="Q46" t="n">
-        <v>8510</v>
+        <v>4340</v>
       </c>
       <c r="R46" t="n">
-        <v>120036</v>
+        <v>1467560</v>
       </c>
       <c r="S46" t="n">
-        <v>8436</v>
+        <v>4556</v>
       </c>
       <c r="T46" t="n">
-        <v>9286.75</v>
+        <v>4716.5</v>
       </c>
       <c r="U46" t="n">
-        <v>9354.25</v>
+        <v>4739.25</v>
       </c>
       <c r="V46" t="n">
-        <v>8754.75</v>
+        <v>3860</v>
       </c>
       <c r="W46" t="n">
-        <v>-342.1216226599718</v>
+        <v>-7.612221611314453</v>
       </c>
       <c r="X46" t="n">
-        <v>-239.8430153937691</v>
+        <v>59.63574959811844</v>
       </c>
       <c r="Y46" t="n">
-        <v>-102.2786072662027</v>
+        <v>-67.2479712094329</v>
       </c>
       <c r="Z46" t="n">
-        <v>-146.0356984286772</v>
+        <v>-51.06745263124361</v>
       </c>
       <c r="AA46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0.1369168356997972</v>
+        <v>-0.0948905109489051</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.7088353413654618</v>
+        <v>0.4490818030050083</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.2297133467167949</v>
+        <v>-0.1841664974186443</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.2817257004687392</v>
+        <v>0.02656970105698786</v>
       </c>
       <c r="AF46" t="n">
-        <v>-0.5114390471855341</v>
+        <v>-0.2107361984756322</v>
       </c>
       <c r="AG46" t="n">
-        <v>7.84313725490196</v>
+        <v>16</v>
       </c>
       <c r="AH46" t="n">
-        <v>56.86274509803921</v>
+        <v>36</v>
       </c>
       <c r="AI46" t="b">
         <v>0</v>
@@ -6836,16 +6922,16 @@
         <v>0</v>
       </c>
       <c r="AM46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
-        <v>9667.360000000001</v>
+        <v>5103.84</v>
       </c>
       <c r="AP46" t="n">
-        <v>10447.63</v>
+        <v>5286.32</v>
       </c>
     </row>
     <row r="47">
@@ -6856,12 +6942,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6870,94 +6956,96 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>20.54901960784314</v>
+        <v>18.2</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>852000</v>
+        <v>107000</v>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="K47" t="b">
         <v>0</v>
       </c>
       <c r="L47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>107000</v>
       </c>
       <c r="N47" t="n">
-        <v>852000</v>
-      </c>
-      <c r="O47" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
       <c r="P47" t="n">
-        <v>2400</v>
+        <v>104</v>
       </c>
       <c r="Q47" t="n">
-        <v>2400</v>
+        <v>104</v>
       </c>
       <c r="R47" t="n">
-        <v>659668</v>
+        <v>13273338</v>
       </c>
       <c r="S47" t="n">
-        <v>2582</v>
+        <v>107</v>
       </c>
       <c r="T47" t="n">
-        <v>2552.75</v>
+        <v>105.625</v>
       </c>
       <c r="U47" t="n">
-        <v>2575.25</v>
+        <v>105.925</v>
       </c>
       <c r="V47" t="n">
-        <v>2356</v>
+        <v>107.906666692098</v>
       </c>
       <c r="W47" t="n">
-        <v>-2.608617156733089</v>
+        <v>-0.2448423497634451</v>
       </c>
       <c r="X47" t="n">
-        <v>11.03284908407442</v>
+        <v>-0.5442127776156785</v>
       </c>
       <c r="Y47" t="n">
-        <v>-13.64146624080751</v>
+        <v>0.2993704278522334</v>
       </c>
       <c r="Z47" t="n">
-        <v>6.328292574221891</v>
+        <v>0.6861140172179395</v>
       </c>
       <c r="AA47" t="b">
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.1578947368421053</v>
+        <v>-0.05454545454545456</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.5894039735099337</v>
+        <v>0.07106077893212204</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.250691247859103</v>
+        <v>-0.1438214410151938</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.1622943326132111</v>
+        <v>-0.3514513230158984</v>
       </c>
       <c r="AF47" t="n">
-        <v>-0.4129855804723142</v>
+        <v>0.2076298820007046</v>
       </c>
       <c r="AG47" t="n">
-        <v>5.88235294117647</v>
+        <v>24</v>
       </c>
       <c r="AH47" t="n">
-        <v>45.09803921568628</v>
+        <v>6</v>
       </c>
       <c r="AI47" t="b">
         <v>0</v>
@@ -6966,22 +7054,24 @@
         <v>0</v>
       </c>
       <c r="AK47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM47" t="b">
         <v>0</v>
       </c>
       <c r="AN47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>2553.6</v>
+        <v>0</v>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP47" t="n">
-        <v>2860.79</v>
+        <v>108.71</v>
       </c>
     </row>
     <row r="48">
@@ -6992,12 +7082,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7006,94 +7096,96 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>20.15686274509804</v>
+        <v>17.4</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>167000</v>
+        <v>1000</v>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
       </c>
       <c r="L48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N48" t="n">
-        <v>167000</v>
-      </c>
-      <c r="O48" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
       <c r="P48" t="n">
-        <v>4515</v>
+        <v>163</v>
       </c>
       <c r="Q48" t="n">
-        <v>4515</v>
+        <v>163</v>
       </c>
       <c r="R48" t="n">
-        <v>539375</v>
+        <v>28620359</v>
       </c>
       <c r="S48" t="n">
-        <v>4596</v>
+        <v>169.9</v>
       </c>
       <c r="T48" t="n">
-        <v>4952</v>
+        <v>167.15</v>
       </c>
       <c r="U48" t="n">
-        <v>4998.75</v>
+        <v>168.275</v>
       </c>
       <c r="V48" t="n">
-        <v>3722.5</v>
+        <v>141.9083333333333</v>
       </c>
       <c r="W48" t="n">
-        <v>-48.55943487179229</v>
+        <v>2.11194560923667</v>
       </c>
       <c r="X48" t="n">
-        <v>64.55348598897068</v>
+        <v>3.245256987494003</v>
       </c>
       <c r="Y48" t="n">
-        <v>-113.112920860763</v>
+        <v>-1.133311378257333</v>
       </c>
       <c r="Z48" t="n">
-        <v>-119.2039387840907</v>
+        <v>-0.4431257960221235</v>
       </c>
       <c r="AA48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>-0.171559633027523</v>
+        <v>-0.1212938005390836</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.061643835616438</v>
+        <v>0.4818181818181819</v>
       </c>
       <c r="AD48" t="n">
-        <v>-0.2643561440445207</v>
+        <v>-0.2105697870088228</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.6345341947197158</v>
+        <v>0.05930607987016145</v>
       </c>
       <c r="AF48" t="n">
-        <v>-0.8988903387642365</v>
+        <v>-0.2698758668789842</v>
       </c>
       <c r="AG48" t="n">
-        <v>3.92156862745098</v>
+        <v>10</v>
       </c>
       <c r="AH48" t="n">
-        <v>78.43137254901961</v>
+        <v>40</v>
       </c>
       <c r="AI48" t="b">
         <v>0</v>
@@ -7108,14 +7200,16 @@
         <v>0</v>
       </c>
       <c r="AM48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>176.04</v>
+      </c>
       <c r="AP48" t="n">
-        <v>5670</v>
+        <v>171.87</v>
       </c>
     </row>
     <row r="49">
@@ -7126,12 +7220,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7140,94 +7234,96 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>19.76470588235294</v>
+        <v>16.8</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>530000</v>
+        <v>852000</v>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
       </c>
       <c r="L49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>852000</v>
       </c>
       <c r="N49" t="n">
-        <v>530000</v>
-      </c>
-      <c r="O49" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
       <c r="P49" t="n">
-        <v>1310</v>
+        <v>2400</v>
       </c>
       <c r="Q49" t="n">
-        <v>1310</v>
+        <v>2400</v>
       </c>
       <c r="R49" t="n">
-        <v>217275</v>
+        <v>2384993</v>
       </c>
       <c r="S49" t="n">
-        <v>1342</v>
+        <v>2582</v>
       </c>
       <c r="T49" t="n">
-        <v>1428.25</v>
+        <v>2552.75</v>
       </c>
       <c r="U49" t="n">
-        <v>1437.25</v>
+        <v>2575.25</v>
       </c>
       <c r="V49" t="n">
-        <v>1248.933333333333</v>
+        <v>2356</v>
       </c>
       <c r="W49" t="n">
-        <v>-25.30325837764099</v>
+        <v>-2.608617156733089</v>
       </c>
       <c r="X49" t="n">
-        <v>-5.043893490937784</v>
+        <v>11.03284908407442</v>
       </c>
       <c r="Y49" t="n">
-        <v>-20.2593648867032</v>
+        <v>-13.64146624080751</v>
       </c>
       <c r="Z49" t="n">
-        <v>-20.096006647351</v>
+        <v>6.328292574221891</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>-0.1208053691275168</v>
+        <v>-0.1578947368421053</v>
       </c>
       <c r="AC49" t="n">
-        <v>0.3519091847265221</v>
+        <v>0.5894039735099337</v>
       </c>
       <c r="AD49" t="n">
-        <v>-0.2136018801445145</v>
+        <v>-0.2471707233118445</v>
       </c>
       <c r="AE49" t="n">
-        <v>-0.07520045617020044</v>
+        <v>0.1668918715619132</v>
       </c>
       <c r="AF49" t="n">
-        <v>-0.1384014239743141</v>
+        <v>-0.4140625948737577</v>
       </c>
       <c r="AG49" t="n">
-        <v>11.76470588235294</v>
+        <v>6</v>
       </c>
       <c r="AH49" t="n">
-        <v>27.45098039215686</v>
+        <v>46</v>
       </c>
       <c r="AI49" t="b">
         <v>0</v>
@@ -7245,13 +7341,13 @@
         <v>0</v>
       </c>
       <c r="AN49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO49" t="n">
-        <v>1537.94</v>
+        <v>2553.6</v>
       </c>
       <c r="AP49" t="n">
-        <v>1629.47</v>
+        <v>2860.79</v>
       </c>
     </row>
     <row r="50">
@@ -7262,12 +7358,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7276,94 +7372,96 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>18.3921568627451</v>
+        <v>16.8</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>107000</v>
+        <v>530000</v>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
       </c>
       <c r="L50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>530000</v>
       </c>
       <c r="N50" t="n">
-        <v>107000</v>
-      </c>
-      <c r="O50" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
       <c r="P50" t="n">
-        <v>104</v>
+        <v>1310</v>
       </c>
       <c r="Q50" t="n">
-        <v>104</v>
+        <v>1310</v>
       </c>
       <c r="R50" t="n">
-        <v>6641744</v>
+        <v>643408</v>
       </c>
       <c r="S50" t="n">
-        <v>107</v>
+        <v>1342</v>
       </c>
       <c r="T50" t="n">
-        <v>105.625</v>
+        <v>1428.25</v>
       </c>
       <c r="U50" t="n">
-        <v>105.925</v>
+        <v>1437.25</v>
       </c>
       <c r="V50" t="n">
-        <v>107.906666692098</v>
+        <v>1248.933333333333</v>
       </c>
       <c r="W50" t="n">
-        <v>-0.2448423497634451</v>
+        <v>-25.30325837764099</v>
       </c>
       <c r="X50" t="n">
-        <v>-0.5442127776156785</v>
+        <v>-5.043893490937784</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.2993704278522334</v>
+        <v>-20.2593648867032</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.6861140172179395</v>
+        <v>-20.096006647351</v>
       </c>
       <c r="AA50" t="b">
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>-0.05454545454545456</v>
+        <v>-0.1208053691275168</v>
       </c>
       <c r="AC50" t="n">
-        <v>0.07106077893212204</v>
+        <v>0.3519091847265221</v>
       </c>
       <c r="AD50" t="n">
-        <v>-0.1473419655624523</v>
+        <v>-0.210081355597256</v>
       </c>
       <c r="AE50" t="n">
-        <v>-0.3560488619646005</v>
+        <v>-0.07060291722149836</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.2087068964021482</v>
+        <v>-0.1394784383757577</v>
       </c>
       <c r="AG50" t="n">
-        <v>23.52941176470588</v>
+        <v>12</v>
       </c>
       <c r="AH50" t="n">
-        <v>5.88235294117647</v>
+        <v>28</v>
       </c>
       <c r="AI50" t="b">
         <v>0</v>
@@ -7372,10 +7470,10 @@
         <v>0</v>
       </c>
       <c r="AK50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM50" t="b">
         <v>0</v>
@@ -7383,13 +7481,11 @@
       <c r="AN50" t="b">
         <v>0</v>
       </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+      <c r="AO50" t="n">
+        <v>1537.94</v>
       </c>
       <c r="AP50" t="n">
-        <v>108.71</v>
+        <v>1629.47</v>
       </c>
     </row>
     <row r="51">
@@ -7400,12 +7496,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7414,94 +7510,96 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>17.41176470588236</v>
+        <v>13.6</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1000</v>
+        <v>4703848</v>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
       </c>
       <c r="L51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>4703848</v>
       </c>
       <c r="N51" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O51" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
       <c r="P51" t="n">
-        <v>4400</v>
+        <v>2155</v>
       </c>
       <c r="Q51" t="n">
-        <v>4400</v>
+        <v>2155</v>
       </c>
       <c r="R51" t="n">
-        <v>599355</v>
+        <v>3368139</v>
       </c>
       <c r="S51" t="n">
-        <v>4568</v>
+        <v>2172</v>
       </c>
       <c r="T51" t="n">
-        <v>4719.5</v>
+        <v>2268.75</v>
       </c>
       <c r="U51" t="n">
-        <v>4739.25</v>
+        <v>2300</v>
       </c>
       <c r="V51" t="n">
-        <v>3861</v>
+        <v>2199</v>
       </c>
       <c r="W51" t="n">
-        <v>-0.9455549446474834</v>
+        <v>-51.05510952642089</v>
       </c>
       <c r="X51" t="n">
-        <v>60.96908293145184</v>
+        <v>-70.09140989411772</v>
       </c>
       <c r="Y51" t="n">
-        <v>-61.91463787609932</v>
+        <v>19.03630036769682</v>
       </c>
       <c r="Z51" t="n">
-        <v>-51.06745263124361</v>
+        <v>23.01011303055475</v>
       </c>
       <c r="AA51" t="b">
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>-0.08237747653806049</v>
+        <v>-0.2248201438848921</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.4691151919866443</v>
+        <v>0.3510971786833856</v>
       </c>
       <c r="AD51" t="n">
-        <v>-0.1751739875550582</v>
+        <v>-0.3140961303546314</v>
       </c>
       <c r="AE51" t="n">
-        <v>0.04200555108992177</v>
+        <v>-0.07141492326463483</v>
       </c>
       <c r="AF51" t="n">
-        <v>-0.21717953864498</v>
+        <v>-0.2426812070899965</v>
       </c>
       <c r="AG51" t="n">
-        <v>15.68627450980392</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="n">
-        <v>37.25490196078432</v>
+        <v>26</v>
       </c>
       <c r="AI51" t="b">
         <v>0</v>
@@ -7510,158 +7608,24 @@
         <v>0</v>
       </c>
       <c r="AK51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM51" t="b">
         <v>0</v>
       </c>
       <c r="AN51" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>5104</v>
+        <v>0</v>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP51" t="n">
-        <v>5226.32</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>5347</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>世界</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>15.84313725490196</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>New Entry</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>20260603</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="n">
-        <v>49</v>
-      </c>
-      <c r="K52" t="b">
-        <v>0</v>
-      </c>
-      <c r="L52" t="b">
-        <v>1</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="R52" t="n">
-        <v>9631188</v>
-      </c>
-      <c r="S52" t="n">
-        <v>169.8</v>
-      </c>
-      <c r="T52" t="n">
-        <v>167.125</v>
-      </c>
-      <c r="U52" t="n">
-        <v>168.275</v>
-      </c>
-      <c r="V52" t="n">
-        <v>141.9</v>
-      </c>
-      <c r="W52" t="n">
-        <v>2.056390053681127</v>
-      </c>
-      <c r="X52" t="n">
-        <v>3.234145876382895</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>-1.177755822701767</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>-0.4431257960221235</v>
-      </c>
-      <c r="AA52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>-0.123989218328841</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0.4772727272727273</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>-0.2167857293458387</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>0.05016308637600475</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>-0.2669488157218435</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>9.803921568627452</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>39.21568627450981</v>
-      </c>
-      <c r="AI52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN52" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO52" t="n">
-        <v>175.82</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>172.37</v>
+        <v>2869.74</v>
       </c>
     </row>
   </sheetData>

--- a/output/daily_screen_latest.xlsx
+++ b/output/daily_screen_latest.xlsx
@@ -703,7 +703,7 @@
         <v>1080</v>
       </c>
       <c r="R2" t="n">
-        <v>93330100</v>
+        <v>90546467</v>
       </c>
       <c r="S2" t="n">
         <v>961.8</v>
@@ -739,13 +739,13 @@
         <v>3.29940411186986</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.7784493248050468</v>
+        <v>0.7553215032965073</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.879427055754038</v>
+        <v>2.931721180709148</v>
       </c>
       <c r="AF2" t="n">
-        <v>-2.100977730948991</v>
+        <v>-2.176399677412641</v>
       </c>
       <c r="AG2" t="n">
         <v>100</v>
@@ -845,7 +845,7 @@
         <v>1835</v>
       </c>
       <c r="R3" t="n">
-        <v>3847667</v>
+        <v>3466139</v>
       </c>
       <c r="S3" t="n">
         <v>1623</v>
@@ -881,13 +881,13 @@
         <v>2.438061772183397</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.2616953941913094</v>
+        <v>0.2385675726827698</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.018084716067575</v>
+        <v>2.070378841022684</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1.756389321876265</v>
+        <v>-1.831811268339914</v>
       </c>
       <c r="AG3" t="n">
         <v>90</v>
@@ -987,7 +987,7 @@
         <v>145.5</v>
       </c>
       <c r="R4" t="n">
-        <v>295448011</v>
+        <v>293666572</v>
       </c>
       <c r="S4" t="n">
         <v>140.3</v>
@@ -1023,13 +1023,13 @@
         <v>1.566137531608332</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.1311000786415373</v>
+        <v>0.1079722571329977</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.14616047549251</v>
+        <v>1.19845460044762</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1.015060396850973</v>
+        <v>-1.090482343314622</v>
       </c>
       <c r="AG4" t="n">
         <v>84</v>
@@ -1129,7 +1129,7 @@
         <v>613</v>
       </c>
       <c r="R5" t="n">
-        <v>35566469</v>
+        <v>34220952</v>
       </c>
       <c r="S5" t="n">
         <v>596</v>
@@ -1147,13 +1147,13 @@
         <v>9.449331750271995</v>
       </c>
       <c r="X5" t="n">
-        <v>8.063435943982336</v>
+        <v>8.063435943982334</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.385895806289659</v>
+        <v>1.38589580628966</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.9674473519951619</v>
+        <v>-0.9674473519951601</v>
       </c>
       <c r="AA5" t="b">
         <v>1</v>
@@ -1165,13 +1165,13 @@
         <v>0.8603945371775417</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.07875051812767642</v>
+        <v>0.05562269661913688</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.4404174810617192</v>
+        <v>0.4927116060168291</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.3616669629340428</v>
+        <v>-0.4370889093976922</v>
       </c>
       <c r="AG5" t="n">
         <v>76</v>
@@ -1271,7 +1271,7 @@
         <v>1110</v>
       </c>
       <c r="R6" t="n">
-        <v>11715655</v>
+        <v>11451045</v>
       </c>
       <c r="S6" t="n">
         <v>1013.8</v>
@@ -1289,13 +1289,13 @@
         <v>68.9095567301747</v>
       </c>
       <c r="X6" t="n">
-        <v>40.17057783521094</v>
+        <v>40.17057783521093</v>
       </c>
       <c r="Y6" t="n">
-        <v>28.73897889496376</v>
+        <v>28.73897889496377</v>
       </c>
       <c r="Z6" t="n">
-        <v>23.63985513649801</v>
+        <v>23.63985513649803</v>
       </c>
       <c r="AA6" t="b">
         <v>1</v>
@@ -1307,13 +1307,13 @@
         <v>1.514156285390714</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.4602419449409125</v>
+        <v>0.437114123432373</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.094179229274891</v>
+        <v>1.146473354230001</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.6339372843339786</v>
+        <v>-0.709359230797628</v>
       </c>
       <c r="AG6" t="n">
         <v>98</v>
@@ -1413,7 +1413,7 @@
         <v>5195</v>
       </c>
       <c r="R7" t="n">
-        <v>2971148</v>
+        <v>2793257</v>
       </c>
       <c r="S7" t="n">
         <v>4728</v>
@@ -1449,13 +1449,13 @@
         <v>1.324384787472036</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.3782348205191532</v>
+        <v>0.3551069990106137</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.9044077313562133</v>
+        <v>0.9567018563113232</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.5261729108370601</v>
+        <v>-0.6015948573007095</v>
       </c>
       <c r="AG7" t="n">
         <v>96</v>
@@ -1555,7 +1555,7 @@
         <v>700</v>
       </c>
       <c r="R8" t="n">
-        <v>5434900</v>
+        <v>5083688</v>
       </c>
       <c r="S8" t="n">
         <v>634</v>
@@ -1576,10 +1576,10 @@
         <v>28.45490455737531</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.100745244828929</v>
+        <v>5.100745244828936</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1.269599205740235</v>
+        <v>-1.269599205740228</v>
       </c>
       <c r="AA8" t="b">
         <v>1</v>
@@ -1591,13 +1591,13 @@
         <v>2.146067415730337</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.2824122237737903</v>
+        <v>0.2592844022652507</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.726090359614515</v>
+        <v>1.778384484569625</v>
       </c>
       <c r="AF8" t="n">
-        <v>-1.443678135840724</v>
+        <v>-1.519100082304374</v>
       </c>
       <c r="AG8" t="n">
         <v>92</v>
@@ -1697,7 +1697,7 @@
         <v>1590</v>
       </c>
       <c r="R9" t="n">
-        <v>5945272</v>
+        <v>5844151</v>
       </c>
       <c r="S9" t="n">
         <v>1377</v>
@@ -1715,13 +1715,13 @@
         <v>98.015285816085</v>
       </c>
       <c r="X9" t="n">
-        <v>47.87158866416893</v>
+        <v>47.87158866416891</v>
       </c>
       <c r="Y9" t="n">
-        <v>50.14369715191607</v>
+        <v>50.14369715191609</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.83645712940327</v>
+        <v>37.83645712940329</v>
       </c>
       <c r="AA9" t="b">
         <v>1</v>
@@ -1733,13 +1733,13 @@
         <v>0.9495338282124184</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.3697474802928242</v>
+        <v>0.3466196587842847</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.5295567720965959</v>
+        <v>0.5818508970517058</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.1598092918037717</v>
+        <v>-0.2352312382674211</v>
       </c>
       <c r="AG9" t="n">
         <v>94</v>
@@ -1839,7 +1839,7 @@
         <v>642</v>
       </c>
       <c r="R10" t="n">
-        <v>52841590</v>
+        <v>52039171</v>
       </c>
       <c r="S10" t="n">
         <v>609.4</v>
@@ -1875,13 +1875,13 @@
         <v>2.215862658556076</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.2535487912800234</v>
+        <v>0.2304209697714839</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.795885602440253</v>
+        <v>1.848179727395363</v>
       </c>
       <c r="AF10" t="n">
-        <v>-1.54233681116023</v>
+        <v>-1.617758757623879</v>
       </c>
       <c r="AG10" t="n">
         <v>88</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>79.8</v>
+        <v>80</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>2410</v>
       </c>
       <c r="R11" t="n">
-        <v>48317253</v>
+        <v>46429815</v>
       </c>
       <c r="S11" t="n">
         <v>2376</v>
@@ -1996,16 +1996,16 @@
         <v>2159.367419433594</v>
       </c>
       <c r="W11" t="n">
-        <v>28.72707528692808</v>
+        <v>28.72707528479623</v>
       </c>
       <c r="X11" t="n">
-        <v>22.60670966297884</v>
+        <v>22.60670965872987</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.12036562394924</v>
+        <v>6.120365626066363</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.263885528615337</v>
+        <v>3.263885530995257</v>
       </c>
       <c r="AA11" t="b">
         <v>1</v>
@@ -2017,19 +2017,19 @@
         <v>0.3350439016104065</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.03960952781443594</v>
+        <v>-0.06273734932297548</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.08493315450541594</v>
+        <v>-0.03263902955030606</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.04532362669098</v>
+        <v>-0.03009831977266941</v>
       </c>
       <c r="AG11" t="n">
         <v>57.99999999999999</v>
       </c>
       <c r="AH11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI11" t="b">
         <v>1</v>
@@ -2123,7 +2123,7 @@
         <v>5600</v>
       </c>
       <c r="R12" t="n">
-        <v>1904716</v>
+        <v>1607030</v>
       </c>
       <c r="S12" t="n">
         <v>5156</v>
@@ -2141,13 +2141,13 @@
         <v>121.2452213367114</v>
       </c>
       <c r="X12" t="n">
-        <v>70.43235211848061</v>
+        <v>70.43235211848045</v>
       </c>
       <c r="Y12" t="n">
-        <v>50.81286921823083</v>
+        <v>50.81286921823099</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.766482249075558</v>
+        <v>8.766482249075764</v>
       </c>
       <c r="AA12" t="b">
         <v>1</v>
@@ -2159,13 +2159,13 @@
         <v>1.003577817531306</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.07081958456021953</v>
+        <v>0.04769176305167999</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.5836007614154832</v>
+        <v>0.6358948863705931</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.5127811768552637</v>
+        <v>-0.5882031233189131</v>
       </c>
       <c r="AG12" t="n">
         <v>74</v>
@@ -2265,7 +2265,7 @@
         <v>232.5</v>
       </c>
       <c r="R13" t="n">
-        <v>14276665</v>
+        <v>13928151</v>
       </c>
       <c r="S13" t="n">
         <v>223.9</v>
@@ -2283,13 +2283,13 @@
         <v>0.1808336102083388</v>
       </c>
       <c r="X13" t="n">
-        <v>0.03026743330141782</v>
+        <v>0.03026743330140001</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.150566176906921</v>
+        <v>0.1505661769069388</v>
       </c>
       <c r="Z13" t="n">
-        <v>-1.391634437305882</v>
+        <v>-1.391634437305859</v>
       </c>
       <c r="AA13" t="b">
         <v>1</v>
@@ -2301,13 +2301,13 @@
         <v>0.603448275862069</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.06156643056961064</v>
+        <v>-0.08469425207815018</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.1834712197462465</v>
+        <v>0.2357653447013563</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.2450376503158571</v>
+        <v>-0.3204595967795065</v>
       </c>
       <c r="AG13" t="n">
         <v>44</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>78.19999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>308.5</v>
       </c>
       <c r="R14" t="n">
-        <v>52208586</v>
+        <v>51061461</v>
       </c>
       <c r="S14" t="n">
         <v>286</v>
@@ -2443,19 +2443,19 @@
         <v>0.07867132867132876</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.04453893751472027</v>
+        <v>-0.0676667590232598</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.3413057274444937</v>
+        <v>-0.2890116024893838</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.2967667899297735</v>
+        <v>0.221344843466124</v>
       </c>
       <c r="AG14" t="n">
         <v>56.00000000000001</v>
       </c>
       <c r="AH14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI14" t="b">
         <v>1</v>
@@ -2549,7 +2549,7 @@
         <v>18960</v>
       </c>
       <c r="R15" t="n">
-        <v>174612</v>
+        <v>149137</v>
       </c>
       <c r="S15" t="n">
         <v>18371</v>
@@ -2567,13 +2567,13 @@
         <v>289.021056815247</v>
       </c>
       <c r="X15" t="n">
-        <v>214.9283984995496</v>
+        <v>214.9283984995492</v>
       </c>
       <c r="Y15" t="n">
-        <v>74.09265831569741</v>
+        <v>74.09265831569778</v>
       </c>
       <c r="Z15" t="n">
-        <v>10.48409714335804</v>
+        <v>10.48409714335853</v>
       </c>
       <c r="AA15" t="b">
         <v>1</v>
@@ -2585,13 +2585,13 @@
         <v>0.6537287396423899</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.03007440534679762</v>
+        <v>0.00694658383825808</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.2337516835265674</v>
+        <v>0.2860458084816773</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.2036772781797698</v>
+        <v>-0.2790992246434192</v>
       </c>
       <c r="AG15" t="n">
         <v>68</v>
@@ -2691,7 +2691,7 @@
         <v>1235</v>
       </c>
       <c r="R16" t="n">
-        <v>1901137</v>
+        <v>1705572</v>
       </c>
       <c r="S16" t="n">
         <v>1149</v>
@@ -2709,13 +2709,13 @@
         <v>15.31122248434031</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.758222819219924</v>
+        <v>-3.758222819220004</v>
       </c>
       <c r="Y16" t="n">
-        <v>19.06944530356023</v>
+        <v>19.06944530356031</v>
       </c>
       <c r="Z16" t="n">
-        <v>10.78046809642058</v>
+        <v>10.78046809642068</v>
       </c>
       <c r="AA16" t="b">
         <v>1</v>
@@ -2727,13 +2727,13 @@
         <v>0.4879518072289157</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.009817256749730774</v>
+        <v>-0.01331056475880876</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.06797475111309326</v>
+        <v>0.1202688760682031</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.05815749436336248</v>
+        <v>-0.1335794408270119</v>
       </c>
       <c r="AG16" t="n">
         <v>62</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>71.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>3965</v>
       </c>
       <c r="R17" t="n">
-        <v>1997604</v>
+        <v>1871730</v>
       </c>
       <c r="S17" t="n">
         <v>3853</v>
@@ -2851,13 +2851,13 @@
         <v>39.06539743496523</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.118622287748748</v>
+        <v>-2.118622287748835</v>
       </c>
       <c r="Y17" t="n">
-        <v>41.18401972271398</v>
+        <v>41.18401972271407</v>
       </c>
       <c r="Z17" t="n">
-        <v>37.57305462714218</v>
+        <v>37.5730546271423</v>
       </c>
       <c r="AA17" t="b">
         <v>1</v>
@@ -2869,19 +2869,19 @@
         <v>0.02987012987012982</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.06748042450464165</v>
+        <v>0.04435260299610211</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.3901069262456927</v>
+        <v>-0.3378128012905828</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.4575873507503343</v>
+        <v>0.3821654042866849</v>
       </c>
       <c r="AG17" t="n">
         <v>70</v>
       </c>
       <c r="AH17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI17" t="b">
         <v>1</v>
@@ -2975,7 +2975,7 @@
         <v>174.5</v>
       </c>
       <c r="R18" t="n">
-        <v>17141419</v>
+        <v>16947495</v>
       </c>
       <c r="S18" t="n">
         <v>171.3</v>
@@ -2999,7 +2999,7 @@
         <v>0.9637640155962179</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.5056640413214175</v>
+        <v>0.5056640413214177</v>
       </c>
       <c r="AA18" t="b">
         <v>1</v>
@@ -3011,13 +3011,13 @@
         <v>0.5442477876106195</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.05593197872427536</v>
+        <v>-0.07905980023281489</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.1242707314947971</v>
+        <v>0.1765648564499069</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.1802027102190724</v>
+        <v>-0.2556246566827218</v>
       </c>
       <c r="AG18" t="n">
         <v>48</v>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>66.60000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>3610</v>
       </c>
       <c r="R19" t="n">
-        <v>392583</v>
+        <v>369274</v>
       </c>
       <c r="S19" t="n">
         <v>3571</v>
@@ -3135,13 +3135,13 @@
         <v>36.41058042260102</v>
       </c>
       <c r="X19" t="n">
-        <v>-4.263569779695589</v>
+        <v>-4.263569779695644</v>
       </c>
       <c r="Y19" t="n">
-        <v>40.6741502022966</v>
+        <v>40.67415020229666</v>
       </c>
       <c r="Z19" t="n">
-        <v>39.22918240294742</v>
+        <v>39.22918240294748</v>
       </c>
       <c r="AA19" t="b">
         <v>1</v>
@@ -3153,19 +3153,19 @@
         <v>0.05865102639296182</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.04559832588754165</v>
+        <v>-0.06872614739608118</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.3613260297228607</v>
+        <v>-0.3090319047677508</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.315727703835319</v>
+        <v>0.2403057573716696</v>
       </c>
       <c r="AG19" t="n">
         <v>54</v>
       </c>
       <c r="AH19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AI19" t="b">
         <v>1</v>
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>62.8</v>
+        <v>63</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>100.5</v>
       </c>
       <c r="R20" t="n">
-        <v>5792966</v>
+        <v>5752558</v>
       </c>
       <c r="S20" t="n">
         <v>99.56000061035157</v>
@@ -3274,16 +3274,16 @@
         <v>97.92833366394044</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8774655556775883</v>
+        <v>0.8774655556775741</v>
       </c>
       <c r="X20" t="n">
-        <v>0.2303048802258596</v>
+        <v>0.2303048802258391</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.6471606754517287</v>
+        <v>0.6471606754517351</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.6278660250203199</v>
+        <v>0.6278660250203277</v>
       </c>
       <c r="AA20" t="b">
         <v>1</v>
@@ -3295,19 +3295,19 @@
         <v>0.08297410231708313</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.0708542452436407</v>
+        <v>-0.09398206675218024</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.3370029537987393</v>
+        <v>-0.2847088288436295</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.2661487085550986</v>
+        <v>0.1907267620914492</v>
       </c>
       <c r="AG20" t="n">
         <v>40</v>
       </c>
       <c r="AH20" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI20" t="b">
         <v>1</v>
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>61.2</v>
+        <v>61.4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>19.10000038146973</v>
       </c>
       <c r="R21" t="n">
-        <v>382092503</v>
+        <v>382434690</v>
       </c>
       <c r="S21" t="n">
         <v>18.87999992370606</v>
@@ -3419,13 +3419,13 @@
         <v>-0.001849338577535775</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.002493650800728089</v>
+        <v>-0.002493650800728161</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.0006443122231923138</v>
+        <v>0.0006443122231923858</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.03545533046064332</v>
+        <v>-0.03545533046064323</v>
       </c>
       <c r="AA21" t="b">
         <v>1</v>
@@ -3437,19 +3437,19 @@
         <v>0.002624732095101834</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.07375973976832828</v>
+        <v>-0.09688756127686782</v>
       </c>
       <c r="AE21" t="n">
-        <v>-0.4173523240207206</v>
+        <v>-0.3650581990656108</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.3435925842523924</v>
+        <v>0.2681706377887429</v>
       </c>
       <c r="AG21" t="n">
         <v>38</v>
       </c>
       <c r="AH21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI21" t="b">
         <v>1</v>
@@ -3543,7 +3543,7 @@
         <v>104</v>
       </c>
       <c r="R22" t="n">
-        <v>73198901</v>
+        <v>72390881</v>
       </c>
       <c r="S22" t="n">
         <v>97.28000030517578</v>
@@ -3561,13 +3561,13 @@
         <v>2.192850877210518</v>
       </c>
       <c r="X22" t="n">
-        <v>2.256292561874765</v>
+        <v>2.256292561874762</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.0634416846642476</v>
+        <v>-0.06344168466424449</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.9254176202801014</v>
+        <v>-0.9254176202800979</v>
       </c>
       <c r="AA22" t="b">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0.7838765242022261</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.247013685186865</v>
+        <v>0.2238858636783254</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.3638994680864036</v>
+        <v>0.4161935930415135</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0.1168857828995387</v>
+        <v>-0.1923077293631881</v>
       </c>
       <c r="AG22" t="n">
         <v>86</v>
@@ -3683,7 +3683,7 @@
         <v>242.5</v>
       </c>
       <c r="R23" t="n">
-        <v>9094925</v>
+        <v>8909870</v>
       </c>
       <c r="S23" t="n">
         <v>234.9</v>
@@ -3701,13 +3701,13 @@
         <v>3.705876277978376</v>
       </c>
       <c r="X23" t="n">
-        <v>5.720424743544816</v>
+        <v>5.720424743544778</v>
       </c>
       <c r="Y23" t="n">
-        <v>-2.01454846556644</v>
+        <v>-2.014548465566402</v>
       </c>
       <c r="Z23" t="n">
-        <v>-3.58913594957022</v>
+        <v>-3.5891359495702</v>
       </c>
       <c r="AA23" t="b">
         <v>1</v>
@@ -3719,13 +3719,13 @@
         <v>0.6819836647615274</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.06887525113996151</v>
+        <v>0.04574742963142198</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.2620066086457049</v>
+        <v>0.3143007336008148</v>
       </c>
       <c r="AF23" t="n">
-        <v>-0.1931313575057434</v>
+        <v>-0.2685533039693928</v>
       </c>
       <c r="AG23" t="n">
         <v>72</v>
@@ -3823,7 +3823,7 @@
         <v>160</v>
       </c>
       <c r="R24" t="n">
-        <v>11946175</v>
+        <v>11662345</v>
       </c>
       <c r="S24" t="n">
         <v>146.6</v>
@@ -3841,13 +3841,13 @@
         <v>2.80391623660816</v>
       </c>
       <c r="X24" t="n">
-        <v>3.644859539006668</v>
+        <v>3.644859539006667</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.8409433023985087</v>
+        <v>-0.8409433023985069</v>
       </c>
       <c r="Z24" t="n">
-        <v>-2.68454642839988</v>
+        <v>-2.684546428399878</v>
       </c>
       <c r="AA24" t="b">
         <v>1</v>
@@ -3859,13 +3859,13 @@
         <v>0.7710085546940613</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.08433690362527169</v>
+        <v>0.06120908211673215</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.3510314985782388</v>
+        <v>0.4033256235333487</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0.2666945949529671</v>
+        <v>-0.3421165414166165</v>
       </c>
       <c r="AG24" t="n">
         <v>78</v>
@@ -3963,7 +3963,7 @@
         <v>252</v>
       </c>
       <c r="R25" t="n">
-        <v>26294690</v>
+        <v>25915908</v>
       </c>
       <c r="S25" t="n">
         <v>231.8113830566406</v>
@@ -3999,13 +3999,13 @@
         <v>2.974146383428255</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.02348721779775031</v>
+        <v>0.0003593962892107783</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.554169327312432</v>
+        <v>2.606463452267542</v>
       </c>
       <c r="AF25" t="n">
-        <v>-2.530682109514682</v>
+        <v>-2.606104055978332</v>
       </c>
       <c r="AG25" t="n">
         <v>66</v>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>46.6</v>
+        <v>46.8</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>376</v>
       </c>
       <c r="R26" t="n">
-        <v>22484821</v>
+        <v>22067558</v>
       </c>
       <c r="S26" t="n">
         <v>370.9</v>
@@ -4139,19 +4139,19 @@
         <v>0.3428571428571427</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.09756895459317172</v>
+        <v>0.07444113308463218</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.07711991325867973</v>
+        <v>-0.02482578830356985</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.1746888678518514</v>
+        <v>0.09926692138820203</v>
       </c>
       <c r="AG26" t="n">
         <v>80</v>
       </c>
       <c r="AH26" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI26" t="b">
         <v>1</v>
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>36.6</v>
+        <v>36.8</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>92.40000152587891</v>
       </c>
       <c r="R27" t="n">
-        <v>2509595</v>
+        <v>2458862</v>
       </c>
       <c r="S27" t="n">
         <v>91.56000213623047</v>
@@ -4258,16 +4258,16 @@
         <v>88.04166653951009</v>
       </c>
       <c r="W27" t="n">
-        <v>0.5871852951527643</v>
+        <v>0.5871852951527501</v>
       </c>
       <c r="X27" t="n">
-        <v>0.6438754215860085</v>
+        <v>0.6438754215859908</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.05669012643324423</v>
+        <v>-0.05669012643324067</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.1623141115072071</v>
+        <v>-0.1623141115072027</v>
       </c>
       <c r="AA27" t="b">
         <v>1</v>
@@ -4279,19 +4279,19 @@
         <v>0.1092436751588939</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.04628720978312884</v>
+        <v>-0.06941503129166837</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.3107333809569286</v>
+        <v>-0.2584392560018187</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.2644461711737998</v>
+        <v>0.1890242247101503</v>
       </c>
       <c r="AG27" t="n">
         <v>52</v>
       </c>
       <c r="AH27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AI27" t="b">
         <v>1</v>
@@ -4383,7 +4383,7 @@
         <v>1380</v>
       </c>
       <c r="R28" t="n">
-        <v>1223811</v>
+        <v>1190191</v>
       </c>
       <c r="S28" t="n">
         <v>1319</v>
@@ -4401,13 +4401,13 @@
         <v>-11.68686481763621</v>
       </c>
       <c r="X28" t="n">
-        <v>-22.99993270421101</v>
+        <v>-22.99993270421102</v>
       </c>
       <c r="Y28" t="n">
         <v>11.31306788657481</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.510448522073439</v>
+        <v>3.510448522073442</v>
       </c>
       <c r="AA28" t="b">
         <v>1</v>
@@ -4419,13 +4419,13 @@
         <v>0.4330218068535825</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.151379280270556</v>
+        <v>-0.1745071017790956</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.01304475073776001</v>
+        <v>0.06533887569286989</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.164424031008316</v>
+        <v>-0.2398459774719655</v>
       </c>
       <c r="AG28" t="n">
         <v>22</v>
@@ -4523,7 +4523,7 @@
         <v>4390</v>
       </c>
       <c r="R29" t="n">
-        <v>12924532</v>
+        <v>12120210</v>
       </c>
       <c r="S29" t="n">
         <v>4412</v>
@@ -4559,13 +4559,13 @@
         <v>1.701538461538461</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.11340945212381</v>
+        <v>0.0902816306152705</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.281561405422639</v>
+        <v>1.333855530377749</v>
       </c>
       <c r="AF29" t="n">
-        <v>-1.168151953298829</v>
+        <v>-1.243573899762478</v>
       </c>
       <c r="AG29" t="n">
         <v>82</v>
@@ -4663,7 +4663,7 @@
         <v>968</v>
       </c>
       <c r="R30" t="n">
-        <v>20949029</v>
+        <v>20033869</v>
       </c>
       <c r="S30" t="n">
         <v>959.8</v>
@@ -4699,13 +4699,13 @@
         <v>0.939879759519038</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.05359700651754062</v>
+        <v>-0.07672482802608016</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.5199027034032155</v>
+        <v>0.5721968283583254</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.5734997099207562</v>
+        <v>-0.6489216563844056</v>
       </c>
       <c r="AG30" t="n">
         <v>50</v>
@@ -4762,7 +4762,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>40.8</v>
+        <v>41</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>268.5</v>
       </c>
       <c r="R31" t="n">
-        <v>68426612</v>
+        <v>67328101</v>
       </c>
       <c r="S31" t="n">
         <v>267.5</v>
@@ -4821,13 +4821,13 @@
         <v>0.5493819255026438</v>
       </c>
       <c r="X31" t="n">
-        <v>3.295099460379339</v>
+        <v>3.295099460379334</v>
       </c>
       <c r="Y31" t="n">
-        <v>-2.745717534876695</v>
+        <v>-2.74571753487669</v>
       </c>
       <c r="Z31" t="n">
-        <v>-3.171731307869642</v>
+        <v>-3.171731307869636</v>
       </c>
       <c r="AA31" t="b">
         <v>1</v>
@@ -4839,19 +4839,19 @@
         <v>0.3698979591836735</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.03836178133756407</v>
+        <v>-0.06148960284610361</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.05007909693214896</v>
+        <v>0.002215028022960919</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.01171731559458489</v>
+        <v>-0.06370463086906453</v>
       </c>
       <c r="AG31" t="n">
         <v>60</v>
       </c>
       <c r="AH31" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AI31" t="b">
         <v>0</v>
@@ -4943,7 +4943,7 @@
         <v>2150</v>
       </c>
       <c r="R32" t="n">
-        <v>11302188</v>
+        <v>10417286</v>
       </c>
       <c r="S32" t="n">
         <v>2185.0763671875</v>
@@ -4979,13 +4979,13 @@
         <v>0.5327960552223616</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.05855884178377746</v>
+        <v>-0.081686663292317</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.1128189991065391</v>
+        <v>0.165113124061649</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.1713778408903166</v>
+        <v>-0.246799787353966</v>
       </c>
       <c r="AG32" t="n">
         <v>46</v>
@@ -5083,7 +5083,7 @@
         <v>1355</v>
       </c>
       <c r="R33" t="n">
-        <v>3570805</v>
+        <v>3381867</v>
       </c>
       <c r="S33" t="n">
         <v>1342</v>
@@ -5101,13 +5101,13 @@
         <v>2.440208659738346</v>
       </c>
       <c r="X33" t="n">
-        <v>5.929656143604378</v>
+        <v>5.929656143604372</v>
       </c>
       <c r="Y33" t="n">
-        <v>-3.489447483866032</v>
+        <v>-3.489447483866027</v>
       </c>
       <c r="Z33" t="n">
-        <v>-3.936062255006854</v>
+        <v>-3.936062255006847</v>
       </c>
       <c r="AA33" t="b">
         <v>1</v>
@@ -5119,13 +5119,13 @@
         <v>0.4085239085239085</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.06873555801484277</v>
+        <v>-0.0918633795233823</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.01145314759191396</v>
+        <v>0.04084097736319592</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.05728241042292881</v>
+        <v>-0.1327043568865782</v>
       </c>
       <c r="AG33" t="n">
         <v>42</v>
@@ -5223,7 +5223,7 @@
         <v>6415</v>
       </c>
       <c r="R34" t="n">
-        <v>805729</v>
+        <v>757141</v>
       </c>
       <c r="S34" t="n">
         <v>6440</v>
@@ -5241,13 +5241,13 @@
         <v>184.0053761849395</v>
       </c>
       <c r="X34" t="n">
-        <v>143.7524475806851</v>
+        <v>143.752447580685</v>
       </c>
       <c r="Y34" t="n">
-        <v>40.25292860425435</v>
+        <v>40.25292860425441</v>
       </c>
       <c r="Z34" t="n">
-        <v>50.27142035210866</v>
+        <v>50.27142035210872</v>
       </c>
       <c r="AA34" t="b">
         <v>0</v>
@@ -5259,13 +5259,13 @@
         <v>0.7267833109017496</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.01218796390244647</v>
+        <v>-0.01093985760609306</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.3068062547859272</v>
+        <v>0.359100379741037</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.2946182908834807</v>
+        <v>-0.3700402373471301</v>
       </c>
       <c r="AG34" t="n">
         <v>64</v>
@@ -5365,7 +5365,7 @@
         <v>874</v>
       </c>
       <c r="R35" t="n">
-        <v>17726675</v>
+        <v>17183890</v>
       </c>
       <c r="S35" t="n">
         <v>868</v>
@@ -5383,13 +5383,13 @@
         <v>2.327944774039224</v>
       </c>
       <c r="X35" t="n">
-        <v>-0.4542524837273172</v>
+        <v>-0.454252483727319</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.782197257766541</v>
+        <v>2.782197257766543</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.850917262450268</v>
+        <v>2.85091726245027</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
@@ -5401,13 +5401,13 @@
         <v>0.6367041198501873</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.1209166882043977</v>
+        <v>-0.1440445097129373</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.2167270637343648</v>
+        <v>0.2690211886894747</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.3376437519387625</v>
+        <v>-0.4130656984024119</v>
       </c>
       <c r="AG35" t="n">
         <v>32</v>
@@ -5507,7 +5507,7 @@
         <v>1365</v>
       </c>
       <c r="R36" t="n">
-        <v>1144164</v>
+        <v>1073522</v>
       </c>
       <c r="S36" t="n">
         <v>1393</v>
@@ -5525,13 +5525,13 @@
         <v>-1.027763504678887</v>
       </c>
       <c r="X36" t="n">
-        <v>15.91647903910819</v>
+        <v>15.91647903910818</v>
       </c>
       <c r="Y36" t="n">
-        <v>-16.94424254378708</v>
+        <v>-16.94424254378707</v>
       </c>
       <c r="Z36" t="n">
-        <v>-16.83967200218795</v>
+        <v>-16.83967200218794</v>
       </c>
       <c r="AA36" t="b">
         <v>0</v>
@@ -5543,13 +5543,13 @@
         <v>0.528555431131019</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.1007383560736894</v>
+        <v>-0.123866177582229</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.1085783750151965</v>
+        <v>0.1608724999703064</v>
       </c>
       <c r="AF36" t="n">
-        <v>-0.2093167310888859</v>
+        <v>-0.2847386775525353</v>
       </c>
       <c r="AG36" t="n">
         <v>36</v>
@@ -5647,7 +5647,7 @@
         <v>2435</v>
       </c>
       <c r="R37" t="n">
-        <v>4225506</v>
+        <v>4075666</v>
       </c>
       <c r="S37" t="n">
         <v>2443</v>
@@ -5665,13 +5665,13 @@
         <v>-0.7191208455669766</v>
       </c>
       <c r="X37" t="n">
-        <v>-1.195271527021309</v>
+        <v>-1.195271527021315</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.4761506814543319</v>
+        <v>0.4761506814543384</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.733790163070471</v>
+        <v>1.733790163070479</v>
       </c>
       <c r="AA37" t="b">
         <v>0</v>
@@ -5683,13 +5683,13 @@
         <v>0.5559105431309903</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.1413554274763716</v>
+        <v>-0.1644832489849112</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.1359334870151678</v>
+        <v>0.1882276119702777</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.2772889144915395</v>
+        <v>-0.3527108609551889</v>
       </c>
       <c r="AG37" t="n">
         <v>28</v>
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>259.5</v>
       </c>
       <c r="R38" t="n">
-        <v>40413905</v>
+        <v>39425678</v>
       </c>
       <c r="S38" t="n">
         <v>258.6</v>
@@ -5805,13 +5805,13 @@
         <v>-1.254231640690193</v>
       </c>
       <c r="X38" t="n">
-        <v>0.365940243720115</v>
+        <v>0.3659402437200756</v>
       </c>
       <c r="Y38" t="n">
-        <v>-1.620171884410308</v>
+        <v>-1.620171884410269</v>
       </c>
       <c r="Z38" t="n">
-        <v>-1.921774657038597</v>
+        <v>-1.921774657038547</v>
       </c>
       <c r="AA38" t="b">
         <v>1</v>
@@ -5823,19 +5823,19 @@
         <v>0.2134372184757403</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.1073093964042247</v>
+        <v>-0.1304372179127642</v>
       </c>
       <c r="AE38" t="n">
-        <v>-0.2065398376400822</v>
+        <v>-0.1542457126849723</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.09923044123585756</v>
+        <v>0.02380849477220814</v>
       </c>
       <c r="AG38" t="n">
         <v>34</v>
       </c>
       <c r="AH38" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI38" t="b">
         <v>0</v>
@@ -5927,7 +5927,7 @@
         <v>4860</v>
       </c>
       <c r="R39" t="n">
-        <v>4586160</v>
+        <v>4599361</v>
       </c>
       <c r="S39" t="n">
         <v>4810</v>
@@ -5945,13 +5945,13 @@
         <v>66.62470605580256</v>
       </c>
       <c r="X39" t="n">
-        <v>-22.60467905852392</v>
+        <v>-22.60467905852409</v>
       </c>
       <c r="Y39" t="n">
-        <v>89.22938511432648</v>
+        <v>89.22938511432665</v>
       </c>
       <c r="Z39" t="n">
-        <v>94.99208888265446</v>
+        <v>94.99208888265466</v>
       </c>
       <c r="AA39" t="b">
         <v>0</v>
@@ -5963,13 +5963,13 @@
         <v>0.8849966592579461</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.1593126539662668</v>
+        <v>-0.1824404754748064</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.4650196031421236</v>
+        <v>0.5173137280972335</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0.6243322571083905</v>
+        <v>-0.6997542035720399</v>
       </c>
       <c r="AG39" t="n">
         <v>16</v>
@@ -6012,12 +6012,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6026,7 +6026,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -6039,11 +6039,11 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>436000</v>
+        <v>4334000</v>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -6052,7 +6052,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>436000</v>
+        <v>4334000</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -6061,87 +6061,85 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>9450</v>
+        <v>204.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>9450</v>
+        <v>204.5</v>
       </c>
       <c r="R40" t="n">
-        <v>193243</v>
+        <v>6051697</v>
       </c>
       <c r="S40" t="n">
-        <v>9672</v>
+        <v>209.1</v>
       </c>
       <c r="T40" t="n">
-        <v>8915.5</v>
+        <v>214.55</v>
       </c>
       <c r="U40" t="n">
-        <v>8918.5</v>
+        <v>215.475</v>
       </c>
       <c r="V40" t="n">
-        <v>9150.5</v>
+        <v>172.7033332824707</v>
       </c>
       <c r="W40" t="n">
-        <v>153.6259703940777</v>
+        <v>-1.089608366741174</v>
       </c>
       <c r="X40" t="n">
-        <v>-16.55327019416922</v>
+        <v>-0.3248805784357559</v>
       </c>
       <c r="Y40" t="n">
-        <v>170.179240588247</v>
+        <v>-0.7647277883054187</v>
       </c>
       <c r="Z40" t="n">
-        <v>210.5980821954069</v>
+        <v>-0.8522392626843568</v>
       </c>
       <c r="AA40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB40" t="n">
-        <v>-0.006309148264984188</v>
+        <v>-0.0829596412556054</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.1984781230183894</v>
+        <v>1.095286918003628</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.1295194144510332</v>
+        <v>-0.229297728950194</v>
       </c>
       <c r="AE40" t="n">
-        <v>-0.2214989330974331</v>
+        <v>0.7276039868429154</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.09197951864639986</v>
+        <v>-0.9569017157931093</v>
       </c>
       <c r="AG40" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AH40" t="n">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="AI40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="b">
         <v>0</v>
       </c>
       <c r="AK40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>213.5</v>
       </c>
       <c r="AP40" t="n">
-        <v>8137.37</v>
+        <v>255.58</v>
       </c>
     </row>
     <row r="41">
@@ -6152,12 +6150,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6166,7 +6164,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>20.4</v>
+        <v>21</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6179,11 +6177,11 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>4334000</v>
+        <v>436000</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -6192,7 +6190,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4334000</v>
+        <v>436000</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -6201,85 +6199,87 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>204.5</v>
+        <v>9450</v>
       </c>
       <c r="Q41" t="n">
-        <v>204.5</v>
+        <v>9450</v>
       </c>
       <c r="R41" t="n">
-        <v>6136098</v>
+        <v>179690</v>
       </c>
       <c r="S41" t="n">
-        <v>209.1</v>
+        <v>9672</v>
       </c>
       <c r="T41" t="n">
-        <v>214.55</v>
+        <v>8915.5</v>
       </c>
       <c r="U41" t="n">
-        <v>215.475</v>
+        <v>8918.5</v>
       </c>
       <c r="V41" t="n">
-        <v>172.7033332824707</v>
+        <v>9150.5</v>
       </c>
       <c r="W41" t="n">
-        <v>-1.089608366741174</v>
+        <v>153.6259703940777</v>
       </c>
       <c r="X41" t="n">
-        <v>-0.3248805784357532</v>
+        <v>-16.55327019416922</v>
       </c>
       <c r="Y41" t="n">
-        <v>-0.7647277883054212</v>
+        <v>170.179240588247</v>
       </c>
       <c r="Z41" t="n">
-        <v>-0.85223926268436</v>
+        <v>210.5980821954069</v>
       </c>
       <c r="AA41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>-0.0829596412556054</v>
+        <v>-0.006309148264984188</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.095286918003628</v>
+        <v>0.1984781230183894</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.2061699074416544</v>
+        <v>-0.1526472359595727</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.6753098618878055</v>
+        <v>-0.1692048081423232</v>
       </c>
       <c r="AF41" t="n">
-        <v>-0.8814797693294599</v>
+        <v>0.01655757218275045</v>
       </c>
       <c r="AG41" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AH41" t="n">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="AI41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ41" t="b">
         <v>0</v>
       </c>
       <c r="AK41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>213.5</v>
+        <v>0</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP41" t="n">
-        <v>255.58</v>
+        <v>8137.37</v>
       </c>
     </row>
     <row r="42">
@@ -6304,7 +6304,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>2100</v>
       </c>
       <c r="R42" t="n">
-        <v>6988221</v>
+        <v>6861015</v>
       </c>
       <c r="S42" t="n">
         <v>2177</v>
@@ -6363,13 +6363,13 @@
         <v>-31.28261017471323</v>
       </c>
       <c r="X42" t="n">
-        <v>-32.07937754523451</v>
+        <v>-32.07937754523452</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.7967673705212803</v>
+        <v>0.7967673705212945</v>
       </c>
       <c r="Z42" t="n">
-        <v>5.65777884855499</v>
+        <v>5.657778848555004</v>
       </c>
       <c r="AA42" t="b">
         <v>0</v>
@@ -6381,19 +6381,19 @@
         <v>0.1864406779661016</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.1487323079493901</v>
+        <v>-0.1718601294579296</v>
       </c>
       <c r="AE42" t="n">
-        <v>-0.2335363781497208</v>
+        <v>-0.181242253194611</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.08480407020033076</v>
+        <v>0.009382123736681347</v>
       </c>
       <c r="AG42" t="n">
         <v>24</v>
       </c>
       <c r="AH42" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI42" t="b">
         <v>0</v>
@@ -6444,7 +6444,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>205</v>
       </c>
       <c r="R43" t="n">
-        <v>3952387</v>
+        <v>3865631</v>
       </c>
       <c r="S43" t="n">
         <v>201.2</v>
@@ -6503,13 +6503,13 @@
         <v>-3.328609751023265</v>
       </c>
       <c r="X43" t="n">
-        <v>-0.4639213831637019</v>
+        <v>-0.463921383163708</v>
       </c>
       <c r="Y43" t="n">
-        <v>-2.864688367859563</v>
+        <v>-2.864688367859557</v>
       </c>
       <c r="Z43" t="n">
-        <v>-3.796386410417729</v>
+        <v>-3.796386410417721</v>
       </c>
       <c r="AA43" t="b">
         <v>1</v>
@@ -6521,19 +6521,19 @@
         <v>0.004901960784313708</v>
       </c>
       <c r="AD43" t="n">
-        <v>-0.1446899797898676</v>
+        <v>-0.1678178012984072</v>
       </c>
       <c r="AE43" t="n">
-        <v>-0.4150750953315088</v>
+        <v>-0.3627809703763989</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.2703851155416411</v>
+        <v>0.1949631690779917</v>
       </c>
       <c r="AG43" t="n">
         <v>26</v>
       </c>
       <c r="AH43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI43" t="b">
         <v>0</v>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6582,7 +6582,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>16.8</v>
+        <v>16.4</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6595,11 +6595,11 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2492000</v>
+        <v>5191000</v>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
@@ -6608,7 +6608,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2492000</v>
+        <v>5191000</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -6617,61 +6617,61 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>5130</v>
+        <v>2400</v>
       </c>
       <c r="Q44" t="n">
-        <v>5130</v>
+        <v>2400</v>
       </c>
       <c r="R44" t="n">
-        <v>1744374</v>
+        <v>3136138</v>
       </c>
       <c r="S44" t="n">
-        <v>4968</v>
+        <v>2390</v>
       </c>
       <c r="T44" t="n">
-        <v>5254.25</v>
+        <v>2560</v>
       </c>
       <c r="U44" t="n">
-        <v>5265</v>
+        <v>2564.75</v>
       </c>
       <c r="V44" t="n">
-        <v>4642.25</v>
+        <v>2471.75</v>
       </c>
       <c r="W44" t="n">
-        <v>-62.95051576770402</v>
+        <v>-60.03117086725797</v>
       </c>
       <c r="X44" t="n">
-        <v>-23.40822264482729</v>
+        <v>-36.900279770715</v>
       </c>
       <c r="Y44" t="n">
-        <v>-39.54229312287673</v>
+        <v>-23.13089109654297</v>
       </c>
       <c r="Z44" t="n">
-        <v>-66.74669513574591</v>
+        <v>-32.40244644054764</v>
       </c>
       <c r="AA44" t="b">
         <v>1</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.04022450888681006</v>
+        <v>-0.03807615230460926</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.4074074074074074</v>
+        <v>0.2030075187969924</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.1634347750728591</v>
+        <v>-0.1844142399991978</v>
       </c>
       <c r="AE44" t="n">
-        <v>-0.01256964870841504</v>
+        <v>-0.1646754123637202</v>
       </c>
       <c r="AF44" t="n">
-        <v>-0.150865126364444</v>
+        <v>-0.01973882763547763</v>
       </c>
       <c r="AG44" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH44" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AI44" t="b">
         <v>0</v>
@@ -6692,10 +6692,10 @@
         <v>1</v>
       </c>
       <c r="AO44" t="n">
-        <v>5581.44</v>
+        <v>2664</v>
       </c>
       <c r="AP44" t="n">
-        <v>5655.79</v>
+        <v>2713.42</v>
       </c>
     </row>
     <row r="45">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6720,7 +6720,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>16.2</v>
+        <v>15.6</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6733,11 +6733,11 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>5191000</v>
+        <v>1811000</v>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -6746,7 +6746,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>5191000</v>
+        <v>1811000</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -6755,61 +6755,61 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2400</v>
+        <v>1755</v>
       </c>
       <c r="Q45" t="n">
-        <v>2400</v>
+        <v>1755</v>
       </c>
       <c r="R45" t="n">
-        <v>3310976</v>
+        <v>814870</v>
       </c>
       <c r="S45" t="n">
-        <v>2390</v>
+        <v>1751</v>
       </c>
       <c r="T45" t="n">
-        <v>2560</v>
+        <v>1859.75</v>
       </c>
       <c r="U45" t="n">
-        <v>2564.75</v>
+        <v>1862.5</v>
       </c>
       <c r="V45" t="n">
-        <v>2471.75</v>
+        <v>1880</v>
       </c>
       <c r="W45" t="n">
-        <v>-60.03117086725797</v>
+        <v>-44.71998733086548</v>
       </c>
       <c r="X45" t="n">
-        <v>-36.90027977071497</v>
+        <v>-21.75812120273915</v>
       </c>
       <c r="Y45" t="n">
-        <v>-23.130891096543</v>
+        <v>-22.96186612812633</v>
       </c>
       <c r="Z45" t="n">
-        <v>-32.40244644054766</v>
+        <v>-30.00913363500874</v>
       </c>
       <c r="AA45" t="b">
         <v>1</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.03807615230460926</v>
+        <v>-0.03038674033149169</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.2030075187969924</v>
+        <v>-0.05898123324396787</v>
       </c>
       <c r="AD45" t="n">
-        <v>-0.1612864184906583</v>
+        <v>-0.1767248280260802</v>
       </c>
       <c r="AE45" t="n">
-        <v>-0.2169695373188301</v>
+        <v>-0.4266641644046805</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.05568311882817178</v>
+        <v>0.2499393363786002</v>
       </c>
       <c r="AG45" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AH45" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="AI45" t="b">
         <v>0</v>
@@ -6830,10 +6830,10 @@
         <v>1</v>
       </c>
       <c r="AO45" t="n">
-        <v>2664</v>
+        <v>2014.74</v>
       </c>
       <c r="AP45" t="n">
-        <v>2713.42</v>
+        <v>1905.26</v>
       </c>
     </row>
     <row r="46">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6858,7 +6858,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>15.4</v>
+        <v>15.6</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6871,11 +6871,11 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1811000</v>
+        <v>1000</v>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
@@ -6884,7 +6884,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1811000</v>
+        <v>1000</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -6893,61 +6893,61 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1755</v>
+        <v>4380</v>
       </c>
       <c r="Q46" t="n">
-        <v>1755</v>
+        <v>4380</v>
       </c>
       <c r="R46" t="n">
-        <v>870216</v>
+        <v>2106090</v>
       </c>
       <c r="S46" t="n">
-        <v>1751</v>
+        <v>4274</v>
       </c>
       <c r="T46" t="n">
-        <v>1859.75</v>
+        <v>4409.5</v>
       </c>
       <c r="U46" t="n">
-        <v>1862.5</v>
+        <v>4435.75</v>
       </c>
       <c r="V46" t="n">
-        <v>1880</v>
+        <v>4024.083333333333</v>
       </c>
       <c r="W46" t="n">
-        <v>-44.71998733086548</v>
+        <v>-48.34781795552317</v>
       </c>
       <c r="X46" t="n">
-        <v>-21.75812120273914</v>
+        <v>-67.41448864829414</v>
       </c>
       <c r="Y46" t="n">
-        <v>-22.96186612812634</v>
+        <v>19.06667069277097</v>
       </c>
       <c r="Z46" t="n">
-        <v>-30.00913363500875</v>
+        <v>3.071073249297058</v>
       </c>
       <c r="AA46" t="b">
         <v>1</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0.03038674033149169</v>
+        <v>-0.1070336391437309</v>
       </c>
       <c r="AC46" t="n">
-        <v>-0.05898123324396787</v>
+        <v>0.3730407523510972</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.1535970065175407</v>
+        <v>-0.2533717268383194</v>
       </c>
       <c r="AE46" t="n">
-        <v>-0.4789582893597903</v>
+        <v>0.005357821190384637</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.3253612828422496</v>
+        <v>-0.2587295480287041</v>
       </c>
       <c r="AG46" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AH46" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="AI46" t="b">
         <v>0</v>
@@ -6956,22 +6956,24 @@
         <v>0</v>
       </c>
       <c r="AK46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM46" t="b">
         <v>1</v>
       </c>
       <c r="AN46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>2014.74</v>
+        <v>0</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP46" t="n">
-        <v>1905.26</v>
+        <v>4926.05</v>
       </c>
     </row>
     <row r="47">
@@ -6996,7 +6998,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -7037,7 +7039,7 @@
         <v>98.09999847412109</v>
       </c>
       <c r="R47" t="n">
-        <v>21638033</v>
+        <v>21501870</v>
       </c>
       <c r="S47" t="n">
         <v>95.83999938964844</v>
@@ -7055,13 +7057,13 @@
         <v>-2.410840006014226</v>
       </c>
       <c r="X47" t="n">
-        <v>-2.569171642122382</v>
+        <v>-2.569171642122389</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.1583316361081564</v>
+        <v>0.158331636108163</v>
       </c>
       <c r="Z47" t="n">
-        <v>-0.3521329216939746</v>
+        <v>-0.3521329216939666</v>
       </c>
       <c r="AA47" t="b">
         <v>1</v>
@@ -7073,19 +7075,19 @@
         <v>-0.05217392778626961</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.1567078181651516</v>
+        <v>-0.1798356396736911</v>
       </c>
       <c r="AE47" t="n">
-        <v>-0.4721509839020921</v>
+        <v>-0.4198568589469822</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.3154431657369405</v>
+        <v>0.2400212192732911</v>
       </c>
       <c r="AG47" t="n">
         <v>18</v>
       </c>
       <c r="AH47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI47" t="b">
         <v>0</v>
@@ -7122,12 +7124,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,11 +7151,11 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1000</v>
+        <v>1642000</v>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -7162,7 +7164,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1000</v>
+        <v>1642000</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -7171,61 +7173,61 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>4380</v>
+        <v>693</v>
       </c>
       <c r="Q48" t="n">
-        <v>4380</v>
+        <v>693</v>
       </c>
       <c r="R48" t="n">
-        <v>2254733</v>
+        <v>2336825</v>
       </c>
       <c r="S48" t="n">
-        <v>4274</v>
+        <v>675.6</v>
       </c>
       <c r="T48" t="n">
-        <v>4409.5</v>
+        <v>750.15</v>
       </c>
       <c r="U48" t="n">
-        <v>4435.75</v>
+        <v>754.95</v>
       </c>
       <c r="V48" t="n">
-        <v>4024.083333333333</v>
+        <v>645.1595260620118</v>
       </c>
       <c r="W48" t="n">
-        <v>-48.34781795552317</v>
+        <v>-22.29641314618584</v>
       </c>
       <c r="X48" t="n">
-        <v>-67.41448864829343</v>
+        <v>-15.37163681673735</v>
       </c>
       <c r="Y48" t="n">
-        <v>19.06667069277026</v>
+        <v>-6.924776329448491</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.071073249296177</v>
+        <v>-12.31809557517377</v>
       </c>
       <c r="AA48" t="b">
         <v>1</v>
       </c>
       <c r="AB48" t="n">
-        <v>-0.1070336391437309</v>
+        <v>-0.1216730038022814</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.3730407523510972</v>
+        <v>0.4149313916455692</v>
       </c>
       <c r="AD48" t="n">
-        <v>-0.2302439053297799</v>
+        <v>-0.26801109149687</v>
       </c>
       <c r="AE48" t="n">
-        <v>-0.04693630376472524</v>
+        <v>0.04724846048485665</v>
       </c>
       <c r="AF48" t="n">
-        <v>-0.1833076015650547</v>
+        <v>-0.3152595519817266</v>
       </c>
       <c r="AG48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH48" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AI48" t="b">
         <v>0</v>
@@ -7234,24 +7236,22 @@
         <v>0</v>
       </c>
       <c r="AK48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="b">
         <v>1</v>
       </c>
       <c r="AN48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>772</v>
       </c>
       <c r="AP48" t="n">
-        <v>4926.05</v>
+        <v>855.16</v>
       </c>
     </row>
     <row r="49">
@@ -7262,12 +7262,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7276,7 +7276,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7289,11 +7289,11 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1642000</v>
+        <v>852000</v>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
@@ -7302,7 +7302,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1642000</v>
+        <v>852000</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -7311,61 +7311,61 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>693</v>
+        <v>2290</v>
       </c>
       <c r="Q49" t="n">
-        <v>693</v>
+        <v>2290</v>
       </c>
       <c r="R49" t="n">
-        <v>2412282</v>
+        <v>1055612</v>
       </c>
       <c r="S49" t="n">
-        <v>675.6</v>
+        <v>2285</v>
       </c>
       <c r="T49" t="n">
-        <v>750.15</v>
+        <v>2426.75</v>
       </c>
       <c r="U49" t="n">
-        <v>754.95</v>
+        <v>2438.5</v>
       </c>
       <c r="V49" t="n">
-        <v>645.1595260620118</v>
+        <v>2429.583333333333</v>
       </c>
       <c r="W49" t="n">
-        <v>-22.29641314618561</v>
+        <v>-59.8052702818286</v>
       </c>
       <c r="X49" t="n">
-        <v>-15.37163681673713</v>
+        <v>-61.02414486816085</v>
       </c>
       <c r="Y49" t="n">
-        <v>-6.924776329448481</v>
+        <v>1.218874586332255</v>
       </c>
       <c r="Z49" t="n">
-        <v>-12.31809557517376</v>
+        <v>-4.526472139308936</v>
       </c>
       <c r="AA49" t="b">
         <v>1</v>
       </c>
       <c r="AB49" t="n">
-        <v>-0.1216730038022814</v>
+        <v>-0.09306930693069304</v>
       </c>
       <c r="AC49" t="n">
-        <v>0.4149313916455692</v>
+        <v>0.1536523929471032</v>
       </c>
       <c r="AD49" t="n">
-        <v>-0.2448832699883304</v>
+        <v>-0.2394073946252816</v>
       </c>
       <c r="AE49" t="n">
-        <v>-0.005045664470253231</v>
+        <v>-0.2140305382136094</v>
       </c>
       <c r="AF49" t="n">
-        <v>-0.2398376055180772</v>
+        <v>-0.0253768564116722</v>
       </c>
       <c r="AG49" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AH49" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="AI49" t="b">
         <v>0</v>
@@ -7374,22 +7374,24 @@
         <v>0</v>
       </c>
       <c r="AK49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM49" t="b">
         <v>1</v>
       </c>
       <c r="AN49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>772</v>
+        <v>0</v>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP49" t="n">
-        <v>855.16</v>
+        <v>2698.95</v>
       </c>
     </row>
     <row r="50">
@@ -7400,12 +7402,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7414,7 +7416,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>13.6</v>
+        <v>13.4</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7427,11 +7429,11 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>852000</v>
+        <v>3528000</v>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
@@ -7440,7 +7442,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>852000</v>
+        <v>3528000</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -7449,61 +7451,61 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2290</v>
+        <v>332.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>2290</v>
+        <v>332.5</v>
       </c>
       <c r="R50" t="n">
-        <v>1086719</v>
+        <v>2278374</v>
       </c>
       <c r="S50" t="n">
-        <v>2285</v>
+        <v>327.5</v>
       </c>
       <c r="T50" t="n">
-        <v>2426.75</v>
+        <v>360.85</v>
       </c>
       <c r="U50" t="n">
-        <v>2438.5</v>
+        <v>363.05</v>
       </c>
       <c r="V50" t="n">
-        <v>2429.583333333333</v>
+        <v>361.4916666666667</v>
       </c>
       <c r="W50" t="n">
-        <v>-59.8052702818286</v>
+        <v>-13.25898126111616</v>
       </c>
       <c r="X50" t="n">
-        <v>-61.02414486816082</v>
+        <v>-10.29216635378428</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.21887458633222</v>
+        <v>-2.966814907331884</v>
       </c>
       <c r="Z50" t="n">
-        <v>-4.526472139308979</v>
+        <v>-4.620011422980134</v>
       </c>
       <c r="AA50" t="b">
         <v>1</v>
       </c>
       <c r="AB50" t="n">
-        <v>-0.09306930693069304</v>
+        <v>-0.1168658698539177</v>
       </c>
       <c r="AC50" t="n">
-        <v>0.1536523929471032</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AD50" t="n">
-        <v>-0.2162795731167421</v>
+        <v>-0.2632039575485062</v>
       </c>
       <c r="AE50" t="n">
-        <v>-0.2663246631687193</v>
+        <v>-0.2010162644940459</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.05004509005197721</v>
+        <v>-0.06218769305446037</v>
       </c>
       <c r="AG50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AH50" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AI50" t="b">
         <v>0</v>
@@ -7512,24 +7514,22 @@
         <v>0</v>
       </c>
       <c r="AK50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM50" t="b">
         <v>1</v>
       </c>
       <c r="AN50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>366.42</v>
       </c>
       <c r="AP50" t="n">
-        <v>2698.95</v>
+        <v>417.34</v>
       </c>
     </row>
     <row r="51">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7554,7 +7554,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>12.6</v>
+        <v>10</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7567,11 +7567,11 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>3528000</v>
+        <v>2492000</v>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -7580,7 +7580,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3528000</v>
+        <v>2492000</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -7589,61 +7589,61 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>332.5</v>
+        <v>1710</v>
       </c>
       <c r="Q51" t="n">
-        <v>332.5</v>
+        <v>1710</v>
       </c>
       <c r="R51" t="n">
-        <v>2347073</v>
+        <v>4638384</v>
       </c>
       <c r="S51" t="n">
-        <v>327.5</v>
+        <v>1656</v>
       </c>
       <c r="T51" t="n">
-        <v>360.85</v>
+        <v>4094.083337402344</v>
       </c>
       <c r="U51" t="n">
-        <v>363.05</v>
+        <v>4275.833337402344</v>
       </c>
       <c r="V51" t="n">
-        <v>361.4916666666667</v>
+        <v>4255.527779134115</v>
       </c>
       <c r="W51" t="n">
-        <v>-13.25898126111616</v>
+        <v>-957.086643197239</v>
       </c>
       <c r="X51" t="n">
-        <v>-10.29216635378428</v>
+        <v>-667.4761941077724</v>
       </c>
       <c r="Y51" t="n">
-        <v>-2.966814907331884</v>
+        <v>-289.6104490894667</v>
       </c>
       <c r="Z51" t="n">
-        <v>-4.620011422980136</v>
+        <v>-385.0157962544139</v>
       </c>
       <c r="AA51" t="b">
         <v>1</v>
       </c>
       <c r="AB51" t="n">
-        <v>-0.1168658698539177</v>
+        <v>-0.6800748362956034</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.1666666666666667</v>
+        <v>-0.5308641975308642</v>
       </c>
       <c r="AD51" t="n">
-        <v>-0.2400761360399667</v>
+        <v>-0.8264129239901919</v>
       </c>
       <c r="AE51" t="n">
-        <v>-0.2533103894491557</v>
+        <v>-0.8985471286915768</v>
       </c>
       <c r="AF51" t="n">
-        <v>0.01323425340918905</v>
+        <v>0.07213420470138487</v>
       </c>
       <c r="AG51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="AI51" t="b">
         <v>0</v>
@@ -7661,13 +7661,11 @@
         <v>1</v>
       </c>
       <c r="AN51" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>366.42</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO51" t="inlineStr"/>
       <c r="AP51" t="n">
-        <v>417.34</v>
+        <v>8034.56</v>
       </c>
     </row>
   </sheetData>

--- a/output/daily_screen_latest.xlsx
+++ b/output/daily_screen_latest.xlsx
@@ -648,12 +648,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -662,96 +662,96 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>99</v>
+        <v>97.2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>325000</v>
+        <v>20300000</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="K2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="b">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>255000</v>
+        <v>20300000</v>
       </c>
       <c r="N2" t="n">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2745098039215687</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>6125</v>
+        <v>1160</v>
       </c>
       <c r="Q2" t="n">
-        <v>6125</v>
+        <v>1160</v>
       </c>
       <c r="R2" t="n">
-        <v>2292229</v>
+        <v>21470271</v>
       </c>
       <c r="S2" t="n">
-        <v>5658</v>
+        <v>1111</v>
       </c>
       <c r="T2" t="n">
-        <v>4980</v>
+        <v>1007.15</v>
       </c>
       <c r="U2" t="n">
-        <v>4838.5</v>
+        <v>983.55</v>
       </c>
       <c r="V2" t="n">
-        <v>4604.819352213542</v>
+        <v>943.9259256998698</v>
       </c>
       <c r="W2" t="n">
-        <v>339.1818959327093</v>
+        <v>53.09956525193888</v>
       </c>
       <c r="X2" t="n">
-        <v>304.5407721244207</v>
+        <v>51.17653034688306</v>
       </c>
       <c r="Y2" t="n">
-        <v>34.64112380828857</v>
+        <v>1.923034905055829</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1.490136852063472</v>
+        <v>-0.7784486064149334</v>
       </c>
       <c r="AA2" t="b">
         <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8588770864946889</v>
+        <v>0.6860465116279071</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.356759499344496</v>
+        <v>0.192179757852287</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.714182778282908</v>
+        <v>0.5413522034161262</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3458478597079302</v>
+        <v>0.1812681182157212</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3683349185749778</v>
+        <v>0.360084085200405</v>
       </c>
       <c r="AG2" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="AH2" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI2" t="b">
         <v>1</v>
@@ -790,12 +790,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -804,96 +804,96 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>96.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>20300000</v>
+        <v>3173000</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="K3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="b">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>20300000</v>
+        <v>2424000</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>749000</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.308993399339934</v>
       </c>
       <c r="P3" t="n">
-        <v>1160</v>
+        <v>598</v>
       </c>
       <c r="Q3" t="n">
-        <v>1160</v>
+        <v>598</v>
       </c>
       <c r="R3" t="n">
-        <v>22498278</v>
+        <v>26832140</v>
       </c>
       <c r="S3" t="n">
-        <v>1111</v>
+        <v>578.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1007.15</v>
+        <v>511.35</v>
       </c>
       <c r="U3" t="n">
-        <v>983.55</v>
+        <v>500.675</v>
       </c>
       <c r="V3" t="n">
-        <v>943.9259256998698</v>
+        <v>482.0725468953451</v>
       </c>
       <c r="W3" t="n">
-        <v>53.09956525193888</v>
+        <v>32.50669457568983</v>
       </c>
       <c r="X3" t="n">
-        <v>51.17653034688306</v>
+        <v>29.21390182987749</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.923034905055829</v>
+        <v>3.292792745812346</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.7784486064149334</v>
+        <v>3.045868092022875</v>
       </c>
       <c r="AA3" t="b">
         <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6860465116279071</v>
+        <v>0.5552665799739922</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.192179757852287</v>
+        <v>-0.04589023547179905</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.5413522034161262</v>
+        <v>0.4105722717622113</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.1812681182157212</v>
+        <v>-0.05680187510836487</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.360084085200405</v>
+        <v>0.4673741468705762</v>
       </c>
       <c r="AG3" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="AH3" t="n">
-        <v>82</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="AI3" t="b">
         <v>1</v>
@@ -932,12 +932,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>89</v>
+        <v>89.60000000000001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,15 +955,15 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2407000</v>
+        <v>325000</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
@@ -972,7 +972,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2407000</v>
+        <v>325000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -981,61 +981,61 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>5725</v>
+        <v>6125</v>
       </c>
       <c r="Q4" t="n">
-        <v>5725</v>
+        <v>6125</v>
       </c>
       <c r="R4" t="n">
-        <v>1731292</v>
+        <v>2077501</v>
       </c>
       <c r="S4" t="n">
-        <v>5416</v>
+        <v>5658</v>
       </c>
       <c r="T4" t="n">
-        <v>4642.75</v>
+        <v>4980</v>
       </c>
       <c r="U4" t="n">
-        <v>4522</v>
+        <v>4838.5</v>
       </c>
       <c r="V4" t="n">
-        <v>3880.174161783854</v>
+        <v>4604.819352213542</v>
       </c>
       <c r="W4" t="n">
-        <v>392.7117627101024</v>
+        <v>339.1818959327093</v>
       </c>
       <c r="X4" t="n">
-        <v>375.877488908665</v>
+        <v>304.5407721244207</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.83427380143746</v>
+        <v>34.64112380828857</v>
       </c>
       <c r="Z4" t="n">
-        <v>-2.202117283806047</v>
+        <v>-1.490136852063472</v>
       </c>
       <c r="AA4" t="b">
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7296072507552871</v>
+        <v>0.8588770864946889</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.4437459276589066</v>
+        <v>0.356759499344496</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.5849129425435062</v>
+        <v>0.714182778282908</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.4328342880223408</v>
+        <v>0.3458478597079302</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1520786545211654</v>
+        <v>0.3683349185749778</v>
       </c>
       <c r="AG4" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AH4" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="AI4" t="b">
         <v>1</v>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>88</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1097,15 +1097,15 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1000</v>
+        <v>2407000</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
@@ -1114,7 +1114,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1000</v>
+        <v>2407000</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1123,61 +1123,61 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>6290</v>
+        <v>5725</v>
       </c>
       <c r="Q5" t="n">
-        <v>6290</v>
+        <v>5725</v>
       </c>
       <c r="R5" t="n">
-        <v>1995217</v>
+        <v>1600389</v>
       </c>
       <c r="S5" t="n">
-        <v>5704</v>
+        <v>5416</v>
       </c>
       <c r="T5" t="n">
-        <v>4815.044262695313</v>
+        <v>4642.75</v>
       </c>
       <c r="U5" t="n">
-        <v>4691.301892089844</v>
+        <v>4522</v>
       </c>
       <c r="V5" t="n">
-        <v>4410.968672688802</v>
+        <v>3880.174161783854</v>
       </c>
       <c r="W5" t="n">
-        <v>429.5721865791093</v>
+        <v>392.7117627101024</v>
       </c>
       <c r="X5" t="n">
-        <v>309.8604652852285</v>
+        <v>375.877488908665</v>
       </c>
       <c r="Y5" t="n">
-        <v>119.7117212938807</v>
+        <v>16.83427380143746</v>
       </c>
       <c r="Z5" t="n">
-        <v>83.99532845591693</v>
+        <v>-2.202117283806047</v>
       </c>
       <c r="AA5" t="b">
         <v>1</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6486889724842442</v>
+        <v>0.7296072507552871</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6486889724842442</v>
+        <v>0.4437459276589066</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.5039946642724633</v>
+        <v>0.5849129425435062</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.6377773328476783</v>
+        <v>0.4328342880223408</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.133782668575215</v>
+        <v>0.1520786545211654</v>
       </c>
       <c r="AG5" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AH5" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AI5" t="b">
         <v>1</v>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>82.39999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,15 +1239,15 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2424000</v>
+        <v>1000</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2424000</v>
+        <v>1000</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1265,61 +1265,61 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>598</v>
+        <v>6290</v>
       </c>
       <c r="Q6" t="n">
-        <v>598</v>
+        <v>6290</v>
       </c>
       <c r="R6" t="n">
-        <v>27131549</v>
+        <v>1767478</v>
       </c>
       <c r="S6" t="n">
-        <v>578.6</v>
+        <v>5704</v>
       </c>
       <c r="T6" t="n">
-        <v>511.35</v>
+        <v>4815.044262695313</v>
       </c>
       <c r="U6" t="n">
-        <v>500.675</v>
+        <v>4691.301892089844</v>
       </c>
       <c r="V6" t="n">
-        <v>482.0725468953451</v>
+        <v>4410.968672688802</v>
       </c>
       <c r="W6" t="n">
-        <v>32.50669457568983</v>
+        <v>429.572186579122</v>
       </c>
       <c r="X6" t="n">
-        <v>29.21390182987749</v>
+        <v>309.8604652852505</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.292792745812346</v>
+        <v>119.7117212938715</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.045868092022875</v>
+        <v>83.99532845590636</v>
       </c>
       <c r="AA6" t="b">
         <v>1</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.5552665799739922</v>
+        <v>0.6486889724842442</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.04589023547179905</v>
+        <v>0.6486889724842442</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.4105722717622113</v>
+        <v>0.5039946642724633</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.05680187510836487</v>
+        <v>0.6377773328476783</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.4673741468705762</v>
+        <v>-0.133782668575215</v>
       </c>
       <c r="AG6" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AH6" t="n">
-        <v>56.00000000000001</v>
+        <v>100</v>
       </c>
       <c r="AI6" t="b">
         <v>1</v>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1372,96 +1372,96 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>82.39999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2264000</v>
+        <v>11775450</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="K7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2264000</v>
+        <v>11275450</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.04434412817226807</v>
       </c>
       <c r="P7" t="n">
-        <v>2025</v>
+        <v>244</v>
       </c>
       <c r="Q7" t="n">
-        <v>2025</v>
+        <v>244</v>
       </c>
       <c r="R7" t="n">
-        <v>3202713</v>
+        <v>11512633</v>
       </c>
       <c r="S7" t="n">
-        <v>1839</v>
+        <v>237.9</v>
       </c>
       <c r="T7" t="n">
-        <v>1719.440997314453</v>
+        <v>240.35</v>
       </c>
       <c r="U7" t="n">
-        <v>1681.001763916016</v>
+        <v>238.775</v>
       </c>
       <c r="V7" t="n">
-        <v>1640.84726155599</v>
+        <v>270.8521397908528</v>
       </c>
       <c r="W7" t="n">
-        <v>79.60340323182891</v>
+        <v>-3.11912456472777</v>
       </c>
       <c r="X7" t="n">
-        <v>77.14416478933049</v>
+        <v>-4.436956679482782</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.459238442498417</v>
+        <v>1.317832114755013</v>
       </c>
       <c r="Z7" t="n">
-        <v>-15.61774800188736</v>
+        <v>0.6721212416469449</v>
       </c>
       <c r="AA7" t="b">
         <v>1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.6119847834731136</v>
+        <v>0.148235294117647</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.06887636399273589</v>
+        <v>-0.1609187609786219</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.4672904752613327</v>
+        <v>0.003540985905866156</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.07978800362930172</v>
+        <v>-0.1718304006151877</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.5470784788906344</v>
+        <v>0.1753713865210539</v>
       </c>
       <c r="AG7" t="n">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="AH7" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="b">
         <v>1</v>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>79</v>
+        <v>82.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1523,24 +1523,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>89518000</v>
+        <v>2264000</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="K8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>89518000</v>
+        <v>2264000</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1549,61 +1549,61 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>123.5</v>
+        <v>2025</v>
       </c>
       <c r="Q8" t="n">
-        <v>123.5</v>
+        <v>2025</v>
       </c>
       <c r="R8" t="n">
-        <v>83311049</v>
+        <v>2911775</v>
       </c>
       <c r="S8" t="n">
-        <v>120.8</v>
+        <v>1839</v>
       </c>
       <c r="T8" t="n">
-        <v>120.075</v>
+        <v>1719.440997314453</v>
       </c>
       <c r="U8" t="n">
-        <v>119.025</v>
+        <v>1681.001763916016</v>
       </c>
       <c r="V8" t="n">
-        <v>136.4694867451986</v>
+        <v>1640.84726155599</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.815054231425961</v>
+        <v>79.60340323182891</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.432987846716038</v>
+        <v>77.14416478933049</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.617933615290077</v>
+        <v>2.459238442498417</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.576373958249577</v>
+        <v>-15.61774800188736</v>
       </c>
       <c r="AA8" t="b">
         <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.2048780487804878</v>
+        <v>0.6119847834731136</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.1122712976242549</v>
+        <v>-0.06887636399273589</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0601837405687069</v>
+        <v>0.4672904752613327</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.1231829372608207</v>
+        <v>-0.07978800362930172</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1833666778295276</v>
+        <v>0.5470784788906344</v>
       </c>
       <c r="AG8" t="n">
+        <v>92</v>
+      </c>
+      <c r="AH8" t="n">
         <v>50</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>42</v>
       </c>
       <c r="AI8" t="b">
         <v>1</v>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>79</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1665,24 +1665,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3249000</v>
+        <v>89518000</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="K9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="b">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3249000</v>
+        <v>89518000</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1691,61 +1691,61 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>199.5</v>
+        <v>123.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>199.5</v>
+        <v>123.5</v>
       </c>
       <c r="R9" t="n">
-        <v>15164857</v>
+        <v>82518327</v>
       </c>
       <c r="S9" t="n">
-        <v>185.4</v>
+        <v>120.8</v>
       </c>
       <c r="T9" t="n">
-        <v>167.75</v>
+        <v>120.075</v>
       </c>
       <c r="U9" t="n">
-        <v>164.6</v>
+        <v>119.025</v>
       </c>
       <c r="V9" t="n">
-        <v>180.5781855265299</v>
+        <v>136.4694867451986</v>
       </c>
       <c r="W9" t="n">
-        <v>6.79835396613791</v>
+        <v>-0.815054231425961</v>
       </c>
       <c r="X9" t="n">
-        <v>3.697889821579373</v>
+        <v>-2.432987846716038</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.100464144558536</v>
+        <v>1.617933615290077</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.976511195033771</v>
+        <v>1.576373958249577</v>
       </c>
       <c r="AA9" t="b">
         <v>1</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.4615384615384615</v>
+        <v>0.2048780487804878</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.04331039666403391</v>
+        <v>-0.1122712976242549</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.3168441533266806</v>
+        <v>0.0601837405687069</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.05422203630059974</v>
+        <v>-0.1231829372608207</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.3710661896272803</v>
+        <v>0.1833666778295276</v>
       </c>
       <c r="AG9" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="AH9" t="n">
-        <v>57.99999999999999</v>
+        <v>42</v>
       </c>
       <c r="AI9" t="b">
         <v>1</v>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>77.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1807,15 +1807,15 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1301000</v>
+        <v>3249000</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -1824,7 +1824,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1301000</v>
+        <v>3249000</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1833,61 +1833,61 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1195</v>
+        <v>199.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1195</v>
+        <v>199.5</v>
       </c>
       <c r="R10" t="n">
-        <v>3087008</v>
+        <v>14854026</v>
       </c>
       <c r="S10" t="n">
-        <v>1156</v>
+        <v>185.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1099.9</v>
+        <v>167.75</v>
       </c>
       <c r="U10" t="n">
-        <v>1083.1</v>
+        <v>164.6</v>
       </c>
       <c r="V10" t="n">
-        <v>1198.95</v>
+        <v>180.5781855265299</v>
       </c>
       <c r="W10" t="n">
-        <v>25.1395080137338</v>
+        <v>6.79835396613791</v>
       </c>
       <c r="X10" t="n">
-        <v>21.27593297386527</v>
+        <v>3.697889821579373</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.863575039868529</v>
+        <v>3.100464144558536</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.309725039438682</v>
+        <v>1.976511195033771</v>
       </c>
       <c r="AA10" t="b">
         <v>1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.3911525029103609</v>
+        <v>0.4615384615384615</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.138095238095238</v>
+        <v>-0.04331039666403391</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.24645819469858</v>
+        <v>0.3168441533266806</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.1271835984586722</v>
+        <v>-0.05422203630059974</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1192745962399078</v>
+        <v>0.3710661896272803</v>
       </c>
       <c r="AG10" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="AH10" t="n">
-        <v>76</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AI10" t="b">
         <v>1</v>
@@ -1926,12 +1926,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>76.2</v>
+        <v>78.2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1949,15 +1949,15 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5000</v>
+        <v>1301000</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>5000</v>
+        <v>1301000</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1975,61 +1975,61 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>150.5</v>
+        <v>1195</v>
       </c>
       <c r="Q11" t="n">
-        <v>150.5</v>
+        <v>1195</v>
       </c>
       <c r="R11" t="n">
-        <v>40338426</v>
+        <v>3010724</v>
       </c>
       <c r="S11" t="n">
-        <v>138.6</v>
+        <v>1156</v>
       </c>
       <c r="T11" t="n">
-        <v>135.1</v>
+        <v>1099.9</v>
       </c>
       <c r="U11" t="n">
-        <v>133.2</v>
+        <v>1083.1</v>
       </c>
       <c r="V11" t="n">
-        <v>157.025</v>
+        <v>1198.95</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1522793311982014</v>
+        <v>25.1395080137338</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.888666613704749</v>
+        <v>21.27593297386527</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.04094594490295</v>
+        <v>3.863575039868529</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.8448485737029552</v>
+        <v>3.309725039438682</v>
       </c>
       <c r="AA11" t="b">
         <v>1</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.3377777777777777</v>
+        <v>0.3911525029103609</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.03082191780821919</v>
+        <v>0.138095238095238</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.1930834695659969</v>
+        <v>0.24645819469858</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.01991027817165336</v>
+        <v>0.1271835984586722</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.1731731913943435</v>
+        <v>0.1192745962399078</v>
       </c>
       <c r="AG11" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AH11" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AI11" t="b">
         <v>1</v>
@@ -2068,12 +2068,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>75.8</v>
+        <v>76.60000000000001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2091,15 +2091,15 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2117,61 +2117,61 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>449.5</v>
+        <v>150.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>449.5</v>
+        <v>150.5</v>
       </c>
       <c r="R12" t="n">
-        <v>32223309</v>
+        <v>39767333</v>
       </c>
       <c r="S12" t="n">
-        <v>429</v>
+        <v>138.6</v>
       </c>
       <c r="T12" t="n">
-        <v>385.425</v>
+        <v>135.1</v>
       </c>
       <c r="U12" t="n">
-        <v>378</v>
+        <v>133.2</v>
       </c>
       <c r="V12" t="n">
-        <v>480.5612726847331</v>
+        <v>157.025</v>
       </c>
       <c r="W12" t="n">
-        <v>13.01704649331185</v>
+        <v>0.1522793311982014</v>
       </c>
       <c r="X12" t="n">
-        <v>5.763736922661741</v>
+        <v>-1.888666613704749</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.253309570650112</v>
+        <v>2.04094594490295</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.63385989645115</v>
+        <v>0.8448485737029552</v>
       </c>
       <c r="AA12" t="b">
         <v>1</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.4933554817275747</v>
+        <v>0.3377777777777777</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.2798130484872482</v>
+        <v>0.03082191780821919</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.3486611735157938</v>
+        <v>0.1930834695659969</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.290724688123814</v>
+        <v>0.01991027817165336</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.6393858616396079</v>
+        <v>0.1731731913943435</v>
       </c>
       <c r="AG12" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="AH12" t="n">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="AI12" t="b">
         <v>1</v>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>75.2</v>
+        <v>76.2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2233,15 +2233,15 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5917000</v>
+        <v>1000</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>5917000</v>
+        <v>1000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2259,61 +2259,61 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>217.5</v>
+        <v>449.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>217.5</v>
+        <v>449.5</v>
       </c>
       <c r="R13" t="n">
-        <v>6805729</v>
+        <v>31514719</v>
       </c>
       <c r="S13" t="n">
-        <v>209.5</v>
+        <v>429</v>
       </c>
       <c r="T13" t="n">
-        <v>206.9</v>
+        <v>385.425</v>
       </c>
       <c r="U13" t="n">
-        <v>204.375</v>
+        <v>378</v>
       </c>
       <c r="V13" t="n">
-        <v>216.080667368571</v>
+        <v>480.5612726847331</v>
       </c>
       <c r="W13" t="n">
-        <v>0.9519244457859202</v>
+        <v>13.01704649331185</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8857455983234011</v>
+        <v>5.763736922661741</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.06617884746251912</v>
+        <v>7.253309570650112</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.7206094220478814</v>
+        <v>6.63385989645115</v>
       </c>
       <c r="AA13" t="b">
         <v>1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.3023952095808384</v>
+        <v>0.4933554817275747</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0341409706012219</v>
+        <v>-0.2798130484872482</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.1577009013690576</v>
+        <v>0.3486611735157938</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.02322933096465607</v>
+        <v>-0.290724688123814</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.1344715704044015</v>
+        <v>0.6393858616396079</v>
       </c>
       <c r="AG13" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="AH13" t="n">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="AI13" t="b">
         <v>1</v>
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>74.60000000000001</v>
+        <v>75.60000000000001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2375,24 +2375,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>11275450</v>
+        <v>5917000</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>11275450</v>
+        <v>5917000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2401,61 +2401,61 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>244</v>
+        <v>217.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>244</v>
+        <v>217.5</v>
       </c>
       <c r="R14" t="n">
-        <v>11841890</v>
+        <v>6732850</v>
       </c>
       <c r="S14" t="n">
-        <v>237.9</v>
+        <v>209.5</v>
       </c>
       <c r="T14" t="n">
-        <v>240.35</v>
+        <v>206.9</v>
       </c>
       <c r="U14" t="n">
-        <v>238.775</v>
+        <v>204.375</v>
       </c>
       <c r="V14" t="n">
-        <v>270.8521397908528</v>
+        <v>216.080667368571</v>
       </c>
       <c r="W14" t="n">
-        <v>-3.11912456472777</v>
+        <v>0.9519244457859202</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.436956679482782</v>
+        <v>0.8857455983234011</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.317832114755013</v>
+        <v>0.06617884746251912</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.6721212416469449</v>
+        <v>-0.7206094220478814</v>
       </c>
       <c r="AA14" t="b">
         <v>1</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.148235294117647</v>
+        <v>0.3023952095808384</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.1609187609786219</v>
+        <v>0.0341409706012219</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.003540985905866156</v>
+        <v>0.1577009013690576</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.1718304006151877</v>
+        <v>0.02322933096465607</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.1753713865210539</v>
+        <v>0.1344715704044015</v>
       </c>
       <c r="AG14" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="AI14" t="b">
         <v>1</v>
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>74.39999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2549,7 +2549,7 @@
         <v>2415</v>
       </c>
       <c r="R15" t="n">
-        <v>19200869</v>
+        <v>17662672</v>
       </c>
       <c r="S15" t="n">
         <v>2395</v>
@@ -2567,13 +2567,13 @@
         <v>7.512379202338707</v>
       </c>
       <c r="X15" t="n">
-        <v>5.194751034107651</v>
+        <v>5.194751034107684</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.317628168231056</v>
+        <v>2.317628168231023</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.4276866482360191</v>
+        <v>0.4276866482359782</v>
       </c>
       <c r="AA15" t="b">
         <v>1</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>73.8</v>
+        <v>74.2</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2691,7 +2691,7 @@
         <v>1040</v>
       </c>
       <c r="R16" t="n">
-        <v>8153691</v>
+        <v>7826161</v>
       </c>
       <c r="S16" t="n">
         <v>989.8</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>73.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2833,7 +2833,7 @@
         <v>208</v>
       </c>
       <c r="R17" t="n">
-        <v>5195633</v>
+        <v>5073518</v>
       </c>
       <c r="S17" t="n">
         <v>197.8</v>
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>71.2</v>
+        <v>71.60000000000001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2975,7 +2975,7 @@
         <v>91.09999847412109</v>
       </c>
       <c r="R18" t="n">
-        <v>32663140</v>
+        <v>32368062</v>
       </c>
       <c r="S18" t="n">
         <v>88.17999877929688</v>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>69</v>
+        <v>69.39999999999999</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -3117,7 +3117,7 @@
         <v>194</v>
       </c>
       <c r="R19" t="n">
-        <v>2807292</v>
+        <v>2754673</v>
       </c>
       <c r="S19" t="n">
         <v>188.2</v>
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>68.8</v>
+        <v>69.2</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -3259,7 +3259,7 @@
         <v>222</v>
       </c>
       <c r="R20" t="n">
-        <v>30006174</v>
+        <v>29560900</v>
       </c>
       <c r="S20" t="n">
         <v>216.6</v>
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>59</v>
+        <v>59.40000000000001</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3401,7 +3401,7 @@
         <v>332.5</v>
       </c>
       <c r="R21" t="n">
-        <v>8367187</v>
+        <v>8159737</v>
       </c>
       <c r="S21" t="n">
         <v>326.9</v>
@@ -3502,7 +3502,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>54.40000000000001</v>
+        <v>54.8</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -3543,7 +3543,7 @@
         <v>576</v>
       </c>
       <c r="R22" t="n">
-        <v>767686</v>
+        <v>739550</v>
       </c>
       <c r="S22" t="n">
         <v>564.4</v>
@@ -3644,16 +3644,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>74.40000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3670,13 +3670,13 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>5899000</v>
+        <v>5979000</v>
       </c>
       <c r="N23" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0.01356162061366333</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>3155</v>
@@ -3685,7 +3685,7 @@
         <v>3155</v>
       </c>
       <c r="R23" t="n">
-        <v>5226432</v>
+        <v>4947461</v>
       </c>
       <c r="S23" t="n">
         <v>2962</v>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>59.2</v>
+        <v>59.60000000000001</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3825,7 +3825,7 @@
         <v>1180</v>
       </c>
       <c r="R24" t="n">
-        <v>14173714</v>
+        <v>13924242</v>
       </c>
       <c r="S24" t="n">
         <v>1161</v>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3924,96 +3924,96 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53.59999999999999</v>
+        <v>53.40000000000001</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>483000</v>
+        <v>7250000</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="K25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>483000</v>
+        <v>7040000</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>0.02982954545454546</v>
       </c>
       <c r="P25" t="n">
-        <v>1300</v>
+        <v>1750</v>
       </c>
       <c r="Q25" t="n">
-        <v>1300</v>
+        <v>1750</v>
       </c>
       <c r="R25" t="n">
-        <v>2719095</v>
+        <v>9443448</v>
       </c>
       <c r="S25" t="n">
-        <v>1247</v>
+        <v>1738</v>
       </c>
       <c r="T25" t="n">
-        <v>1162.336657714844</v>
+        <v>1734.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1141.278103637695</v>
+        <v>1721.75</v>
       </c>
       <c r="V25" t="n">
-        <v>1081.19375406901</v>
+        <v>1906.26767171224</v>
       </c>
       <c r="W25" t="n">
-        <v>50.25264169210459</v>
+        <v>-5.643885602726868</v>
       </c>
       <c r="X25" t="n">
-        <v>53.96917078675011</v>
+        <v>1.336199419208324</v>
       </c>
       <c r="Y25" t="n">
-        <v>-3.716529094645523</v>
+        <v>-6.980085021935193</v>
       </c>
       <c r="Z25" t="n">
-        <v>-6.275085345966502</v>
+        <v>-8.510734281924716</v>
       </c>
       <c r="AA25" t="b">
         <v>1</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.4792412637973078</v>
+        <v>0.1705685618729098</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.3034898426481789</v>
+        <v>-0.254597101830272</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.3345469555855269</v>
+        <v>0.02587425366112894</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.2925782030116131</v>
+        <v>-0.2655087414668378</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.04196875257391386</v>
+        <v>0.2913829951279667</v>
       </c>
       <c r="AG25" t="n">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="AH25" t="n">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="AI25" t="b">
         <v>1</v>
@@ -4034,7 +4034,7 @@
         <v>1</v>
       </c>
       <c r="AO25" t="n">
-        <v>1344.2</v>
+        <v>1830.5</v>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>51.8</v>
+        <v>52.2</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -4105,7 +4105,7 @@
         <v>1530</v>
       </c>
       <c r="R26" t="n">
-        <v>5819709</v>
+        <v>5596627</v>
       </c>
       <c r="S26" t="n">
         <v>1508</v>
@@ -4190,12 +4190,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4204,7 +4204,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>51</v>
+        <v>47.8</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4213,15 +4213,15 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4843000</v>
+        <v>2226000</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
@@ -4230,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4843000</v>
+        <v>2226000</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -4239,61 +4239,61 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>5895</v>
+        <v>6785</v>
       </c>
       <c r="Q27" t="n">
-        <v>5895</v>
+        <v>6785</v>
       </c>
       <c r="R27" t="n">
-        <v>1869810</v>
+        <v>1733540</v>
       </c>
       <c r="S27" t="n">
-        <v>5717</v>
+        <v>6421</v>
       </c>
       <c r="T27" t="n">
-        <v>5520</v>
+        <v>6146.5</v>
       </c>
       <c r="U27" t="n">
-        <v>5430.25</v>
+        <v>6064</v>
       </c>
       <c r="V27" t="n">
-        <v>5257.833333333333</v>
+        <v>5391.983430989583</v>
       </c>
       <c r="W27" t="n">
-        <v>130.6047571326762</v>
+        <v>209.9020609841891</v>
       </c>
       <c r="X27" t="n">
-        <v>182.471503824608</v>
+        <v>211.2717442920707</v>
       </c>
       <c r="Y27" t="n">
-        <v>-51.86674669193175</v>
+        <v>-1.369683307881559</v>
       </c>
       <c r="Z27" t="n">
-        <v>-71.28822437679554</v>
+        <v>-33.9433149578627</v>
       </c>
       <c r="AA27" t="b">
         <v>1</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.4378048780487804</v>
+        <v>0.3213242453748784</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.212962962962963</v>
+        <v>0.2751607087289127</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.2931105698369996</v>
+        <v>0.1766299371630975</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.2020513233263972</v>
+        <v>0.2642490690923469</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.09105924651060238</v>
+        <v>-0.08761913192924942</v>
       </c>
       <c r="AG27" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="AH27" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="AI27" t="b">
         <v>1</v>
@@ -4314,7 +4314,7 @@
         <v>1</v>
       </c>
       <c r="AO27" t="n">
-        <v>6484.5</v>
+        <v>6812.14</v>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
@@ -4330,12 +4330,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4344,7 +4344,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>47.39999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4353,15 +4353,15 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2226000</v>
+        <v>1000</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
@@ -4370,7 +4370,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2226000</v>
+        <v>1000</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -4379,61 +4379,61 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>6785</v>
+        <v>3960</v>
       </c>
       <c r="Q28" t="n">
-        <v>6785</v>
+        <v>3960</v>
       </c>
       <c r="R28" t="n">
-        <v>1893940</v>
+        <v>2220335</v>
       </c>
       <c r="S28" t="n">
-        <v>6421</v>
+        <v>3802</v>
       </c>
       <c r="T28" t="n">
-        <v>6146.5</v>
+        <v>3704.75</v>
       </c>
       <c r="U28" t="n">
-        <v>6064</v>
+        <v>3647</v>
       </c>
       <c r="V28" t="n">
-        <v>5391.983430989583</v>
+        <v>3913.583333333333</v>
       </c>
       <c r="W28" t="n">
-        <v>209.9020609841891</v>
+        <v>49.20178499683698</v>
       </c>
       <c r="X28" t="n">
-        <v>211.2717442920707</v>
+        <v>50.31683805013369</v>
       </c>
       <c r="Y28" t="n">
-        <v>-1.369683307881559</v>
+        <v>-1.115053053296712</v>
       </c>
       <c r="Z28" t="n">
-        <v>-33.9433149578627</v>
+        <v>-15.54292848961093</v>
       </c>
       <c r="AA28" t="b">
         <v>1</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.3213242453748784</v>
+        <v>0.411764705882353</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.2751607087289127</v>
+        <v>-0.1344262295081967</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.1766299371630975</v>
+        <v>0.2670703976705722</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.2642490690923469</v>
+        <v>-0.1453378691447625</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.08761913192924942</v>
+        <v>0.4124082668153347</v>
       </c>
       <c r="AG28" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="AH28" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="AI28" t="b">
         <v>1</v>
@@ -4454,7 +4454,7 @@
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>6812.14</v>
+        <v>3975.84</v>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4484,24 +4484,24 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>44.39999999999999</v>
+        <v>44.2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Sell</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1000</v>
+        <v>283000</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -4510,70 +4510,70 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1000</v>
+        <v>483000</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>-200000</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>-0.4140786749482402</v>
       </c>
       <c r="P29" t="n">
-        <v>3960</v>
+        <v>1300</v>
       </c>
       <c r="Q29" t="n">
-        <v>3960</v>
+        <v>1300</v>
       </c>
       <c r="R29" t="n">
-        <v>2363105</v>
+        <v>2617519</v>
       </c>
       <c r="S29" t="n">
-        <v>3802</v>
+        <v>1247</v>
       </c>
       <c r="T29" t="n">
-        <v>3704.75</v>
+        <v>1162.336657714844</v>
       </c>
       <c r="U29" t="n">
-        <v>3647</v>
+        <v>1141.278103637695</v>
       </c>
       <c r="V29" t="n">
-        <v>3913.583333333333</v>
+        <v>1081.19375406901</v>
       </c>
       <c r="W29" t="n">
-        <v>49.20178499683698</v>
+        <v>50.25264169210459</v>
       </c>
       <c r="X29" t="n">
-        <v>50.31683805013369</v>
+        <v>53.96917078675011</v>
       </c>
       <c r="Y29" t="n">
-        <v>-1.115053053296712</v>
+        <v>-3.716529094645523</v>
       </c>
       <c r="Z29" t="n">
-        <v>-15.54292848961093</v>
+        <v>-6.275085345966502</v>
       </c>
       <c r="AA29" t="b">
         <v>1</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.411764705882353</v>
+        <v>0.4792412637973078</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.1344262295081967</v>
+        <v>0.3034898426481789</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.2670703976705722</v>
+        <v>0.3345469555855269</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.1453378691447625</v>
+        <v>0.2925782030116131</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.4124082668153347</v>
+        <v>0.04196875257391386</v>
       </c>
       <c r="AG29" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AH29" t="n">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="AI29" t="b">
         <v>1</v>
@@ -4594,7 +4594,7 @@
         <v>1</v>
       </c>
       <c r="AO29" t="n">
-        <v>3975.84</v>
+        <v>1344.2</v>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
@@ -4610,12 +4610,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4624,96 +4624,96 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>44</v>
+        <v>42.4</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Sell</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>7040000</v>
+        <v>4807000</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="b">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>7040000</v>
+        <v>4843000</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>-36000</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>-0.007433409043981004</v>
       </c>
       <c r="P30" t="n">
-        <v>1750</v>
+        <v>5895</v>
       </c>
       <c r="Q30" t="n">
-        <v>1750</v>
+        <v>5895</v>
       </c>
       <c r="R30" t="n">
-        <v>9938772</v>
+        <v>1753709</v>
       </c>
       <c r="S30" t="n">
-        <v>1738</v>
+        <v>5717</v>
       </c>
       <c r="T30" t="n">
-        <v>1734.5</v>
+        <v>5520</v>
       </c>
       <c r="U30" t="n">
-        <v>1721.75</v>
+        <v>5430.25</v>
       </c>
       <c r="V30" t="n">
-        <v>1906.26767171224</v>
+        <v>5257.833333333333</v>
       </c>
       <c r="W30" t="n">
-        <v>-5.643885602726868</v>
+        <v>130.6047571326762</v>
       </c>
       <c r="X30" t="n">
-        <v>1.336199419208324</v>
+        <v>182.471503824608</v>
       </c>
       <c r="Y30" t="n">
-        <v>-6.980085021935193</v>
+        <v>-51.86674669193175</v>
       </c>
       <c r="Z30" t="n">
-        <v>-8.510734281924716</v>
+        <v>-71.28822437679554</v>
       </c>
       <c r="AA30" t="b">
         <v>1</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.1705685618729098</v>
+        <v>0.4378048780487804</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.254597101830272</v>
+        <v>0.212962962962963</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.02587425366112894</v>
+        <v>0.2931105698369996</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.2655087414668378</v>
+        <v>0.2020513233263972</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.2913829951279667</v>
+        <v>0.09105924651060238</v>
       </c>
       <c r="AG30" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="AH30" t="n">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="AI30" t="b">
         <v>1</v>
@@ -4734,7 +4734,7 @@
         <v>1</v>
       </c>
       <c r="AO30" t="n">
-        <v>1830.5</v>
+        <v>6484.5</v>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>40.2</v>
+        <v>40.6</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -4805,7 +4805,7 @@
         <v>3945</v>
       </c>
       <c r="R31" t="n">
-        <v>8299924</v>
+        <v>7501023</v>
       </c>
       <c r="S31" t="n">
         <v>3787</v>
@@ -4826,10 +4826,10 @@
         <v>15.39100404754068</v>
       </c>
       <c r="Y31" t="n">
-        <v>-22.6445720672195</v>
+        <v>-22.64457206721951</v>
       </c>
       <c r="Z31" t="n">
-        <v>-43.79699896300946</v>
+        <v>-43.79699896300947</v>
       </c>
       <c r="AA31" t="b">
         <v>1</v>
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>37.2</v>
+        <v>37.6</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -4945,7 +4945,7 @@
         <v>1470</v>
       </c>
       <c r="R32" t="n">
-        <v>486965</v>
+        <v>471091</v>
       </c>
       <c r="S32" t="n">
         <v>1444</v>
@@ -5044,7 +5044,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>29.2</v>
+        <v>29.6</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -5085,7 +5085,7 @@
         <v>19.35000038146973</v>
       </c>
       <c r="R33" t="n">
-        <v>25207623</v>
+        <v>25171525</v>
       </c>
       <c r="S33" t="n">
         <v>19.28000030517578</v>
@@ -5184,7 +5184,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>42.40000000000001</v>
+        <v>42.8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -5225,7 +5225,7 @@
         <v>517</v>
       </c>
       <c r="R34" t="n">
-        <v>58731409</v>
+        <v>57881824</v>
       </c>
       <c r="S34" t="n">
         <v>514.6</v>
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>40.59999999999999</v>
+        <v>41</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -5365,7 +5365,7 @@
         <v>592</v>
       </c>
       <c r="R35" t="n">
-        <v>12198897</v>
+        <v>11769909</v>
       </c>
       <c r="S35" t="n">
         <v>590.4</v>
@@ -5450,12 +5450,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5464,7 +5464,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>31.4</v>
+        <v>30.40000000000001</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5473,15 +5473,15 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>383900</v>
+        <v>1000</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
@@ -5490,7 +5490,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>383900</v>
+        <v>1000</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -5499,82 +5499,84 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>15690</v>
+        <v>91.19999694824219</v>
       </c>
       <c r="Q36" t="n">
-        <v>15690</v>
+        <v>91.19999694824219</v>
       </c>
       <c r="R36" t="n">
-        <v>223397</v>
+        <v>11137453</v>
       </c>
       <c r="S36" t="n">
-        <v>15461</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="T36" t="n">
-        <v>16053</v>
+        <v>88.21999969482422</v>
       </c>
       <c r="U36" t="n">
-        <v>15914</v>
+        <v>87.67999992370605</v>
       </c>
       <c r="V36" t="n">
-        <v>15406.29347330729</v>
+        <v>81.64677772521972</v>
       </c>
       <c r="W36" t="n">
-        <v>-49.33758276984918</v>
+        <v>2.905609005013147</v>
       </c>
       <c r="X36" t="n">
-        <v>218.1345124574603</v>
+        <v>2.716943779565505</v>
       </c>
       <c r="Y36" t="n">
-        <v>-267.4720952273095</v>
+        <v>0.1886652254476422</v>
       </c>
       <c r="Z36" t="n">
-        <v>-321.9627095028877</v>
+        <v>0.9185145754391195</v>
       </c>
       <c r="AA36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.2153369481022462</v>
+        <v>0.134328298723813</v>
       </c>
       <c r="AC36" t="n">
-        <v>-0.04180143162973249</v>
+        <v>0.2379744336808547</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.07064263989046538</v>
+        <v>-0.01036600948796784</v>
       </c>
       <c r="AE36" t="n">
-        <v>-0.05271307126629832</v>
+        <v>0.2270627940442889</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.1233557111567637</v>
+        <v>-0.2374288035322567</v>
       </c>
       <c r="AG36" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="AH36" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="AI36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ36" t="b">
         <v>1</v>
       </c>
       <c r="AK36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="b">
         <v>0</v>
       </c>
-      <c r="AO36" t="n">
-        <v>18702.48</v>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
@@ -5590,12 +5592,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5604,7 +5606,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>30</v>
+        <v>30.2</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5613,24 +5615,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1000</v>
+        <v>6564000</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="K37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1000</v>
+        <v>6564000</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -5639,84 +5641,82 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>91.19999694824219</v>
+        <v>2055</v>
       </c>
       <c r="Q37" t="n">
-        <v>91.19999694824219</v>
+        <v>2055</v>
       </c>
       <c r="R37" t="n">
-        <v>11248773</v>
+        <v>3247188</v>
       </c>
       <c r="S37" t="n">
-        <v>96.09999847412109</v>
+        <v>2059</v>
       </c>
       <c r="T37" t="n">
-        <v>88.21999969482422</v>
+        <v>2187.25</v>
       </c>
       <c r="U37" t="n">
-        <v>87.67999992370605</v>
+        <v>2179.25</v>
       </c>
       <c r="V37" t="n">
-        <v>81.64677772521972</v>
+        <v>2311.557167561849</v>
       </c>
       <c r="W37" t="n">
-        <v>2.905609005013147</v>
+        <v>-51.1452606034818</v>
       </c>
       <c r="X37" t="n">
-        <v>2.716943779565505</v>
+        <v>-31.54152827317287</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.1886652254476422</v>
+        <v>-19.60373233030893</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.9185145754391195</v>
+        <v>-23.4004029675668</v>
       </c>
       <c r="AA37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.134328298723813</v>
+        <v>0.08443271767810034</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.2379744336808547</v>
+        <v>-0.1458695128482645</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.01036600948796784</v>
+        <v>-0.06026159053368052</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.2270627940442889</v>
+        <v>-0.1567811524848304</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.2374288035322567</v>
+        <v>0.09651956195114986</v>
       </c>
       <c r="AG37" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AH37" t="n">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="AI37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="b">
         <v>1</v>
       </c>
       <c r="AK37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>2276.94</v>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>29.8</v>
+        <v>26.6</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5755,24 +5755,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>6564000</v>
+        <v>1000</v>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="K38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="b">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>6564000</v>
+        <v>1000</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -5781,61 +5781,61 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2055</v>
+        <v>152</v>
       </c>
       <c r="Q38" t="n">
-        <v>2055</v>
+        <v>152</v>
       </c>
       <c r="R38" t="n">
-        <v>3415568</v>
+        <v>11281769</v>
       </c>
       <c r="S38" t="n">
-        <v>2059</v>
+        <v>151.7</v>
       </c>
       <c r="T38" t="n">
-        <v>2187.25</v>
+        <v>153.625</v>
       </c>
       <c r="U38" t="n">
-        <v>2179.25</v>
+        <v>152.675</v>
       </c>
       <c r="V38" t="n">
-        <v>2311.557167561849</v>
+        <v>166.6832621256511</v>
       </c>
       <c r="W38" t="n">
-        <v>-51.1452606034818</v>
+        <v>-1.78985609537591</v>
       </c>
       <c r="X38" t="n">
-        <v>-31.54152827317287</v>
+        <v>-1.674732104938934</v>
       </c>
       <c r="Y38" t="n">
-        <v>-19.60373233030893</v>
+        <v>-0.1151239904369759</v>
       </c>
       <c r="Z38" t="n">
-        <v>-23.4004029675668</v>
+        <v>-0.2217527988386259</v>
       </c>
       <c r="AA38" t="b">
         <v>1</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.08443271767810034</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AC38" t="n">
-        <v>-0.1458695128482645</v>
+        <v>-0.09272616902400055</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.06026159053368052</v>
+        <v>-0.001837165354638071</v>
       </c>
       <c r="AE38" t="n">
-        <v>-0.1567811524848304</v>
+        <v>-0.1036378086605664</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.09651956195114986</v>
+        <v>0.1018006433059283</v>
       </c>
       <c r="AG38" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AH38" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AI38" t="b">
         <v>0</v>
@@ -5856,7 +5856,7 @@
         <v>1</v>
       </c>
       <c r="AO38" t="n">
-        <v>2276.94</v>
+        <v>153.52</v>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
@@ -5872,12 +5872,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5886,7 +5886,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>26.2</v>
+        <v>25.8</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5895,24 +5895,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1000</v>
+        <v>25387000</v>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="K39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="b">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1000</v>
+        <v>25387000</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -5921,61 +5921,61 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>152</v>
+        <v>537</v>
       </c>
       <c r="Q39" t="n">
-        <v>152</v>
+        <v>537</v>
       </c>
       <c r="R39" t="n">
-        <v>11383874</v>
+        <v>26535435</v>
       </c>
       <c r="S39" t="n">
-        <v>151.7</v>
+        <v>549.6</v>
       </c>
       <c r="T39" t="n">
-        <v>153.625</v>
+        <v>567.425</v>
       </c>
       <c r="U39" t="n">
-        <v>152.675</v>
+        <v>565.925</v>
       </c>
       <c r="V39" t="n">
-        <v>166.6832621256511</v>
+        <v>764.7803100585937</v>
       </c>
       <c r="W39" t="n">
-        <v>-1.78985609537591</v>
+        <v>-21.93529906746051</v>
       </c>
       <c r="X39" t="n">
-        <v>-1.674732104938934</v>
+        <v>-22.80430718396826</v>
       </c>
       <c r="Y39" t="n">
-        <v>-0.1151239904369759</v>
+        <v>0.8690081165077537</v>
       </c>
       <c r="Z39" t="n">
-        <v>-0.2217527988386259</v>
+        <v>2.055263017190207</v>
       </c>
       <c r="AA39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.05917159763313617</v>
       </c>
       <c r="AC39" t="n">
-        <v>-0.09272616902400055</v>
+        <v>-0.3606937072254218</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.001837165354638071</v>
+        <v>-0.08552271057864469</v>
       </c>
       <c r="AE39" t="n">
-        <v>-0.1036378086605664</v>
+        <v>-0.3716053468619877</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.1018006433059283</v>
+        <v>0.286082636283343</v>
       </c>
       <c r="AG39" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="AH39" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="AI39" t="b">
         <v>0</v>
@@ -5984,19 +5984,21 @@
         <v>1</v>
       </c>
       <c r="AK39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>153.52</v>
+        <v>0</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
@@ -6012,12 +6014,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6026,7 +6028,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>25.4</v>
+        <v>25.2</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -6035,24 +6037,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>25387000</v>
+        <v>1000</v>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="K40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="b">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>25387000</v>
+        <v>1000</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -6061,64 +6063,64 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>537</v>
+        <v>949</v>
       </c>
       <c r="Q40" t="n">
-        <v>537</v>
+        <v>949</v>
       </c>
       <c r="R40" t="n">
-        <v>27507869</v>
+        <v>9129018</v>
       </c>
       <c r="S40" t="n">
-        <v>549.6</v>
+        <v>974.6</v>
       </c>
       <c r="T40" t="n">
-        <v>567.425</v>
+        <v>933.7</v>
       </c>
       <c r="U40" t="n">
-        <v>565.925</v>
+        <v>929.45</v>
       </c>
       <c r="V40" t="n">
-        <v>764.7803100585937</v>
+        <v>1037.341233317057</v>
       </c>
       <c r="W40" t="n">
-        <v>-21.93529906746051</v>
+        <v>-4.335645302454736</v>
       </c>
       <c r="X40" t="n">
-        <v>-22.80430718396826</v>
+        <v>-11.64239755272294</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.8690081165077537</v>
+        <v>7.3067522502682</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.055263017190207</v>
+        <v>12.75356855944192</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.05917159763313617</v>
+        <v>0.09837962962962954</v>
       </c>
       <c r="AC40" t="n">
-        <v>-0.3606937072254218</v>
+        <v>0.01347775939281615</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.08552271057864469</v>
+        <v>-0.04631467858215133</v>
       </c>
       <c r="AE40" t="n">
-        <v>-0.3716053468619877</v>
+        <v>0.002566119756250318</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.286082636283343</v>
+        <v>-0.04888079833840164</v>
       </c>
       <c r="AG40" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AH40" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="AI40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ40" t="b">
         <v>1</v>
@@ -6154,12 +6156,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6177,15 +6179,15 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1000</v>
+        <v>1645000</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -6194,7 +6196,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1000</v>
+        <v>1645000</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -6203,84 +6205,82 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>949</v>
+        <v>453</v>
       </c>
       <c r="Q41" t="n">
-        <v>949</v>
+        <v>453</v>
       </c>
       <c r="R41" t="n">
-        <v>9687682</v>
+        <v>14016263</v>
       </c>
       <c r="S41" t="n">
-        <v>974.6</v>
+        <v>447.3</v>
       </c>
       <c r="T41" t="n">
-        <v>933.7</v>
+        <v>458.375</v>
       </c>
       <c r="U41" t="n">
-        <v>929.45</v>
+        <v>455.95</v>
       </c>
       <c r="V41" t="n">
-        <v>1037.341233317057</v>
+        <v>524.8462041219076</v>
       </c>
       <c r="W41" t="n">
-        <v>-4.335645302454736</v>
+        <v>-9.638643715942294</v>
       </c>
       <c r="X41" t="n">
-        <v>-11.64239755272294</v>
+        <v>-8.794831568317107</v>
       </c>
       <c r="Y41" t="n">
-        <v>7.3067522502682</v>
+        <v>-0.8438121476251865</v>
       </c>
       <c r="Z41" t="n">
-        <v>12.75356855944192</v>
+        <v>-1.96093506684165</v>
       </c>
       <c r="AA41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.09837962962962954</v>
+        <v>0.1199011124845488</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.01347775939281615</v>
+        <v>-0.1228913714855601</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.04631467858215133</v>
+        <v>-0.02479319572723204</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.002566119756250318</v>
+        <v>-0.1338030111221259</v>
       </c>
       <c r="AF41" t="n">
-        <v>-0.04888079833840164</v>
+        <v>0.1090098153948938</v>
       </c>
       <c r="AG41" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AH41" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="AI41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="b">
         <v>1</v>
       </c>
       <c r="AK41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>462.97</v>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
@@ -6296,12 +6296,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6310,24 +6310,24 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>24.4</v>
+        <v>22.4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Sell</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1645000</v>
+        <v>341900</v>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
@@ -6336,70 +6336,70 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1645000</v>
+        <v>383900</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>-42000</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>-0.1094034904923157</v>
       </c>
       <c r="P42" t="n">
-        <v>453</v>
+        <v>15690</v>
       </c>
       <c r="Q42" t="n">
-        <v>453</v>
+        <v>15690</v>
       </c>
       <c r="R42" t="n">
-        <v>14285689</v>
+        <v>210154</v>
       </c>
       <c r="S42" t="n">
-        <v>447.3</v>
+        <v>15461</v>
       </c>
       <c r="T42" t="n">
-        <v>458.375</v>
+        <v>16053</v>
       </c>
       <c r="U42" t="n">
-        <v>455.95</v>
+        <v>15914</v>
       </c>
       <c r="V42" t="n">
-        <v>524.8462041219076</v>
+        <v>15406.29347330729</v>
       </c>
       <c r="W42" t="n">
-        <v>-9.638643715942294</v>
+        <v>-49.33758276984918</v>
       </c>
       <c r="X42" t="n">
-        <v>-8.794831568317107</v>
+        <v>218.1345124574603</v>
       </c>
       <c r="Y42" t="n">
-        <v>-0.8438121476251865</v>
+        <v>-267.4720952273095</v>
       </c>
       <c r="Z42" t="n">
-        <v>-1.96093506684165</v>
+        <v>-321.9627095028877</v>
       </c>
       <c r="AA42" t="b">
         <v>1</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.1199011124845488</v>
+        <v>0.2153369481022462</v>
       </c>
       <c r="AC42" t="n">
-        <v>-0.1228913714855601</v>
+        <v>-0.04180143162973249</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.02479319572723204</v>
+        <v>0.07064263989046538</v>
       </c>
       <c r="AE42" t="n">
-        <v>-0.1338030111221259</v>
+        <v>-0.05271307126629832</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.1090098153948938</v>
+        <v>0.1233557111567637</v>
       </c>
       <c r="AG42" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="AH42" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AI42" t="b">
         <v>0</v>
@@ -6417,10 +6417,10 @@
         <v>1</v>
       </c>
       <c r="AN42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
-        <v>462.97</v>
+        <v>18702.48</v>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>21.2</v>
+        <v>21.6</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -6491,7 +6491,7 @@
         <v>6025</v>
       </c>
       <c r="R43" t="n">
-        <v>427689</v>
+        <v>373180</v>
       </c>
       <c r="S43" t="n">
         <v>6241</v>
@@ -6590,7 +6590,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
@@ -6631,7 +6631,7 @@
         <v>2620</v>
       </c>
       <c r="R44" t="n">
-        <v>421296</v>
+        <v>399759</v>
       </c>
       <c r="S44" t="n">
         <v>2672</v>
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>19.2</v>
+        <v>19.6</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -6771,7 +6771,7 @@
         <v>5040</v>
       </c>
       <c r="R45" t="n">
-        <v>1914923</v>
+        <v>1554719</v>
       </c>
       <c r="S45" t="n">
         <v>5464</v>
@@ -6870,7 +6870,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -6911,7 +6911,7 @@
         <v>1980</v>
       </c>
       <c r="R46" t="n">
-        <v>2422998</v>
+        <v>2326025</v>
       </c>
       <c r="S46" t="n">
         <v>2051</v>
@@ -7008,7 +7008,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>16.2</v>
+        <v>16.6</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -7049,7 +7049,7 @@
         <v>82.09999847412109</v>
       </c>
       <c r="R47" t="n">
-        <v>1220393</v>
+        <v>1206158</v>
       </c>
       <c r="S47" t="n">
         <v>81.73999938964843</v>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -7189,7 +7189,7 @@
         <v>246.5</v>
       </c>
       <c r="R48" t="n">
-        <v>24136634</v>
+        <v>23533805</v>
       </c>
       <c r="S48" t="n">
         <v>245</v>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>15.6</v>
+        <v>16</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -7326,52 +7326,52 @@
         <v>82.09999847412109</v>
       </c>
       <c r="Q49" t="n">
-        <v>82.09999847412109</v>
+        <v>78.01576232910156</v>
       </c>
       <c r="R49" t="n">
-        <v>1640463</v>
+        <v>1631823</v>
       </c>
       <c r="S49" t="n">
-        <v>82.26000061035157</v>
+        <v>78.16780548095703</v>
       </c>
       <c r="T49" t="n">
-        <v>81.06999931335449</v>
+        <v>77.03700141906738</v>
       </c>
       <c r="U49" t="n">
-        <v>81.02999954223633</v>
+        <v>76.99899139404297</v>
       </c>
       <c r="V49" t="n">
-        <v>86.09833335876465</v>
+        <v>81.81518987019857</v>
       </c>
       <c r="W49" t="n">
-        <v>-0.008477399916941408</v>
+        <v>-0.008055093080699294</v>
       </c>
       <c r="X49" t="n">
-        <v>-0.4824197974681779</v>
+        <v>-0.4584205495680107</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.4739423975512365</v>
+        <v>0.4503654564873114</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.5207173265460285</v>
+        <v>0.4948135903438754</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.009840041726123738</v>
+        <v>0.00984007471429349</v>
       </c>
       <c r="AC49" t="n">
-        <v>-0.1219251500094001</v>
+        <v>-0.1219251612415708</v>
       </c>
       <c r="AD49" t="n">
-        <v>-0.1348542664856571</v>
+        <v>-0.1348542334974874</v>
       </c>
       <c r="AE49" t="n">
-        <v>-0.1328367896459659</v>
+        <v>-0.1328368008781367</v>
       </c>
       <c r="AF49" t="n">
-        <v>-0.002017476839691223</v>
+        <v>-0.002017432619350723</v>
       </c>
       <c r="AG49" t="n">
         <v>6</v>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>15.2</v>
+        <v>15.6</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -7471,7 +7471,7 @@
         <v>2005</v>
       </c>
       <c r="R50" t="n">
-        <v>4871179</v>
+        <v>4573570</v>
       </c>
       <c r="S50" t="n">
         <v>2131</v>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -7609,7 +7609,7 @@
         <v>974</v>
       </c>
       <c r="R51" t="n">
-        <v>846978</v>
+        <v>805564</v>
       </c>
       <c r="S51" t="n">
         <v>962.8</v>
